--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1796,10 +1796,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731962</v>
+        <v>119731926</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1812,21 +1812,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525906</v>
+        <v>525888</v>
       </c>
       <c r="R10" t="n">
-        <v>7179007</v>
+        <v>7178777</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1904,27 +1904,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1942,10 +1922,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119731956</v>
+        <v>119731962</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>90846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1958,21 +1938,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1985,10 +1965,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525939</v>
+        <v>525906</v>
       </c>
       <c r="R11" t="n">
-        <v>7178962</v>
+        <v>7179007</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2020,7 +2000,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2030,12 +2010,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2055,22 +2035,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2088,10 +2068,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119731926</v>
+        <v>119731956</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2104,21 +2084,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2131,10 +2111,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525888</v>
+        <v>525939</v>
       </c>
       <c r="R12" t="n">
-        <v>7178777</v>
+        <v>7178962</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2166,7 +2146,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2176,12 +2156,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2196,7 +2176,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119731921</v>
+        <v>119731946</v>
       </c>
       <c r="B13" t="n">
-        <v>79643</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2226,25 +2226,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525859</v>
+        <v>525974</v>
       </c>
       <c r="R13" t="n">
-        <v>7178751</v>
+        <v>7178925</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2322,27 +2322,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2506,10 +2506,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119731946</v>
+        <v>119731921</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>79643</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2518,25 +2518,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525974</v>
+        <v>525859</v>
       </c>
       <c r="R15" t="n">
-        <v>7178925</v>
+        <v>7178751</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119731919</v>
+        <v>119731969</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2668,31 +2668,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2700,10 +2695,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525842</v>
+        <v>525973</v>
       </c>
       <c r="R16" t="n">
-        <v>7178749</v>
+        <v>7178969</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2735,7 +2730,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2745,12 +2740,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2759,27 +2749,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2797,10 +2773,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119731935</v>
+        <v>119731919</v>
       </c>
       <c r="B17" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2813,26 +2789,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2840,10 +2821,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525983</v>
+        <v>525842</v>
       </c>
       <c r="R17" t="n">
-        <v>7178824</v>
+        <v>7178749</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2875,7 +2856,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,12 +2866,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2899,33 +2880,27 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2943,7 +2918,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119731939</v>
+        <v>119731935</v>
       </c>
       <c r="B18" t="n">
         <v>79608</v>
@@ -2986,10 +2961,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525986</v>
+        <v>525983</v>
       </c>
       <c r="R18" t="n">
-        <v>7178882</v>
+        <v>7178824</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -3021,7 +2996,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3031,12 +3006,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på knäckt levande sälg</t>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3056,12 +3031,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3071,7 +3046,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3089,10 +3064,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119731969</v>
+        <v>119731939</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3105,21 +3080,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3132,10 +3107,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525973</v>
+        <v>525986</v>
       </c>
       <c r="R19" t="n">
-        <v>7178969</v>
+        <v>7178882</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3167,7 +3142,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3177,7 +3152,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>på knäckt levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3193,6 +3173,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119731964</v>
+        <v>119731954</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3664,21 +3664,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525926</v>
+        <v>525946</v>
       </c>
       <c r="R23" t="n">
-        <v>7178980</v>
+        <v>7178956</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3736,7 +3736,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3752,6 +3757,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3769,10 +3794,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119731954</v>
+        <v>119731964</v>
       </c>
       <c r="B24" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3785,21 +3810,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3812,10 +3837,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525946</v>
+        <v>525926</v>
       </c>
       <c r="R24" t="n">
-        <v>7178956</v>
+        <v>7178980</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3847,7 +3872,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3857,12 +3882,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3878,26 +3898,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119731952</v>
+        <v>119731944</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4364,25 +4364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525970</v>
+        <v>525985</v>
       </c>
       <c r="R28" t="n">
-        <v>7178943</v>
+        <v>7178897</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4498,10 +4498,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119731944</v>
+        <v>119731952</v>
       </c>
       <c r="B29" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4510,25 +4510,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525985</v>
+        <v>525970</v>
       </c>
       <c r="R29" t="n">
-        <v>7178897</v>
+        <v>7178943</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -7681,10 +7681,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119731907</v>
+        <v>119731870</v>
       </c>
       <c r="B52" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7693,35 +7693,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7729,10 +7724,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525765</v>
+        <v>525790</v>
       </c>
       <c r="R52" t="n">
-        <v>7178799</v>
+        <v>7178955</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7764,7 +7759,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7774,12 +7769,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7788,6 +7783,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7798,17 +7794,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7826,7 +7827,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119731876</v>
+        <v>119731907</v>
       </c>
       <c r="B53" t="n">
         <v>57310</v>
@@ -7874,10 +7875,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525781</v>
+        <v>525765</v>
       </c>
       <c r="R53" t="n">
-        <v>7178998</v>
+        <v>7178799</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7909,7 +7910,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7919,7 +7920,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7971,10 +7972,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119731870</v>
+        <v>119731876</v>
       </c>
       <c r="B54" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7983,30 +7984,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -8014,10 +8020,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525790</v>
+        <v>525781</v>
       </c>
       <c r="R54" t="n">
-        <v>7178955</v>
+        <v>7178998</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -8049,7 +8055,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8059,12 +8065,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8073,7 +8079,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -8084,22 +8089,17 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -9092,10 +9092,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119731905</v>
+        <v>119731867</v>
       </c>
       <c r="B62" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9108,21 +9108,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525762</v>
+        <v>525802</v>
       </c>
       <c r="R62" t="n">
-        <v>7178853</v>
+        <v>7178930</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9238,10 +9238,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731897</v>
+        <v>119731854</v>
       </c>
       <c r="B63" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9254,21 +9254,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525705</v>
+        <v>525857</v>
       </c>
       <c r="R63" t="n">
-        <v>7178875</v>
+        <v>7178804</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9347,26 +9347,6 @@
       <c r="AH63" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9384,10 +9364,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731867</v>
+        <v>119731905</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9400,21 +9380,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9427,10 +9407,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525802</v>
+        <v>525762</v>
       </c>
       <c r="R64" t="n">
-        <v>7178930</v>
+        <v>7178853</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9462,7 +9442,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9472,12 +9452,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9497,12 +9477,12 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
@@ -9512,7 +9492,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9530,10 +9510,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119731854</v>
+        <v>119731897</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9546,21 +9526,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9573,10 +9553,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525857</v>
+        <v>525705</v>
       </c>
       <c r="R65" t="n">
-        <v>7178804</v>
+        <v>7178875</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9608,7 +9588,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9618,12 +9598,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9639,6 +9619,26 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -10365,10 +10365,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119731843</v>
+        <v>119731838</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10377,35 +10377,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -10413,10 +10408,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525949</v>
+        <v>525933</v>
       </c>
       <c r="R71" t="n">
-        <v>7178888</v>
+        <v>7178937</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10448,7 +10443,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10458,12 +10453,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10472,6 +10467,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -10482,17 +10478,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10510,10 +10511,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119731838</v>
+        <v>119731916</v>
       </c>
       <c r="B72" t="n">
-        <v>79636</v>
+        <v>79643</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10526,21 +10527,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10553,10 +10554,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>525933</v>
+        <v>525842</v>
       </c>
       <c r="R72" t="n">
-        <v>7178937</v>
+        <v>7178769</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -10588,7 +10589,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10598,7 +10599,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
@@ -10618,7 +10619,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10656,10 +10657,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119731916</v>
+        <v>119731843</v>
       </c>
       <c r="B73" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10668,30 +10669,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10699,10 +10705,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525842</v>
+        <v>525949</v>
       </c>
       <c r="R73" t="n">
-        <v>7178769</v>
+        <v>7178888</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -10734,7 +10740,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10744,12 +10750,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10758,33 +10764,27 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -11823,10 +11823,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731865</v>
+        <v>119731904</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11835,25 +11835,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11866,10 +11866,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525818</v>
+        <v>525762</v>
       </c>
       <c r="R81" t="n">
-        <v>7178903</v>
+        <v>7178853</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11901,7 +11901,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -11969,10 +11969,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731904</v>
+        <v>119731865</v>
       </c>
       <c r="B82" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11981,25 +11981,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -12012,10 +12012,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525762</v>
+        <v>525818</v>
       </c>
       <c r="R82" t="n">
-        <v>7178853</v>
+        <v>7178903</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12115,10 +12115,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119731896</v>
+        <v>119731914</v>
       </c>
       <c r="B83" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12131,31 +12131,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -12163,10 +12158,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525699</v>
+        <v>525792</v>
       </c>
       <c r="R83" t="n">
-        <v>7178908</v>
+        <v>7178785</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -12198,7 +12193,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12208,12 +12203,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -12222,6 +12217,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -12240,9 +12236,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12260,10 +12261,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119731912</v>
+        <v>119731917</v>
       </c>
       <c r="B84" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12276,31 +12277,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -12308,10 +12304,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525763</v>
+        <v>525842</v>
       </c>
       <c r="R84" t="n">
-        <v>7178776</v>
+        <v>7178769</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -12343,7 +12339,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12353,12 +12349,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12367,27 +12363,33 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -12405,10 +12407,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119731914</v>
+        <v>119731896</v>
       </c>
       <c r="B85" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12421,26 +12423,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -12448,10 +12455,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525792</v>
+        <v>525699</v>
       </c>
       <c r="R85" t="n">
-        <v>7178785</v>
+        <v>7178908</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -12483,7 +12490,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12493,12 +12500,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>på gammal stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12507,7 +12514,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -12526,14 +12532,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12551,10 +12552,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731917</v>
+        <v>119731912</v>
       </c>
       <c r="B86" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12567,26 +12568,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12594,10 +12600,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525842</v>
+        <v>525763</v>
       </c>
       <c r="R86" t="n">
-        <v>7178769</v>
+        <v>7178776</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12629,7 +12635,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12639,12 +12645,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12653,33 +12659,27 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1796,10 +1796,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731926</v>
+        <v>119731962</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1812,21 +1812,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525888</v>
+        <v>525906</v>
       </c>
       <c r="R10" t="n">
-        <v>7178777</v>
+        <v>7179007</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1904,7 +1904,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1922,10 +1942,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119731962</v>
+        <v>119731956</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>79608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1938,21 +1958,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1965,10 +1985,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525906</v>
+        <v>525939</v>
       </c>
       <c r="R11" t="n">
-        <v>7179007</v>
+        <v>7178962</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2000,7 +2020,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2010,12 +2030,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2035,22 +2055,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2068,10 +2088,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119731956</v>
+        <v>119731926</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2084,21 +2104,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2111,10 +2131,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525939</v>
+        <v>525888</v>
       </c>
       <c r="R12" t="n">
-        <v>7178962</v>
+        <v>7178777</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2146,7 +2166,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2156,12 +2176,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2176,27 +2196,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -4061,10 +4061,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119731927</v>
+        <v>119731925</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4077,26 +4077,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4104,10 +4109,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525918</v>
+        <v>525849</v>
       </c>
       <c r="R26" t="n">
-        <v>7178789</v>
+        <v>7178772</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4139,7 +4144,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4149,12 +4154,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4163,33 +4168,27 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4207,10 +4206,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119731925</v>
+        <v>119731927</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4223,31 +4222,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4255,10 +4249,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525849</v>
+        <v>525918</v>
       </c>
       <c r="R27" t="n">
-        <v>7178772</v>
+        <v>7178789</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4290,7 +4284,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4300,12 +4294,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4314,27 +4308,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119731944</v>
+        <v>119731952</v>
       </c>
       <c r="B28" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4364,25 +4364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4395,10 +4395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525985</v>
+        <v>525970</v>
       </c>
       <c r="R28" t="n">
-        <v>7178897</v>
+        <v>7178943</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4498,10 +4498,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119731952</v>
+        <v>119731944</v>
       </c>
       <c r="B29" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4510,25 +4510,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525970</v>
+        <v>525985</v>
       </c>
       <c r="R29" t="n">
-        <v>7178943</v>
+        <v>7178897</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -8674,10 +8674,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119731888</v>
+        <v>119731895</v>
       </c>
       <c r="B59" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8690,21 +8690,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8717,10 +8717,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525689</v>
+        <v>525699</v>
       </c>
       <c r="R59" t="n">
-        <v>7179025</v>
+        <v>7178908</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8783,26 +8783,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8820,10 +8800,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119731895</v>
+        <v>119731888</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8836,21 +8816,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8863,10 +8843,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525699</v>
+        <v>525689</v>
       </c>
       <c r="R60" t="n">
-        <v>7178908</v>
+        <v>7179025</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8898,7 +8878,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8908,12 +8888,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8929,6 +8909,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -9656,10 +9656,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731848</v>
+        <v>119731889</v>
       </c>
       <c r="B66" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9672,21 +9672,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525936</v>
+        <v>525688</v>
       </c>
       <c r="R66" t="n">
-        <v>7178808</v>
+        <v>7179014</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9764,27 +9764,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9802,10 +9782,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731855</v>
+        <v>119731860</v>
       </c>
       <c r="B67" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9818,26 +9798,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9845,10 +9830,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525852</v>
+        <v>525848</v>
       </c>
       <c r="R67" t="n">
-        <v>7178820</v>
+        <v>7178857</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9880,7 +9865,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9890,12 +9875,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9904,7 +9889,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9915,22 +9899,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9948,7 +9927,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119731861</v>
+        <v>119731848</v>
       </c>
       <c r="B68" t="n">
         <v>79608</v>
@@ -9991,10 +9970,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525826</v>
+        <v>525936</v>
       </c>
       <c r="R68" t="n">
-        <v>7178869</v>
+        <v>7178808</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -10026,7 +10005,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10036,7 +10015,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10056,7 +10035,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -10094,10 +10073,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119731889</v>
+        <v>119731855</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10110,21 +10089,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -10137,10 +10116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525688</v>
+        <v>525852</v>
       </c>
       <c r="R69" t="n">
-        <v>7179014</v>
+        <v>7178820</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -10172,7 +10151,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10182,12 +10161,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10203,6 +10182,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -10220,10 +10219,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119731860</v>
+        <v>119731861</v>
       </c>
       <c r="B70" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -10236,31 +10235,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -10268,10 +10262,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525848</v>
+        <v>525826</v>
       </c>
       <c r="R70" t="n">
-        <v>7178857</v>
+        <v>7178869</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10303,7 +10297,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10313,12 +10307,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10327,6 +10321,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -10337,17 +10332,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -12115,10 +12115,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119731914</v>
+        <v>119731896</v>
       </c>
       <c r="B83" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12131,26 +12131,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -12158,10 +12163,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525792</v>
+        <v>525699</v>
       </c>
       <c r="R83" t="n">
-        <v>7178785</v>
+        <v>7178908</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -12193,7 +12198,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12203,12 +12208,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>på gammal stubbe</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -12217,7 +12222,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -12236,14 +12240,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12261,10 +12260,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119731917</v>
+        <v>119731912</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12277,26 +12276,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -12304,10 +12308,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525842</v>
+        <v>525763</v>
       </c>
       <c r="R84" t="n">
-        <v>7178769</v>
+        <v>7178776</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -12339,7 +12343,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12349,12 +12353,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12363,33 +12367,27 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -12407,10 +12405,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119731896</v>
+        <v>119731914</v>
       </c>
       <c r="B85" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12423,31 +12421,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -12455,10 +12448,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525699</v>
+        <v>525792</v>
       </c>
       <c r="R85" t="n">
-        <v>7178908</v>
+        <v>7178785</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -12490,7 +12483,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12500,12 +12493,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12514,6 +12507,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -12532,9 +12526,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12552,10 +12551,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731912</v>
+        <v>119731917</v>
       </c>
       <c r="B86" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12568,31 +12567,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12600,10 +12594,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525763</v>
+        <v>525842</v>
       </c>
       <c r="R86" t="n">
-        <v>7178776</v>
+        <v>7178769</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12635,7 +12629,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12645,12 +12639,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12659,27 +12653,33 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1092,7 +1092,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119731922</v>
+        <v>119731930</v>
       </c>
       <c r="B5" t="n">
         <v>79608</v>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525859</v>
+        <v>525916</v>
       </c>
       <c r="R5" t="n">
-        <v>7178751</v>
+        <v>7178775</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1238,7 +1238,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119731932</v>
+        <v>119731969</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525935</v>
+        <v>525973</v>
       </c>
       <c r="R6" t="n">
-        <v>7178787</v>
+        <v>7178969</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1359,7 +1359,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119731924</v>
+        <v>119731966</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525862</v>
+        <v>525966</v>
       </c>
       <c r="R7" t="n">
-        <v>7178759</v>
+        <v>7178973</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1504,10 +1504,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119731950</v>
+        <v>119731919</v>
       </c>
       <c r="B8" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1516,30 +1516,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1547,10 +1552,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525969</v>
+        <v>525842</v>
       </c>
       <c r="R8" t="n">
-        <v>7178936</v>
+        <v>7178749</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1582,7 +1587,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1592,12 +1597,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på liggande död björkstam</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1606,33 +1611,27 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1650,10 +1649,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119731942</v>
+        <v>119731935</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1662,25 +1661,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1693,10 +1692,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525970</v>
+        <v>525983</v>
       </c>
       <c r="R9" t="n">
-        <v>7178901</v>
+        <v>7178824</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1728,7 +1727,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1738,12 +1737,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1763,12 +1762,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1778,7 +1777,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1796,10 +1795,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731962</v>
+        <v>119731939</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>79608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1812,21 +1811,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1839,10 +1838,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525906</v>
+        <v>525986</v>
       </c>
       <c r="R10" t="n">
-        <v>7179007</v>
+        <v>7178882</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1874,7 +1873,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1884,12 +1883,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på knäckt levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1909,22 +1908,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1942,10 +1941,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119731956</v>
+        <v>119731964</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1958,21 +1957,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1985,10 +1984,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525939</v>
+        <v>525926</v>
       </c>
       <c r="R11" t="n">
-        <v>7178962</v>
+        <v>7178980</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2020,7 +2019,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2030,12 +2029,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2051,26 +2045,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2088,10 +2062,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119731926</v>
+        <v>119731924</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2104,26 +2078,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2131,10 +2110,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525888</v>
+        <v>525862</v>
       </c>
       <c r="R12" t="n">
-        <v>7178777</v>
+        <v>7178759</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2166,7 +2145,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2176,12 +2155,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2190,13 +2169,27 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2214,10 +2207,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119731946</v>
+        <v>119731925</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2230,26 +2223,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2257,10 +2255,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525974</v>
+        <v>525849</v>
       </c>
       <c r="R13" t="n">
-        <v>7178925</v>
+        <v>7178772</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2292,7 +2290,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2302,12 +2300,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2316,13 +2314,12 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2335,14 +2332,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2360,10 +2352,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119731930</v>
+        <v>119731945</v>
       </c>
       <c r="B14" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2376,37 +2368,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525916</v>
+        <v>525961</v>
       </c>
       <c r="R14" t="n">
-        <v>7178775</v>
+        <v>7178906</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2438,7 +2427,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2448,12 +2437,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2462,34 +2446,8 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2506,10 +2464,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119731921</v>
+        <v>119731928</v>
       </c>
       <c r="B15" t="n">
-        <v>79643</v>
+        <v>79636</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2522,21 +2480,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2549,10 +2507,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525859</v>
+        <v>525916</v>
       </c>
       <c r="R15" t="n">
-        <v>7178751</v>
+        <v>7178775</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2584,7 +2542,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2594,7 +2552,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2614,7 +2572,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2652,10 +2610,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119731969</v>
+        <v>119731954</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2668,21 +2626,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2695,10 +2653,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525973</v>
+        <v>525946</v>
       </c>
       <c r="R16" t="n">
-        <v>7178969</v>
+        <v>7178956</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2730,7 +2688,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2740,7 +2698,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2756,6 +2719,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2773,10 +2756,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119731919</v>
+        <v>119731943</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2785,35 +2768,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2821,10 +2799,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525842</v>
+        <v>525979</v>
       </c>
       <c r="R17" t="n">
-        <v>7178749</v>
+        <v>7178902</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2856,7 +2834,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2866,12 +2844,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2880,27 +2858,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2918,10 +2902,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119731935</v>
+        <v>119731942</v>
       </c>
       <c r="B18" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2930,25 +2914,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2961,10 +2945,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525983</v>
+        <v>525970</v>
       </c>
       <c r="R18" t="n">
-        <v>7178824</v>
+        <v>7178901</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2996,7 +2980,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3006,12 +2990,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3031,12 +3015,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3046,7 +3030,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3064,10 +3048,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119731939</v>
+        <v>119731952</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3076,25 +3060,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3107,10 +3091,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525986</v>
+        <v>525970</v>
       </c>
       <c r="R19" t="n">
-        <v>7178882</v>
+        <v>7178943</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3142,7 +3126,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3152,12 +3136,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på knäckt levande sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3210,10 +3194,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119731928</v>
+        <v>119731933</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3222,25 +3206,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3253,10 +3237,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525916</v>
+        <v>525971</v>
       </c>
       <c r="R20" t="n">
-        <v>7178775</v>
+        <v>7178801</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3288,7 +3272,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3298,12 +3282,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3319,26 +3298,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3356,10 +3315,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119731940</v>
+        <v>119731962</v>
       </c>
       <c r="B21" t="n">
-        <v>79608</v>
+        <v>90846</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3372,21 +3331,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3399,10 +3358,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525970</v>
+        <v>525906</v>
       </c>
       <c r="R21" t="n">
-        <v>7178901</v>
+        <v>7179007</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3434,7 +3393,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3444,12 +3403,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3469,22 +3428,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3502,7 +3461,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119731957</v>
+        <v>119731927</v>
       </c>
       <c r="B22" t="n">
         <v>79608</v>
@@ -3545,10 +3504,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525916</v>
+        <v>525918</v>
       </c>
       <c r="R22" t="n">
-        <v>7178975</v>
+        <v>7178789</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3580,7 +3539,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3590,7 +3549,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3648,7 +3607,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119731954</v>
+        <v>119731940</v>
       </c>
       <c r="B23" t="n">
         <v>79608</v>
@@ -3691,10 +3650,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525946</v>
+        <v>525970</v>
       </c>
       <c r="R23" t="n">
-        <v>7178956</v>
+        <v>7178901</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3726,7 +3685,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3736,7 +3695,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3794,10 +3753,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119731964</v>
+        <v>119731938</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3810,26 +3769,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3837,10 +3801,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525926</v>
+        <v>525979</v>
       </c>
       <c r="R24" t="n">
-        <v>7178980</v>
+        <v>7178844</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3872,7 +3836,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3882,7 +3846,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3891,13 +3860,27 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3915,10 +3898,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119731920</v>
+        <v>119731956</v>
       </c>
       <c r="B25" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3931,21 +3914,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3958,10 +3941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525843</v>
+        <v>525939</v>
       </c>
       <c r="R25" t="n">
-        <v>7178750</v>
+        <v>7178962</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3993,7 +3976,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4003,12 +3986,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4023,27 +4006,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4061,10 +4044,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119731925</v>
+        <v>119731950</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4073,35 +4056,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4109,10 +4087,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525849</v>
+        <v>525969</v>
       </c>
       <c r="R26" t="n">
-        <v>7178772</v>
+        <v>7178936</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4144,7 +4122,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4154,12 +4132,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på liggande död björkstam</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4168,27 +4146,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4206,10 +4190,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119731927</v>
+        <v>119731932</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4222,21 +4206,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4249,10 +4233,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525918</v>
+        <v>525935</v>
       </c>
       <c r="R27" t="n">
-        <v>7178789</v>
+        <v>7178787</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4284,7 +4268,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4294,12 +4278,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4315,26 +4294,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4352,10 +4311,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119731952</v>
+        <v>119731953</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4364,25 +4323,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4395,10 +4354,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525970</v>
+        <v>525946</v>
       </c>
       <c r="R28" t="n">
-        <v>7178943</v>
+        <v>7178938</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4430,7 +4389,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4440,12 +4399,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4461,26 +4415,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4498,7 +4432,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119731944</v>
+        <v>119731957</v>
       </c>
       <c r="B29" t="n">
         <v>79608</v>
@@ -4541,10 +4475,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525985</v>
+        <v>525916</v>
       </c>
       <c r="R29" t="n">
-        <v>7178897</v>
+        <v>7178975</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4576,7 +4510,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4586,7 +4520,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4644,10 +4578,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119731936</v>
+        <v>119731921</v>
       </c>
       <c r="B30" t="n">
-        <v>79636</v>
+        <v>79643</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4660,21 +4594,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4687,10 +4621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525983</v>
+        <v>525859</v>
       </c>
       <c r="R30" t="n">
-        <v>7178824</v>
+        <v>7178751</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4722,7 +4656,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4732,12 +4666,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4752,17 +4686,17 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4772,7 +4706,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4790,10 +4724,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119731933</v>
+        <v>119731936</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4802,25 +4736,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4833,10 +4767,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525971</v>
+        <v>525983</v>
       </c>
       <c r="R31" t="n">
-        <v>7178801</v>
+        <v>7178824</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4868,7 +4802,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4878,7 +4812,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4894,6 +4833,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4911,10 +4870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119731953</v>
+        <v>119731922</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4927,21 +4886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4954,10 +4913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525946</v>
+        <v>525859</v>
       </c>
       <c r="R32" t="n">
-        <v>7178938</v>
+        <v>7178751</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4989,7 +4948,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4999,7 +4958,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5014,7 +4978,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5177,10 +5161,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119731966</v>
+        <v>119731965</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5193,31 +5177,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5225,10 +5204,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525966</v>
+        <v>525945</v>
       </c>
       <c r="R34" t="n">
-        <v>7178973</v>
+        <v>7178975</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -5260,7 +5239,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5270,12 +5249,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5284,6 +5263,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5294,17 +5274,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5322,10 +5307,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119731938</v>
+        <v>119731946</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5338,31 +5323,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5370,10 +5350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525979</v>
+        <v>525974</v>
       </c>
       <c r="R35" t="n">
-        <v>7178844</v>
+        <v>7178925</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5405,7 +5385,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5415,12 +5395,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5429,6 +5409,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5447,9 +5428,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5467,10 +5453,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119731943</v>
+        <v>119731926</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5479,25 +5465,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5510,10 +5496,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525979</v>
+        <v>525888</v>
       </c>
       <c r="R36" t="n">
-        <v>7178902</v>
+        <v>7178777</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5545,7 +5531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5555,12 +5541,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5575,27 +5561,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5613,10 +5579,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119731965</v>
+        <v>119731920</v>
       </c>
       <c r="B37" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5629,21 +5595,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5656,10 +5622,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525945</v>
+        <v>525843</v>
       </c>
       <c r="R37" t="n">
-        <v>7178975</v>
+        <v>7178750</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5691,7 +5657,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5701,12 +5667,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5721,27 +5687,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5759,10 +5725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119731945</v>
+        <v>119731944</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5775,34 +5741,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525961</v>
+        <v>525985</v>
       </c>
       <c r="R38" t="n">
-        <v>7178906</v>
+        <v>7178897</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5834,7 +5803,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5844,7 +5813,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5853,8 +5827,34 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5871,7 +5871,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119731913</v>
+        <v>119731889</v>
       </c>
       <c r="B39" t="n">
         <v>78526</v>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525778</v>
+        <v>525688</v>
       </c>
       <c r="R39" t="n">
-        <v>7178782</v>
+        <v>7179014</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5959,7 +5959,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5992,10 +5997,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119731887</v>
+        <v>119731914</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6008,31 +6013,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525707</v>
+        <v>525792</v>
       </c>
       <c r="R40" t="n">
-        <v>7178998</v>
+        <v>7178785</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6085,12 +6085,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6099,6 +6099,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -6117,9 +6118,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6137,10 +6143,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119731885</v>
+        <v>119731917</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6153,31 +6159,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -6185,10 +6186,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525697</v>
+        <v>525842</v>
       </c>
       <c r="R41" t="n">
-        <v>7179006</v>
+        <v>7178769</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -6220,7 +6221,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6230,12 +6231,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6244,27 +6245,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6282,10 +6289,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119731903</v>
+        <v>119731867</v>
       </c>
       <c r="B42" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6298,21 +6305,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6325,10 +6332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525774</v>
+        <v>525802</v>
       </c>
       <c r="R42" t="n">
-        <v>7178852</v>
+        <v>7178930</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6360,7 +6367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6370,12 +6377,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6405,12 +6412,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6428,10 +6435,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119731857</v>
+        <v>119731884</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6444,31 +6451,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6476,10 +6478,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525853</v>
+        <v>525725</v>
       </c>
       <c r="R43" t="n">
-        <v>7178853</v>
+        <v>7178979</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6511,7 +6513,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6521,12 +6523,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6535,6 +6537,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6545,17 +6548,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6573,10 +6581,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119731900</v>
+        <v>119731888</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6589,34 +6597,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525738</v>
+        <v>525689</v>
       </c>
       <c r="R44" t="n">
-        <v>7178870</v>
+        <v>7179025</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6648,7 +6659,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6658,7 +6669,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6667,8 +6683,34 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6685,10 +6727,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119731856</v>
+        <v>119731912</v>
       </c>
       <c r="B45" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6701,26 +6743,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6728,10 +6775,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525854</v>
+        <v>525763</v>
       </c>
       <c r="R45" t="n">
-        <v>7178867</v>
+        <v>7178776</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6763,7 +6810,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6773,12 +6820,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6787,7 +6834,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6798,22 +6844,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6831,10 +6872,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119731915</v>
+        <v>119731882</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6847,21 +6888,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6874,10 +6915,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525820</v>
+        <v>525731</v>
       </c>
       <c r="R46" t="n">
-        <v>7178762</v>
+        <v>7178963</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6909,7 +6950,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6919,7 +6960,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6934,7 +6980,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6952,10 +7018,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119731899</v>
+        <v>119731842</v>
       </c>
       <c r="B47" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6964,25 +7030,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6995,10 +7061,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525724</v>
+        <v>525950</v>
       </c>
       <c r="R47" t="n">
-        <v>7178884</v>
+        <v>7178893</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -7030,7 +7096,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7040,12 +7106,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>på levande asp</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7065,12 +7131,12 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -7080,7 +7146,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7098,10 +7164,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119731883</v>
+        <v>119731897</v>
       </c>
       <c r="B48" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7110,25 +7176,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -7141,10 +7207,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525725</v>
+        <v>525705</v>
       </c>
       <c r="R48" t="n">
-        <v>7178979</v>
+        <v>7178875</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -7176,7 +7242,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7186,7 +7252,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7244,10 +7310,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119731910</v>
+        <v>119731865</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7260,31 +7326,26 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -7292,10 +7353,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525767</v>
+        <v>525818</v>
       </c>
       <c r="R49" t="n">
-        <v>7178808</v>
+        <v>7178903</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7327,7 +7388,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7337,12 +7398,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7351,6 +7412,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -7361,17 +7423,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7389,10 +7456,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119731858</v>
+        <v>119731866</v>
       </c>
       <c r="B50" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7405,21 +7472,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7432,10 +7499,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525845</v>
+        <v>525806</v>
       </c>
       <c r="R50" t="n">
-        <v>7178853</v>
+        <v>7178927</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7467,7 +7534,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7477,12 +7544,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7498,26 +7560,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7535,10 +7577,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119731902</v>
+        <v>119731907</v>
       </c>
       <c r="B51" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7551,26 +7593,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7578,10 +7625,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525769</v>
+        <v>525765</v>
       </c>
       <c r="R51" t="n">
-        <v>7178869</v>
+        <v>7178799</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7613,7 +7660,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7623,12 +7670,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>på levande liggande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7637,7 +7684,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7648,22 +7694,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7681,10 +7722,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119731870</v>
+        <v>119731905</v>
       </c>
       <c r="B52" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7693,25 +7734,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7724,10 +7765,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525790</v>
+        <v>525762</v>
       </c>
       <c r="R52" t="n">
-        <v>7178955</v>
+        <v>7178853</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7759,7 +7800,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7769,12 +7810,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7794,12 +7835,12 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -7809,7 +7850,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7827,7 +7868,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119731907</v>
+        <v>119731910</v>
       </c>
       <c r="B53" t="n">
         <v>57310</v>
@@ -7875,10 +7916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525765</v>
+        <v>525767</v>
       </c>
       <c r="R53" t="n">
-        <v>7178799</v>
+        <v>7178808</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7910,7 +7951,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7920,7 +7961,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -7972,7 +8013,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119731876</v>
+        <v>119731860</v>
       </c>
       <c r="B54" t="n">
         <v>57310</v>
@@ -8010,7 +8051,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -8020,10 +8061,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525781</v>
+        <v>525848</v>
       </c>
       <c r="R54" t="n">
-        <v>7178998</v>
+        <v>7178857</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -8055,7 +8096,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8065,12 +8106,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8117,10 +8158,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119731890</v>
+        <v>119731858</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8133,21 +8174,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -8160,10 +8201,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525658</v>
+        <v>525845</v>
       </c>
       <c r="R55" t="n">
-        <v>7178997</v>
+        <v>7178853</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -8195,7 +8236,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8205,7 +8246,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8221,6 +8267,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8238,10 +8304,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119731901</v>
+        <v>119731895</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8254,31 +8320,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -8286,10 +8347,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525747</v>
+        <v>525699</v>
       </c>
       <c r="R56" t="n">
-        <v>7178865</v>
+        <v>7178908</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -8321,7 +8382,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8331,12 +8392,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8345,27 +8406,13 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8383,10 +8430,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119731840</v>
+        <v>119731893</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8399,31 +8446,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -8431,10 +8473,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525933</v>
+        <v>525694</v>
       </c>
       <c r="R57" t="n">
-        <v>7178939</v>
+        <v>7178950</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -8466,7 +8508,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8476,12 +8518,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8490,27 +8532,13 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8528,10 +8556,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119731868</v>
+        <v>119731883</v>
       </c>
       <c r="B58" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8540,25 +8568,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8571,10 +8599,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525802</v>
+        <v>525725</v>
       </c>
       <c r="R58" t="n">
-        <v>7178930</v>
+        <v>7178979</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8606,7 +8634,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8616,7 +8644,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8674,10 +8702,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119731895</v>
+        <v>119731851</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8690,26 +8718,31 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8717,10 +8750,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525699</v>
+        <v>525862</v>
       </c>
       <c r="R59" t="n">
-        <v>7178908</v>
+        <v>7178784</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8752,7 +8785,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8762,12 +8795,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8776,13 +8809,27 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8800,10 +8847,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119731888</v>
+        <v>119731857</v>
       </c>
       <c r="B60" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8816,26 +8863,31 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8843,10 +8895,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525689</v>
+        <v>525853</v>
       </c>
       <c r="R60" t="n">
-        <v>7179025</v>
+        <v>7178853</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8878,7 +8930,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8888,12 +8940,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8902,7 +8954,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8913,22 +8964,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8946,10 +8992,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119731898</v>
+        <v>119731840</v>
       </c>
       <c r="B61" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8962,26 +9008,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8989,10 +9040,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525707</v>
+        <v>525933</v>
       </c>
       <c r="R61" t="n">
-        <v>7178873</v>
+        <v>7178939</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -9024,7 +9075,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9034,12 +9085,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9048,7 +9099,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -9067,14 +9117,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -9092,10 +9137,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119731867</v>
+        <v>119731841</v>
       </c>
       <c r="B62" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9108,26 +9153,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -9135,10 +9185,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525802</v>
+        <v>525940</v>
       </c>
       <c r="R62" t="n">
-        <v>7178930</v>
+        <v>7178908</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -9170,7 +9220,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9180,12 +9230,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9194,7 +9244,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -9205,22 +9254,17 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9238,10 +9282,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731854</v>
+        <v>119731876</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9254,26 +9298,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -9281,10 +9330,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525857</v>
+        <v>525781</v>
       </c>
       <c r="R63" t="n">
-        <v>7178804</v>
+        <v>7178998</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9316,7 +9365,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9326,12 +9375,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9340,13 +9389,27 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9364,10 +9427,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731905</v>
+        <v>119731880</v>
       </c>
       <c r="B64" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9380,26 +9443,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -9407,10 +9475,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525762</v>
+        <v>525751</v>
       </c>
       <c r="R64" t="n">
-        <v>7178853</v>
+        <v>7178999</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9442,7 +9510,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9452,12 +9520,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9466,7 +9534,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -9485,14 +9552,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9510,7 +9572,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119731897</v>
+        <v>119731903</v>
       </c>
       <c r="B65" t="n">
         <v>79608</v>
@@ -9553,10 +9615,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525705</v>
+        <v>525774</v>
       </c>
       <c r="R65" t="n">
-        <v>7178875</v>
+        <v>7178852</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9588,7 +9650,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9598,12 +9660,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9633,12 +9695,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9656,7 +9718,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731889</v>
+        <v>119731918</v>
       </c>
       <c r="B66" t="n">
         <v>78526</v>
@@ -9699,10 +9761,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525688</v>
+        <v>525837</v>
       </c>
       <c r="R66" t="n">
-        <v>7179014</v>
+        <v>7178762</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9734,7 +9796,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9744,12 +9806,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9764,7 +9821,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9782,10 +9839,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731860</v>
+        <v>119731913</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9798,31 +9855,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9830,10 +9882,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525848</v>
+        <v>525778</v>
       </c>
       <c r="R67" t="n">
-        <v>7178857</v>
+        <v>7178782</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9865,7 +9917,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9875,12 +9927,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9889,27 +9936,13 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -10073,7 +10106,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119731855</v>
+        <v>119731874</v>
       </c>
       <c r="B69" t="n">
         <v>79608</v>
@@ -10116,10 +10149,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525852</v>
+        <v>525790</v>
       </c>
       <c r="R69" t="n">
-        <v>7178820</v>
+        <v>7178955</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -10151,7 +10184,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10161,12 +10194,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10196,12 +10229,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -10219,10 +10252,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119731861</v>
+        <v>119731887</v>
       </c>
       <c r="B70" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -10235,26 +10268,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -10262,10 +10300,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525826</v>
+        <v>525707</v>
       </c>
       <c r="R70" t="n">
-        <v>7178869</v>
+        <v>7178998</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10297,7 +10335,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10307,12 +10345,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10321,7 +10359,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -10332,22 +10369,17 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -10511,10 +10543,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119731916</v>
+        <v>119731896</v>
       </c>
       <c r="B72" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10523,30 +10555,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -10554,10 +10591,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>525842</v>
+        <v>525699</v>
       </c>
       <c r="R72" t="n">
-        <v>7178769</v>
+        <v>7178908</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -10589,7 +10626,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10599,12 +10636,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10613,33 +10650,27 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10657,10 +10688,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119731843</v>
+        <v>119731855</v>
       </c>
       <c r="B73" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10673,31 +10704,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -10705,10 +10731,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525949</v>
+        <v>525852</v>
       </c>
       <c r="R73" t="n">
-        <v>7178888</v>
+        <v>7178820</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -10740,7 +10766,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10750,12 +10776,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10764,6 +10790,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -10774,17 +10801,22 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10802,10 +10834,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119731850</v>
+        <v>119731904</v>
       </c>
       <c r="B74" t="n">
-        <v>90558</v>
+        <v>79643</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10814,25 +10846,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10845,10 +10877,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>525907</v>
+        <v>525762</v>
       </c>
       <c r="R74" t="n">
-        <v>7178822</v>
+        <v>7178853</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -10880,7 +10912,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10890,12 +10922,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>på 2 stående döda granar</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10910,27 +10942,27 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10948,10 +10980,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119731841</v>
+        <v>119731902</v>
       </c>
       <c r="B75" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10964,31 +10996,26 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10996,10 +11023,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>525940</v>
+        <v>525769</v>
       </c>
       <c r="R75" t="n">
-        <v>7178908</v>
+        <v>7178869</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -11031,7 +11058,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11041,12 +11068,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande liggande sälg</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -11055,6 +11082,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -11065,17 +11093,22 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -11093,7 +11126,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119731863</v>
+        <v>119731856</v>
       </c>
       <c r="B76" t="n">
         <v>79608</v>
@@ -11136,10 +11169,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>525807</v>
+        <v>525854</v>
       </c>
       <c r="R76" t="n">
-        <v>7178896</v>
+        <v>7178867</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -11171,7 +11204,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11181,7 +11214,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -11239,10 +11272,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119731874</v>
+        <v>119731916</v>
       </c>
       <c r="B77" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -11251,25 +11284,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -11282,10 +11315,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525790</v>
+        <v>525842</v>
       </c>
       <c r="R77" t="n">
-        <v>7178955</v>
+        <v>7178769</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -11317,7 +11350,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11327,7 +11360,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -11347,7 +11380,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -11385,10 +11418,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119731842</v>
+        <v>119731875</v>
       </c>
       <c r="B78" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11401,26 +11434,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -11428,10 +11466,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525950</v>
+        <v>525792</v>
       </c>
       <c r="R78" t="n">
-        <v>7178893</v>
+        <v>7178967</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -11463,7 +11501,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11473,12 +11511,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11487,7 +11525,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -11498,22 +11535,17 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11531,10 +11563,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119731884</v>
+        <v>119731870</v>
       </c>
       <c r="B79" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11543,25 +11575,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11574,10 +11606,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525725</v>
+        <v>525790</v>
       </c>
       <c r="R79" t="n">
-        <v>7178979</v>
+        <v>7178955</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -11609,7 +11641,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11619,7 +11651,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -11677,10 +11709,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731881</v>
+        <v>119731900</v>
       </c>
       <c r="B80" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11693,27 +11725,24 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
@@ -11723,7 +11752,7 @@
         <v>525738</v>
       </c>
       <c r="R80" t="n">
-        <v>7178966</v>
+        <v>7178870</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11755,7 +11784,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11765,12 +11794,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11779,34 +11803,8 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -11823,10 +11821,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731904</v>
+        <v>119731854</v>
       </c>
       <c r="B81" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11835,25 +11833,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11866,10 +11864,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525762</v>
+        <v>525857</v>
       </c>
       <c r="R81" t="n">
-        <v>7178853</v>
+        <v>7178804</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11901,7 +11899,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11911,12 +11909,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11932,26 +11930,6 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11969,10 +11947,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731865</v>
+        <v>119731853</v>
       </c>
       <c r="B82" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11985,26 +11963,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -12012,10 +11995,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525818</v>
+        <v>525853</v>
       </c>
       <c r="R82" t="n">
-        <v>7178903</v>
+        <v>7178800</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12047,7 +12030,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12057,12 +12040,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -12071,7 +12054,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -12082,22 +12064,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -12115,10 +12092,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119731896</v>
+        <v>119731898</v>
       </c>
       <c r="B83" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12131,31 +12108,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -12163,10 +12135,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525699</v>
+        <v>525707</v>
       </c>
       <c r="R83" t="n">
-        <v>7178908</v>
+        <v>7178873</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -12198,7 +12170,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12208,12 +12180,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -12222,6 +12194,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -12240,9 +12213,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12260,10 +12238,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119731912</v>
+        <v>119731839</v>
       </c>
       <c r="B84" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12276,31 +12254,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -12308,10 +12281,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525763</v>
+        <v>525933</v>
       </c>
       <c r="R84" t="n">
-        <v>7178776</v>
+        <v>7178937</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -12343,7 +12316,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12353,12 +12326,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12367,6 +12340,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -12377,17 +12351,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -12405,10 +12384,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119731914</v>
+        <v>119731899</v>
       </c>
       <c r="B85" t="n">
-        <v>90558</v>
+        <v>79643</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12417,25 +12396,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -12448,10 +12427,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525792</v>
+        <v>525724</v>
       </c>
       <c r="R85" t="n">
-        <v>7178785</v>
+        <v>7178884</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -12483,7 +12462,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12493,12 +12472,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>på gammal stubbe</t>
+          <t>på levande asp</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12518,22 +12497,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12551,7 +12530,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731917</v>
+        <v>119731881</v>
       </c>
       <c r="B86" t="n">
         <v>79608</v>
@@ -12594,10 +12573,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525842</v>
+        <v>525738</v>
       </c>
       <c r="R86" t="n">
-        <v>7178769</v>
+        <v>7178966</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12629,7 +12608,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12639,7 +12618,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -12659,7 +12638,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -12697,7 +12676,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119731891</v>
+        <v>119731868</v>
       </c>
       <c r="B87" t="n">
         <v>79608</v>
@@ -12740,10 +12719,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525653</v>
+        <v>525802</v>
       </c>
       <c r="R87" t="n">
-        <v>7178999</v>
+        <v>7178930</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -12775,7 +12754,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12785,12 +12764,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>på död högstubbe av sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12820,12 +12799,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12843,7 +12822,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119731880</v>
+        <v>119731901</v>
       </c>
       <c r="B88" t="n">
         <v>57310</v>
@@ -12891,10 +12870,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525751</v>
+        <v>525747</v>
       </c>
       <c r="R88" t="n">
-        <v>7178999</v>
+        <v>7178865</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -12926,7 +12905,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12936,7 +12915,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -12988,10 +12967,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119731839</v>
+        <v>119731850</v>
       </c>
       <c r="B89" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -13004,21 +12983,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -13031,10 +13010,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525933</v>
+        <v>525907</v>
       </c>
       <c r="R89" t="n">
-        <v>7178937</v>
+        <v>7178822</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -13066,7 +13045,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13076,12 +13055,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på 2 stående döda granar</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -13096,27 +13075,27 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -13134,10 +13113,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119731866</v>
+        <v>119731906</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -13150,21 +13129,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -13177,10 +13156,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525806</v>
+        <v>525765</v>
       </c>
       <c r="R90" t="n">
-        <v>7178927</v>
+        <v>7178799</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -13212,7 +13191,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13222,7 +13201,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -13238,6 +13222,26 @@
       <c r="AH90" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -13255,10 +13259,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119731875</v>
+        <v>119731890</v>
       </c>
       <c r="B91" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13271,31 +13275,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -13303,10 +13302,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525792</v>
+        <v>525658</v>
       </c>
       <c r="R91" t="n">
-        <v>7178967</v>
+        <v>7178997</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -13338,7 +13337,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13348,12 +13347,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -13362,27 +13356,13 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13400,7 +13380,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119731851</v>
+        <v>119731885</v>
       </c>
       <c r="B92" t="n">
         <v>57310</v>
@@ -13448,10 +13428,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525862</v>
+        <v>525697</v>
       </c>
       <c r="R92" t="n">
-        <v>7178784</v>
+        <v>7179006</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -13483,7 +13463,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13493,7 +13473,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -13545,10 +13525,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119731853</v>
+        <v>119731863</v>
       </c>
       <c r="B93" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13561,31 +13541,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -13593,10 +13568,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>525853</v>
+        <v>525807</v>
       </c>
       <c r="R93" t="n">
-        <v>7178800</v>
+        <v>7178896</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -13628,7 +13603,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13638,12 +13613,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13652,6 +13627,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -13662,17 +13638,22 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -13690,10 +13671,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119731906</v>
+        <v>119731891</v>
       </c>
       <c r="B94" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13706,21 +13687,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -13733,10 +13714,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>525765</v>
+        <v>525653</v>
       </c>
       <c r="R94" t="n">
-        <v>7178799</v>
+        <v>7178999</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -13768,7 +13749,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13778,12 +13759,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på död högstubbe av sälg</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13803,22 +13784,22 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -13836,10 +13817,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119731918</v>
+        <v>119731861</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13852,21 +13833,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -13879,10 +13860,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>525837</v>
+        <v>525826</v>
       </c>
       <c r="R95" t="n">
-        <v>7178762</v>
+        <v>7178869</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -13914,7 +13895,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13924,7 +13905,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13939,7 +13925,27 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13957,10 +13963,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119731893</v>
+        <v>119731843</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13973,26 +13979,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -14000,10 +14011,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>525694</v>
+        <v>525949</v>
       </c>
       <c r="R96" t="n">
-        <v>7178950</v>
+        <v>7178888</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -14035,7 +14046,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14045,12 +14056,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -14059,13 +14070,27 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -14083,10 +14108,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119731882</v>
+        <v>119731915</v>
       </c>
       <c r="B97" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -14099,21 +14124,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -14126,10 +14151,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>525731</v>
+        <v>525820</v>
       </c>
       <c r="R97" t="n">
-        <v>7178963</v>
+        <v>7178762</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -14161,7 +14186,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14171,12 +14196,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>på död stående gran</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -14191,27 +14211,7 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -14229,10 +14229,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119894773</v>
+        <v>119894748</v>
       </c>
       <c r="B98" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>på gran stubbe</t>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -14375,10 +14375,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119894748</v>
+        <v>119894773</v>
       </c>
       <c r="B99" t="n">
-        <v>90562</v>
+        <v>90558</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -14391,21 +14391,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>på granlåga med bark</t>
+          <t>på gran stubbe</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -14498,12 +14498,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -2062,7 +2062,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119731924</v>
+        <v>119731925</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525862</v>
+        <v>525849</v>
       </c>
       <c r="R12" t="n">
-        <v>7178759</v>
+        <v>7178772</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2207,7 +2207,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119731925</v>
+        <v>119731924</v>
       </c>
       <c r="B13" t="n">
         <v>57310</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525849</v>
+        <v>525862</v>
       </c>
       <c r="R13" t="n">
-        <v>7178772</v>
+        <v>7178759</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -5453,10 +5453,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119731926</v>
+        <v>119731944</v>
       </c>
       <c r="B36" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5469,21 +5469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5496,10 +5496,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525888</v>
+        <v>525985</v>
       </c>
       <c r="R36" t="n">
-        <v>7178777</v>
+        <v>7178897</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5561,7 +5561,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5725,10 +5745,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119731944</v>
+        <v>119731926</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5741,21 +5761,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5768,10 +5788,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525985</v>
+        <v>525888</v>
       </c>
       <c r="R38" t="n">
-        <v>7178897</v>
+        <v>7178777</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5803,7 +5823,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5813,12 +5833,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5833,27 +5853,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -6289,10 +6289,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119731867</v>
+        <v>119731884</v>
       </c>
       <c r="B42" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6305,21 +6305,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525802</v>
+        <v>525725</v>
       </c>
       <c r="R42" t="n">
-        <v>7178930</v>
+        <v>7178979</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6435,7 +6435,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119731884</v>
+        <v>119731888</v>
       </c>
       <c r="B43" t="n">
         <v>79608</v>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525725</v>
+        <v>525689</v>
       </c>
       <c r="R43" t="n">
-        <v>7178979</v>
+        <v>7179025</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6581,10 +6581,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119731888</v>
+        <v>119731867</v>
       </c>
       <c r="B44" t="n">
-        <v>79608</v>
+        <v>79607</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6597,21 +6597,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525689</v>
+        <v>525802</v>
       </c>
       <c r="R44" t="n">
-        <v>7179025</v>
+        <v>7178930</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -8556,10 +8556,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119731883</v>
+        <v>119731857</v>
       </c>
       <c r="B58" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8568,30 +8568,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8599,10 +8604,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525725</v>
+        <v>525853</v>
       </c>
       <c r="R58" t="n">
-        <v>7178979</v>
+        <v>7178853</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8634,7 +8639,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8644,12 +8649,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8658,7 +8663,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8669,22 +8673,17 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8702,7 +8701,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119731851</v>
+        <v>119731840</v>
       </c>
       <c r="B59" t="n">
         <v>57310</v>
@@ -8750,10 +8749,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525862</v>
+        <v>525933</v>
       </c>
       <c r="R59" t="n">
-        <v>7178784</v>
+        <v>7178939</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8785,7 +8784,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8795,7 +8794,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8847,10 +8846,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119731857</v>
+        <v>119731883</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8859,35 +8858,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -8895,10 +8889,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525853</v>
+        <v>525725</v>
       </c>
       <c r="R60" t="n">
-        <v>7178853</v>
+        <v>7178979</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8930,7 +8924,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8940,12 +8934,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8954,6 +8948,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -8964,17 +8959,22 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119731840</v>
+        <v>119731851</v>
       </c>
       <c r="B61" t="n">
         <v>57310</v>
@@ -9040,10 +9040,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525933</v>
+        <v>525862</v>
       </c>
       <c r="R61" t="n">
-        <v>7178939</v>
+        <v>7178784</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -9718,10 +9718,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731918</v>
+        <v>119731848</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9734,21 +9734,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9761,10 +9761,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525837</v>
+        <v>525936</v>
       </c>
       <c r="R66" t="n">
-        <v>7178762</v>
+        <v>7178808</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9806,7 +9806,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9821,7 +9826,27 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9839,10 +9864,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731913</v>
+        <v>119731874</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9855,21 +9880,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9882,10 +9907,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525778</v>
+        <v>525790</v>
       </c>
       <c r="R67" t="n">
-        <v>7178782</v>
+        <v>7178955</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9917,7 +9942,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9927,7 +9952,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9943,6 +9973,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9960,10 +10010,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119731848</v>
+        <v>119731918</v>
       </c>
       <c r="B68" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9976,21 +10026,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -10003,10 +10053,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525936</v>
+        <v>525837</v>
       </c>
       <c r="R68" t="n">
-        <v>7178808</v>
+        <v>7178762</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -10038,7 +10088,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10048,12 +10098,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -10068,27 +10113,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -10106,10 +10131,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119731874</v>
+        <v>119731913</v>
       </c>
       <c r="B69" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10122,21 +10147,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -10149,10 +10174,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525790</v>
+        <v>525778</v>
       </c>
       <c r="R69" t="n">
-        <v>7178955</v>
+        <v>7178782</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -10184,7 +10209,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10194,12 +10219,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10215,26 +10235,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -11418,10 +11418,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119731875</v>
+        <v>119731900</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11434,42 +11434,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525792</v>
+        <v>525738</v>
       </c>
       <c r="R78" t="n">
-        <v>7178967</v>
+        <v>7178870</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -11501,7 +11493,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11511,12 +11503,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11527,26 +11514,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -11709,10 +11676,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731900</v>
+        <v>119731875</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11725,34 +11692,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525738</v>
+        <v>525792</v>
       </c>
       <c r="R80" t="n">
-        <v>7178870</v>
+        <v>7178967</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11784,7 +11759,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11794,7 +11769,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11805,6 +11785,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -13963,10 +13963,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119731843</v>
+        <v>119731915</v>
       </c>
       <c r="B96" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13979,31 +13979,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -14011,10 +14006,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>525949</v>
+        <v>525820</v>
       </c>
       <c r="R96" t="n">
-        <v>7178888</v>
+        <v>7178762</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -14046,7 +14041,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14056,12 +14051,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -14070,27 +14060,13 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -14108,10 +14084,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119731915</v>
+        <v>119731843</v>
       </c>
       <c r="B97" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -14124,26 +14100,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -14151,10 +14132,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>525820</v>
+        <v>525949</v>
       </c>
       <c r="R97" t="n">
-        <v>7178762</v>
+        <v>7178888</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -14186,7 +14167,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14196,7 +14177,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -14205,13 +14191,27 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119731930</v>
+        <v>119731966</v>
       </c>
       <c r="B5" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,26 +1108,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1135,10 +1140,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525916</v>
+        <v>525966</v>
       </c>
       <c r="R5" t="n">
-        <v>7178775</v>
+        <v>7178973</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1170,7 +1175,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,12 +1185,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1199,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1205,22 +1209,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1359,10 +1358,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119731966</v>
+        <v>119731933</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1375,31 +1374,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1407,10 +1401,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525966</v>
+        <v>525971</v>
       </c>
       <c r="R7" t="n">
-        <v>7178973</v>
+        <v>7178801</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1442,7 +1436,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1452,12 +1446,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1466,27 +1455,13 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1504,10 +1479,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119731919</v>
+        <v>119731932</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1520,31 +1495,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1552,10 +1522,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525842</v>
+        <v>525935</v>
       </c>
       <c r="R8" t="n">
-        <v>7178749</v>
+        <v>7178787</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1587,7 +1557,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1597,12 +1567,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1611,27 +1576,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1649,7 +1600,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119731935</v>
+        <v>119731944</v>
       </c>
       <c r="B9" t="n">
         <v>79608</v>
@@ -1692,10 +1643,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525983</v>
+        <v>525985</v>
       </c>
       <c r="R9" t="n">
-        <v>7178824</v>
+        <v>7178897</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1727,7 +1678,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1737,12 +1688,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1762,12 +1713,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1777,7 +1728,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1795,10 +1746,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731939</v>
+        <v>119731921</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1807,25 +1758,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1838,10 +1789,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525986</v>
+        <v>525859</v>
       </c>
       <c r="R10" t="n">
-        <v>7178882</v>
+        <v>7178751</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1873,7 +1824,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1883,12 +1834,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på knäckt levande sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1903,7 +1854,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1941,10 +1892,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119731964</v>
+        <v>119731952</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1953,25 +1904,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1984,10 +1935,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525926</v>
+        <v>525970</v>
       </c>
       <c r="R11" t="n">
-        <v>7178980</v>
+        <v>7178943</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2019,7 +1970,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2029,7 +1980,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2045,6 +2001,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2062,7 +2038,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119731925</v>
+        <v>119731948</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -2100,7 +2076,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2110,10 +2086,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525849</v>
+        <v>525970</v>
       </c>
       <c r="R12" t="n">
-        <v>7178772</v>
+        <v>7178928</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2145,7 +2121,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2155,12 +2131,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2174,7 +2150,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2207,10 +2183,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119731924</v>
+        <v>119731939</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2223,31 +2199,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2255,10 +2226,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525862</v>
+        <v>525986</v>
       </c>
       <c r="R13" t="n">
-        <v>7178759</v>
+        <v>7178882</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2290,7 +2261,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2300,12 +2271,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på knäckt levande sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2314,27 +2285,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2352,10 +2329,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119731945</v>
+        <v>119731928</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2364,38 +2341,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525961</v>
+        <v>525916</v>
       </c>
       <c r="R14" t="n">
-        <v>7178906</v>
+        <v>7178775</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2427,7 +2407,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2437,7 +2417,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2446,8 +2431,34 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2464,10 +2475,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119731928</v>
+        <v>119731924</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2476,30 +2487,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2507,10 +2523,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525916</v>
+        <v>525862</v>
       </c>
       <c r="R15" t="n">
-        <v>7178775</v>
+        <v>7178759</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2542,7 +2558,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2552,12 +2568,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2566,33 +2582,27 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2610,10 +2620,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119731954</v>
+        <v>119731920</v>
       </c>
       <c r="B16" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2626,21 +2636,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2653,10 +2663,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525946</v>
+        <v>525843</v>
       </c>
       <c r="R16" t="n">
-        <v>7178956</v>
+        <v>7178750</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2688,7 +2698,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2698,12 +2708,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2718,27 +2728,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2756,10 +2766,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119731943</v>
+        <v>119731950</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>79643</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2772,21 +2782,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2799,10 +2809,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525979</v>
+        <v>525969</v>
       </c>
       <c r="R17" t="n">
-        <v>7178902</v>
+        <v>7178936</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2834,7 +2844,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2844,12 +2854,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på liggande död björkstam</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2869,22 +2879,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2902,10 +2912,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119731942</v>
+        <v>119731965</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2914,25 +2924,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2945,10 +2955,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525970</v>
+        <v>525945</v>
       </c>
       <c r="R18" t="n">
-        <v>7178901</v>
+        <v>7178975</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2980,7 +2990,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2990,7 +3000,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3048,10 +3058,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119731952</v>
+        <v>119731940</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3060,25 +3070,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3094,7 +3104,7 @@
         <v>525970</v>
       </c>
       <c r="R19" t="n">
-        <v>7178943</v>
+        <v>7178901</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3126,7 +3136,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3136,7 +3146,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3194,10 +3204,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119731933</v>
+        <v>119731936</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3206,25 +3216,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3237,10 +3247,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525971</v>
+        <v>525983</v>
       </c>
       <c r="R20" t="n">
-        <v>7178801</v>
+        <v>7178824</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3272,7 +3282,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3282,7 +3292,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3298,6 +3313,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3315,10 +3350,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119731962</v>
+        <v>119731919</v>
       </c>
       <c r="B21" t="n">
-        <v>90846</v>
+        <v>57310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3331,26 +3366,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3358,10 +3398,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525906</v>
+        <v>525842</v>
       </c>
       <c r="R21" t="n">
-        <v>7179007</v>
+        <v>7178749</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3393,7 +3433,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3403,12 +3443,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3417,13 +3457,12 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3436,14 +3475,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3461,10 +3495,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119731927</v>
+        <v>119731945</v>
       </c>
       <c r="B22" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3477,37 +3511,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525918</v>
+        <v>525961</v>
       </c>
       <c r="R22" t="n">
-        <v>7178789</v>
+        <v>7178906</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3539,7 +3570,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3549,12 +3580,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3563,34 +3589,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3607,7 +3607,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119731940</v>
+        <v>119731935</v>
       </c>
       <c r="B23" t="n">
         <v>79608</v>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525970</v>
+        <v>525983</v>
       </c>
       <c r="R23" t="n">
-        <v>7178901</v>
+        <v>7178824</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119731938</v>
+        <v>119731956</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3769,31 +3769,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3801,10 +3796,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525979</v>
+        <v>525939</v>
       </c>
       <c r="R24" t="n">
-        <v>7178844</v>
+        <v>7178962</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3836,7 +3831,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3846,12 +3841,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3860,6 +3855,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3870,17 +3866,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3898,10 +3899,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119731956</v>
+        <v>119731953</v>
       </c>
       <c r="B25" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3914,21 +3915,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3941,10 +3942,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525939</v>
+        <v>525946</v>
       </c>
       <c r="R25" t="n">
-        <v>7178962</v>
+        <v>7178938</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3976,7 +3977,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3986,12 +3987,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4007,26 +4003,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4044,10 +4020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119731950</v>
+        <v>119731943</v>
       </c>
       <c r="B26" t="n">
-        <v>79643</v>
+        <v>79636</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4060,21 +4036,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -4087,10 +4063,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525969</v>
+        <v>525979</v>
       </c>
       <c r="R26" t="n">
-        <v>7178936</v>
+        <v>7178902</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4122,7 +4098,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4132,12 +4108,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på liggande död björkstam</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4157,22 +4133,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4190,10 +4166,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119731932</v>
+        <v>119731954</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4206,21 +4182,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -4233,10 +4209,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525935</v>
+        <v>525946</v>
       </c>
       <c r="R27" t="n">
-        <v>7178787</v>
+        <v>7178956</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4268,7 +4244,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4278,7 +4254,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4294,6 +4275,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4311,10 +4312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119731953</v>
+        <v>119731922</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4327,21 +4328,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4354,10 +4355,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525946</v>
+        <v>525859</v>
       </c>
       <c r="R28" t="n">
-        <v>7178938</v>
+        <v>7178751</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4389,7 +4390,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4399,7 +4400,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4414,7 +4420,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4432,10 +4458,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119731957</v>
+        <v>119731964</v>
       </c>
       <c r="B29" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4448,21 +4474,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4475,10 +4501,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525916</v>
+        <v>525926</v>
       </c>
       <c r="R29" t="n">
-        <v>7178975</v>
+        <v>7178980</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4510,7 +4536,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4520,12 +4546,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4541,26 +4562,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4578,10 +4579,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119731921</v>
+        <v>119731962</v>
       </c>
       <c r="B30" t="n">
-        <v>79643</v>
+        <v>90846</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4590,25 +4591,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4621,10 +4622,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525859</v>
+        <v>525906</v>
       </c>
       <c r="R30" t="n">
-        <v>7178751</v>
+        <v>7179007</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4656,7 +4657,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4666,12 +4667,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4686,27 +4687,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4724,10 +4725,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119731936</v>
+        <v>119731938</v>
       </c>
       <c r="B31" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4736,30 +4737,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4767,10 +4773,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525983</v>
+        <v>525979</v>
       </c>
       <c r="R31" t="n">
-        <v>7178824</v>
+        <v>7178844</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4802,7 +4808,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4812,12 +4818,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4826,7 +4832,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4837,22 +4842,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119731922</v>
+        <v>119731927</v>
       </c>
       <c r="B32" t="n">
         <v>79608</v>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525859</v>
+        <v>525918</v>
       </c>
       <c r="R32" t="n">
-        <v>7178751</v>
+        <v>7178789</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -5016,10 +5016,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119731948</v>
+        <v>119731926</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5032,31 +5032,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -5064,10 +5059,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525970</v>
+        <v>525888</v>
       </c>
       <c r="R33" t="n">
-        <v>7178928</v>
+        <v>7178777</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -5099,7 +5094,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5109,12 +5104,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5123,27 +5118,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5161,10 +5142,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119731965</v>
+        <v>119731942</v>
       </c>
       <c r="B34" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5173,25 +5154,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -5204,10 +5185,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525945</v>
+        <v>525970</v>
       </c>
       <c r="R34" t="n">
-        <v>7178975</v>
+        <v>7178901</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -5239,7 +5220,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5249,7 +5230,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5453,7 +5434,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119731944</v>
+        <v>119731930</v>
       </c>
       <c r="B36" t="n">
         <v>79608</v>
@@ -5496,10 +5477,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525985</v>
+        <v>525916</v>
       </c>
       <c r="R36" t="n">
-        <v>7178897</v>
+        <v>7178775</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5531,7 +5512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5541,7 +5522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5599,10 +5580,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119731920</v>
+        <v>119731957</v>
       </c>
       <c r="B37" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5615,21 +5596,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5642,10 +5623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525843</v>
+        <v>525916</v>
       </c>
       <c r="R37" t="n">
-        <v>7178750</v>
+        <v>7178975</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5677,7 +5658,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5687,12 +5668,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5707,27 +5688,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5745,10 +5726,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119731926</v>
+        <v>119731925</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5761,26 +5742,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5788,10 +5774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525888</v>
+        <v>525849</v>
       </c>
       <c r="R38" t="n">
-        <v>7178777</v>
+        <v>7178772</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5823,7 +5809,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5833,12 +5819,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5847,13 +5833,27 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119731889</v>
+        <v>119731856</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5887,21 +5887,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525688</v>
+        <v>525854</v>
       </c>
       <c r="R39" t="n">
-        <v>7179014</v>
+        <v>7178867</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5980,6 +5980,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5997,10 +6017,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119731914</v>
+        <v>119731900</v>
       </c>
       <c r="B40" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6013,37 +6033,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525792</v>
+        <v>525738</v>
       </c>
       <c r="R40" t="n">
-        <v>7178785</v>
+        <v>7178870</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -6075,7 +6092,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6085,12 +6102,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>på gammal stubbe</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6099,34 +6111,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -6143,10 +6129,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119731917</v>
+        <v>119731916</v>
       </c>
       <c r="B41" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6155,25 +6141,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -6289,10 +6275,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119731884</v>
+        <v>119731915</v>
       </c>
       <c r="B42" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6305,21 +6291,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6332,10 +6318,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525725</v>
+        <v>525820</v>
       </c>
       <c r="R42" t="n">
-        <v>7178979</v>
+        <v>7178762</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6367,7 +6353,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6377,12 +6363,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6397,27 +6378,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6435,7 +6396,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119731888</v>
+        <v>119731868</v>
       </c>
       <c r="B43" t="n">
         <v>79608</v>
@@ -6478,10 +6439,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525689</v>
+        <v>525802</v>
       </c>
       <c r="R43" t="n">
-        <v>7179025</v>
+        <v>7178930</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6513,7 +6474,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6523,7 +6484,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6581,10 +6542,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119731867</v>
+        <v>119731870</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6593,25 +6554,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6624,10 +6585,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525802</v>
+        <v>525790</v>
       </c>
       <c r="R44" t="n">
-        <v>7178930</v>
+        <v>7178955</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6659,7 +6620,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6669,7 +6630,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6727,10 +6688,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119731912</v>
+        <v>119731899</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6739,35 +6700,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6775,10 +6731,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525763</v>
+        <v>525724</v>
       </c>
       <c r="R45" t="n">
-        <v>7178776</v>
+        <v>7178884</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6810,7 +6766,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6820,12 +6776,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande asp</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6834,6 +6790,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6844,17 +6801,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6872,10 +6834,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119731882</v>
+        <v>119731893</v>
       </c>
       <c r="B46" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6888,21 +6850,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6915,10 +6877,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525731</v>
+        <v>525694</v>
       </c>
       <c r="R46" t="n">
-        <v>7178963</v>
+        <v>7178950</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6950,7 +6912,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6960,12 +6922,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6981,26 +6943,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7018,10 +6960,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119731842</v>
+        <v>119731910</v>
       </c>
       <c r="B47" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7034,26 +6976,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -7061,10 +7008,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525950</v>
+        <v>525767</v>
       </c>
       <c r="R47" t="n">
-        <v>7178893</v>
+        <v>7178808</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -7096,7 +7043,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7106,12 +7053,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7120,7 +7067,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -7131,22 +7077,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7164,7 +7105,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119731897</v>
+        <v>119731863</v>
       </c>
       <c r="B48" t="n">
         <v>79608</v>
@@ -7207,10 +7148,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525705</v>
+        <v>525807</v>
       </c>
       <c r="R48" t="n">
-        <v>7178875</v>
+        <v>7178896</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -7242,7 +7183,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7252,7 +7193,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7310,7 +7251,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119731865</v>
+        <v>119731842</v>
       </c>
       <c r="B49" t="n">
         <v>79608</v>
@@ -7353,10 +7294,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525818</v>
+        <v>525950</v>
       </c>
       <c r="R49" t="n">
-        <v>7178903</v>
+        <v>7178893</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7388,7 +7329,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7398,7 +7339,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7456,10 +7397,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119731866</v>
+        <v>119731841</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7472,26 +7413,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7499,10 +7445,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525806</v>
+        <v>525940</v>
       </c>
       <c r="R50" t="n">
-        <v>7178927</v>
+        <v>7178908</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7534,7 +7480,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7544,7 +7490,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7553,13 +7504,27 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7577,7 +7542,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119731907</v>
+        <v>119731876</v>
       </c>
       <c r="B51" t="n">
         <v>57310</v>
@@ -7625,10 +7590,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525765</v>
+        <v>525781</v>
       </c>
       <c r="R51" t="n">
-        <v>7178799</v>
+        <v>7178998</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7660,7 +7625,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7670,7 +7635,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7722,7 +7687,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119731905</v>
+        <v>119731874</v>
       </c>
       <c r="B52" t="n">
         <v>79608</v>
@@ -7765,10 +7730,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525762</v>
+        <v>525790</v>
       </c>
       <c r="R52" t="n">
-        <v>7178853</v>
+        <v>7178955</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7800,7 +7765,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7810,12 +7775,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7835,12 +7800,12 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -7850,7 +7815,7 @@
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7868,10 +7833,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119731910</v>
+        <v>119731902</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7884,31 +7849,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7916,10 +7876,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525767</v>
+        <v>525769</v>
       </c>
       <c r="R53" t="n">
-        <v>7178808</v>
+        <v>7178869</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7951,7 +7911,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7961,12 +7921,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande liggande sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7975,6 +7935,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7985,17 +7946,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8013,7 +7979,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119731860</v>
+        <v>119731880</v>
       </c>
       <c r="B54" t="n">
         <v>57310</v>
@@ -8051,7 +8017,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -8061,10 +8027,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525848</v>
+        <v>525751</v>
       </c>
       <c r="R54" t="n">
-        <v>7178857</v>
+        <v>7178999</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -8096,7 +8062,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8106,12 +8072,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8158,10 +8124,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119731858</v>
+        <v>119731918</v>
       </c>
       <c r="B55" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8174,21 +8140,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -8201,10 +8167,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525845</v>
+        <v>525837</v>
       </c>
       <c r="R55" t="n">
-        <v>7178853</v>
+        <v>7178762</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -8236,7 +8202,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8246,12 +8212,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:27</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8266,27 +8227,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8304,10 +8245,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119731895</v>
+        <v>119731838</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8316,25 +8257,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8347,10 +8288,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525699</v>
+        <v>525933</v>
       </c>
       <c r="R56" t="n">
-        <v>7178908</v>
+        <v>7178937</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -8382,7 +8323,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8392,12 +8333,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8413,6 +8354,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8430,10 +8391,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119731893</v>
+        <v>119731898</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8446,21 +8407,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8473,10 +8434,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525694</v>
+        <v>525707</v>
       </c>
       <c r="R57" t="n">
-        <v>7178950</v>
+        <v>7178873</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -8508,7 +8469,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8518,12 +8479,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8539,6 +8500,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8556,10 +8537,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119731857</v>
+        <v>119731895</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8572,31 +8553,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -8604,10 +8580,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525853</v>
+        <v>525699</v>
       </c>
       <c r="R58" t="n">
-        <v>7178853</v>
+        <v>7178908</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8639,7 +8615,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8649,12 +8625,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8663,27 +8639,13 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8701,10 +8663,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119731840</v>
+        <v>119731890</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8717,31 +8679,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8749,10 +8706,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525933</v>
+        <v>525658</v>
       </c>
       <c r="R59" t="n">
-        <v>7178939</v>
+        <v>7178997</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8784,7 +8741,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8794,12 +8751,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8808,27 +8760,13 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8846,7 +8784,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119731883</v>
+        <v>119731904</v>
       </c>
       <c r="B60" t="n">
         <v>79643</v>
@@ -8889,10 +8827,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525725</v>
+        <v>525762</v>
       </c>
       <c r="R60" t="n">
-        <v>7178979</v>
+        <v>7178853</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8924,7 +8862,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8934,7 +8872,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -8992,10 +8930,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119731851</v>
+        <v>119731850</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -9008,31 +8946,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -9040,10 +8973,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525862</v>
+        <v>525907</v>
       </c>
       <c r="R61" t="n">
-        <v>7178784</v>
+        <v>7178822</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -9075,7 +9008,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9085,12 +9018,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på 2 stående döda granar</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9099,12 +9032,13 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -9117,9 +9051,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -9137,10 +9076,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119731841</v>
+        <v>119731855</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9153,31 +9092,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -9185,10 +9119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525940</v>
+        <v>525852</v>
       </c>
       <c r="R62" t="n">
-        <v>7178908</v>
+        <v>7178820</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -9220,7 +9154,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9230,12 +9164,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9244,6 +9178,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -9254,17 +9189,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9282,7 +9222,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731876</v>
+        <v>119731857</v>
       </c>
       <c r="B63" t="n">
         <v>57310</v>
@@ -9330,10 +9270,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525781</v>
+        <v>525853</v>
       </c>
       <c r="R63" t="n">
-        <v>7178998</v>
+        <v>7178853</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9365,7 +9305,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9375,7 +9315,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9427,10 +9367,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731880</v>
+        <v>119731881</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9443,31 +9383,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -9475,10 +9410,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525751</v>
+        <v>525738</v>
       </c>
       <c r="R64" t="n">
-        <v>7178999</v>
+        <v>7178966</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9510,7 +9445,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9520,12 +9455,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9534,6 +9469,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -9544,17 +9480,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9718,7 +9659,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731848</v>
+        <v>119731865</v>
       </c>
       <c r="B66" t="n">
         <v>79608</v>
@@ -9761,10 +9702,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525936</v>
+        <v>525818</v>
       </c>
       <c r="R66" t="n">
-        <v>7178808</v>
+        <v>7178903</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9796,7 +9737,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9806,7 +9747,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9826,7 +9767,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9864,10 +9805,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731874</v>
+        <v>119731906</v>
       </c>
       <c r="B67" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9880,21 +9821,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9907,10 +9848,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525790</v>
+        <v>525765</v>
       </c>
       <c r="R67" t="n">
-        <v>7178955</v>
+        <v>7178799</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9942,7 +9883,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9952,12 +9893,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9977,22 +9918,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -10010,10 +9951,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119731918</v>
+        <v>119731901</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -10026,26 +9967,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -10053,10 +9999,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525837</v>
+        <v>525747</v>
       </c>
       <c r="R68" t="n">
-        <v>7178762</v>
+        <v>7178865</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -10088,7 +10034,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10098,7 +10044,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -10107,13 +10058,27 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -10131,10 +10096,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119731913</v>
+        <v>119731853</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10147,26 +10112,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -10174,10 +10144,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525778</v>
+        <v>525853</v>
       </c>
       <c r="R69" t="n">
-        <v>7178782</v>
+        <v>7178800</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -10209,7 +10179,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10219,7 +10189,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10228,13 +10203,27 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -10252,7 +10241,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119731887</v>
+        <v>119731912</v>
       </c>
       <c r="B70" t="n">
         <v>57310</v>
@@ -10290,7 +10279,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -10300,10 +10289,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525707</v>
+        <v>525763</v>
       </c>
       <c r="R70" t="n">
-        <v>7178998</v>
+        <v>7178776</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10335,7 +10324,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10345,12 +10334,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10397,10 +10386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119731838</v>
+        <v>119731917</v>
       </c>
       <c r="B71" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10409,25 +10398,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10440,10 +10429,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525933</v>
+        <v>525842</v>
       </c>
       <c r="R71" t="n">
-        <v>7178937</v>
+        <v>7178769</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10475,7 +10464,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10485,7 +10474,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10505,7 +10494,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -10543,10 +10532,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119731896</v>
+        <v>119731882</v>
       </c>
       <c r="B72" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10559,31 +10548,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -10591,10 +10575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>525699</v>
+        <v>525731</v>
       </c>
       <c r="R72" t="n">
-        <v>7178908</v>
+        <v>7178963</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -10626,7 +10610,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10636,12 +10620,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10650,6 +10634,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -10668,9 +10653,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10688,10 +10678,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119731855</v>
+        <v>119731866</v>
       </c>
       <c r="B73" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10704,21 +10694,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10731,10 +10721,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525852</v>
+        <v>525806</v>
       </c>
       <c r="R73" t="n">
-        <v>7178820</v>
+        <v>7178927</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -10766,7 +10756,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10776,12 +10766,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>på död sälg</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10797,26 +10782,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10834,10 +10799,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119731904</v>
+        <v>119731887</v>
       </c>
       <c r="B74" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10846,30 +10811,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10877,10 +10847,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>525762</v>
+        <v>525707</v>
       </c>
       <c r="R74" t="n">
-        <v>7178853</v>
+        <v>7178998</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -10912,7 +10882,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10922,12 +10892,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10936,7 +10906,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10947,22 +10916,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10980,7 +10944,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119731902</v>
+        <v>119731848</v>
       </c>
       <c r="B75" t="n">
         <v>79608</v>
@@ -11023,10 +10987,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>525769</v>
+        <v>525936</v>
       </c>
       <c r="R75" t="n">
-        <v>7178869</v>
+        <v>7178808</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -11058,7 +11022,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11068,12 +11032,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>på levande liggande sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -11088,7 +11052,7 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -11126,7 +11090,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119731856</v>
+        <v>119731861</v>
       </c>
       <c r="B76" t="n">
         <v>79608</v>
@@ -11169,10 +11133,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>525854</v>
+        <v>525826</v>
       </c>
       <c r="R76" t="n">
-        <v>7178867</v>
+        <v>7178869</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -11204,7 +11168,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11214,7 +11178,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -11272,10 +11236,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119731916</v>
+        <v>119731889</v>
       </c>
       <c r="B77" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -11284,25 +11248,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -11315,10 +11279,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525842</v>
+        <v>525688</v>
       </c>
       <c r="R77" t="n">
-        <v>7178769</v>
+        <v>7179014</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -11350,7 +11314,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11360,12 +11324,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -11380,27 +11344,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -11418,10 +11362,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119731900</v>
+        <v>119731896</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11434,34 +11378,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525738</v>
+        <v>525699</v>
       </c>
       <c r="R78" t="n">
-        <v>7178870</v>
+        <v>7178908</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -11493,7 +11445,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11503,7 +11455,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11514,6 +11471,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -11530,10 +11507,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119731870</v>
+        <v>119731913</v>
       </c>
       <c r="B79" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11542,25 +11519,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11573,10 +11550,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525790</v>
+        <v>525778</v>
       </c>
       <c r="R79" t="n">
-        <v>7178955</v>
+        <v>7178782</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -11608,7 +11585,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11618,12 +11595,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11639,26 +11611,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11676,10 +11628,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731875</v>
+        <v>119731867</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11692,31 +11644,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -11724,10 +11671,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525792</v>
+        <v>525802</v>
       </c>
       <c r="R80" t="n">
-        <v>7178967</v>
+        <v>7178930</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11759,7 +11706,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11769,12 +11716,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11783,6 +11730,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -11793,17 +11741,22 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11821,10 +11774,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731854</v>
+        <v>119731888</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11837,21 +11790,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11864,10 +11817,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525857</v>
+        <v>525689</v>
       </c>
       <c r="R81" t="n">
-        <v>7178804</v>
+        <v>7179025</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11899,7 +11852,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11909,12 +11862,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11930,6 +11883,26 @@
       <c r="AH81" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11947,7 +11920,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731853</v>
+        <v>119731851</v>
       </c>
       <c r="B82" t="n">
         <v>57310</v>
@@ -11995,10 +11968,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525853</v>
+        <v>525862</v>
       </c>
       <c r="R82" t="n">
-        <v>7178800</v>
+        <v>7178784</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12030,7 +12003,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12040,7 +12013,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12092,10 +12065,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119731898</v>
+        <v>119731907</v>
       </c>
       <c r="B83" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12108,26 +12081,31 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -12135,10 +12113,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525707</v>
+        <v>525765</v>
       </c>
       <c r="R83" t="n">
-        <v>7178873</v>
+        <v>7178799</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -12170,7 +12148,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12180,12 +12158,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -12194,7 +12172,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -12213,14 +12190,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12238,10 +12210,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119731839</v>
+        <v>119731843</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12254,26 +12226,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -12281,10 +12258,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525933</v>
+        <v>525949</v>
       </c>
       <c r="R84" t="n">
-        <v>7178937</v>
+        <v>7178888</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -12316,7 +12293,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12326,12 +12303,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12340,7 +12317,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -12351,22 +12327,17 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -12384,10 +12355,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119731899</v>
+        <v>119731875</v>
       </c>
       <c r="B85" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12396,30 +12367,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -12427,10 +12403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525724</v>
+        <v>525792</v>
       </c>
       <c r="R85" t="n">
-        <v>7178884</v>
+        <v>7178967</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -12462,7 +12438,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12472,12 +12448,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>på levande asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12486,7 +12462,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -12497,22 +12472,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12530,10 +12500,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731881</v>
+        <v>119731885</v>
       </c>
       <c r="B86" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12546,26 +12516,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12573,10 +12548,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525738</v>
+        <v>525697</v>
       </c>
       <c r="R86" t="n">
-        <v>7178966</v>
+        <v>7179006</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12608,7 +12583,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12618,12 +12593,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12632,7 +12607,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -12643,22 +12617,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12676,7 +12645,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119731868</v>
+        <v>119731905</v>
       </c>
       <c r="B87" t="n">
         <v>79608</v>
@@ -12719,10 +12688,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525802</v>
+        <v>525762</v>
       </c>
       <c r="R87" t="n">
-        <v>7178930</v>
+        <v>7178853</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -12754,7 +12723,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12764,12 +12733,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12789,12 +12758,12 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -12804,7 +12773,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12822,10 +12791,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119731901</v>
+        <v>119731884</v>
       </c>
       <c r="B88" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12838,31 +12807,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -12870,10 +12834,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525747</v>
+        <v>525725</v>
       </c>
       <c r="R88" t="n">
-        <v>7178865</v>
+        <v>7178979</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -12905,7 +12869,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12915,12 +12879,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12929,6 +12893,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -12939,17 +12904,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12967,10 +12937,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119731850</v>
+        <v>119731858</v>
       </c>
       <c r="B89" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12983,21 +12953,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -13010,10 +12980,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525907</v>
+        <v>525845</v>
       </c>
       <c r="R89" t="n">
-        <v>7178822</v>
+        <v>7178853</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -13045,7 +13015,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13055,12 +13025,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>på 2 stående döda granar</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -13075,27 +13045,27 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -13113,10 +13083,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119731906</v>
+        <v>119731897</v>
       </c>
       <c r="B90" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -13129,21 +13099,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -13156,10 +13126,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525765</v>
+        <v>525705</v>
       </c>
       <c r="R90" t="n">
-        <v>7178799</v>
+        <v>7178875</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -13191,7 +13161,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13201,12 +13171,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -13226,22 +13196,22 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -13259,7 +13229,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119731890</v>
+        <v>119731854</v>
       </c>
       <c r="B91" t="n">
         <v>78526</v>
@@ -13302,10 +13272,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525658</v>
+        <v>525857</v>
       </c>
       <c r="R91" t="n">
-        <v>7178997</v>
+        <v>7178804</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -13337,7 +13307,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13347,7 +13317,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -13380,10 +13355,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119731885</v>
+        <v>119731883</v>
       </c>
       <c r="B92" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13392,35 +13367,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -13428,10 +13398,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525697</v>
+        <v>525725</v>
       </c>
       <c r="R92" t="n">
-        <v>7179006</v>
+        <v>7178979</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -13463,7 +13433,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13473,12 +13443,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13487,6 +13457,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -13497,17 +13468,22 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -13525,10 +13501,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119731863</v>
+        <v>119731840</v>
       </c>
       <c r="B93" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13541,26 +13517,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -13568,10 +13549,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>525807</v>
+        <v>525933</v>
       </c>
       <c r="R93" t="n">
-        <v>7178896</v>
+        <v>7178939</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -13603,7 +13584,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13613,12 +13594,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13627,7 +13608,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -13638,22 +13618,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -13671,10 +13646,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119731891</v>
+        <v>119731914</v>
       </c>
       <c r="B94" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13687,21 +13662,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -13714,10 +13689,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>525653</v>
+        <v>525792</v>
       </c>
       <c r="R94" t="n">
-        <v>7178999</v>
+        <v>7178785</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -13749,7 +13724,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13759,12 +13734,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>på död högstubbe av sälg</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13784,22 +13759,22 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -13817,10 +13792,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119731861</v>
+        <v>119731860</v>
       </c>
       <c r="B95" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13833,26 +13808,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -13860,10 +13840,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>525826</v>
+        <v>525848</v>
       </c>
       <c r="R95" t="n">
-        <v>7178869</v>
+        <v>7178857</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -13895,7 +13875,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13905,12 +13885,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13919,7 +13899,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -13930,22 +13909,17 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13963,10 +13937,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119731915</v>
+        <v>119731891</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13979,21 +13953,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -14006,10 +13980,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>525820</v>
+        <v>525653</v>
       </c>
       <c r="R96" t="n">
-        <v>7178762</v>
+        <v>7178999</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -14041,7 +14015,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14051,7 +14025,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>på död högstubbe av sälg</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -14066,7 +14045,27 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -14084,10 +14083,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119731843</v>
+        <v>119731839</v>
       </c>
       <c r="B97" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -14100,31 +14099,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -14132,10 +14126,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>525949</v>
+        <v>525933</v>
       </c>
       <c r="R97" t="n">
-        <v>7178888</v>
+        <v>7178937</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -14167,7 +14161,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14177,12 +14171,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -14191,6 +14185,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -14201,17 +14196,22 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -8537,10 +8537,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119731895</v>
+        <v>119731855</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8553,21 +8553,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8580,10 +8580,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525699</v>
+        <v>525852</v>
       </c>
       <c r="R58" t="n">
-        <v>7178908</v>
+        <v>7178820</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8646,6 +8646,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8663,7 +8683,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119731890</v>
+        <v>119731895</v>
       </c>
       <c r="B59" t="n">
         <v>78526</v>
@@ -8706,10 +8726,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525658</v>
+        <v>525699</v>
       </c>
       <c r="R59" t="n">
-        <v>7178997</v>
+        <v>7178908</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8741,7 +8761,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8751,7 +8771,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8784,10 +8809,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119731904</v>
+        <v>119731890</v>
       </c>
       <c r="B60" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8796,25 +8821,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8827,10 +8852,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525762</v>
+        <v>525658</v>
       </c>
       <c r="R60" t="n">
-        <v>7178853</v>
+        <v>7178997</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8862,7 +8887,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8872,12 +8897,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8893,26 +8913,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119731850</v>
+        <v>119731904</v>
       </c>
       <c r="B61" t="n">
-        <v>90558</v>
+        <v>79643</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8942,25 +8942,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525907</v>
+        <v>525762</v>
       </c>
       <c r="R61" t="n">
-        <v>7178822</v>
+        <v>7178853</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>på 2 stående döda granar</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9038,27 +9038,27 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -9076,10 +9076,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119731855</v>
+        <v>119731850</v>
       </c>
       <c r="B62" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9092,21 +9092,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -9119,10 +9119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525852</v>
+        <v>525907</v>
       </c>
       <c r="R62" t="n">
-        <v>7178820</v>
+        <v>7178822</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på 2 stående döda granar</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9184,27 +9184,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9222,10 +9222,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731857</v>
+        <v>119731881</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9238,31 +9238,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -9270,10 +9265,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525853</v>
+        <v>525738</v>
       </c>
       <c r="R63" t="n">
-        <v>7178853</v>
+        <v>7178966</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9305,7 +9300,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9315,12 +9310,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9329,6 +9324,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -9339,17 +9335,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9367,7 +9368,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731881</v>
+        <v>119731903</v>
       </c>
       <c r="B64" t="n">
         <v>79608</v>
@@ -9410,10 +9411,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525738</v>
+        <v>525774</v>
       </c>
       <c r="R64" t="n">
-        <v>7178966</v>
+        <v>7178852</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9445,7 +9446,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9455,12 +9456,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9490,12 +9491,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9513,7 +9514,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119731903</v>
+        <v>119731865</v>
       </c>
       <c r="B65" t="n">
         <v>79608</v>
@@ -9556,10 +9557,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525774</v>
+        <v>525818</v>
       </c>
       <c r="R65" t="n">
-        <v>7178852</v>
+        <v>7178903</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9591,7 +9592,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9601,12 +9602,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9636,12 +9637,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9659,10 +9660,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731865</v>
+        <v>119731906</v>
       </c>
       <c r="B66" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9675,21 +9676,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9702,10 +9703,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525818</v>
+        <v>525765</v>
       </c>
       <c r="R66" t="n">
-        <v>7178903</v>
+        <v>7178799</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9737,7 +9738,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9747,12 +9748,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9772,22 +9773,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9805,10 +9806,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731906</v>
+        <v>119731857</v>
       </c>
       <c r="B67" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9821,26 +9822,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9848,10 +9854,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525765</v>
+        <v>525853</v>
       </c>
       <c r="R67" t="n">
-        <v>7178799</v>
+        <v>7178853</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9883,7 +9889,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9893,12 +9899,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9907,7 +9913,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9926,14 +9931,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -10386,10 +10386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119731917</v>
+        <v>119731866</v>
       </c>
       <c r="B71" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10402,21 +10402,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10429,10 +10429,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525842</v>
+        <v>525806</v>
       </c>
       <c r="R71" t="n">
-        <v>7178769</v>
+        <v>7178927</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10474,12 +10474,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10494,27 +10489,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10678,10 +10653,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119731866</v>
+        <v>119731917</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10694,21 +10669,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10721,10 +10696,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525806</v>
+        <v>525842</v>
       </c>
       <c r="R73" t="n">
-        <v>7178927</v>
+        <v>7178769</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -10756,7 +10731,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10766,7 +10741,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10781,7 +10761,27 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -13646,10 +13646,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119731914</v>
+        <v>119731860</v>
       </c>
       <c r="B94" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13662,26 +13662,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -13689,10 +13694,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>525792</v>
+        <v>525848</v>
       </c>
       <c r="R94" t="n">
-        <v>7178785</v>
+        <v>7178857</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -13724,7 +13729,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13734,12 +13739,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>på gammal stubbe</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13748,7 +13753,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -13767,14 +13771,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -13792,10 +13791,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119731860</v>
+        <v>119731914</v>
       </c>
       <c r="B95" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13808,31 +13807,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -13840,10 +13834,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>525848</v>
+        <v>525792</v>
       </c>
       <c r="R95" t="n">
-        <v>7178857</v>
+        <v>7178785</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -13875,7 +13869,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13885,12 +13879,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13899,6 +13893,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -13917,9 +13912,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119731966</v>
+        <v>119731946</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,31 +1108,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1140,10 +1135,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525966</v>
+        <v>525974</v>
       </c>
       <c r="R5" t="n">
-        <v>7178973</v>
+        <v>7178925</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1175,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1185,12 +1180,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,6 +1194,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1217,9 +1213,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1237,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119731969</v>
+        <v>119731922</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1253,21 +1254,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1280,10 +1281,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525973</v>
+        <v>525859</v>
       </c>
       <c r="R6" t="n">
-        <v>7178969</v>
+        <v>7178751</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1315,7 +1316,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1325,7 +1326,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1340,7 +1346,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1358,10 +1384,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119731933</v>
+        <v>119731936</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1370,25 +1396,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1401,10 +1427,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525971</v>
+        <v>525983</v>
       </c>
       <c r="R7" t="n">
-        <v>7178801</v>
+        <v>7178824</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1436,7 +1462,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1446,7 +1472,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1462,6 +1493,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1479,10 +1530,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119731932</v>
+        <v>119731948</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1495,26 +1546,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1522,10 +1578,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525935</v>
+        <v>525970</v>
       </c>
       <c r="R8" t="n">
-        <v>7178787</v>
+        <v>7178928</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1557,7 +1613,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1567,7 +1623,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1576,13 +1637,27 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1600,7 +1675,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119731944</v>
+        <v>119731965</v>
       </c>
       <c r="B9" t="n">
         <v>79608</v>
@@ -1643,10 +1718,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525985</v>
+        <v>525945</v>
       </c>
       <c r="R9" t="n">
-        <v>7178897</v>
+        <v>7178975</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1678,7 +1753,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1688,7 +1763,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1746,10 +1821,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731921</v>
+        <v>119731964</v>
       </c>
       <c r="B10" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1758,25 +1833,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1789,10 +1864,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525859</v>
+        <v>525926</v>
       </c>
       <c r="R10" t="n">
-        <v>7178751</v>
+        <v>7178980</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1824,7 +1899,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1834,12 +1909,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1854,27 +1924,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1892,10 +1942,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119731952</v>
+        <v>119731957</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1904,25 +1954,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1935,10 +1985,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525970</v>
+        <v>525916</v>
       </c>
       <c r="R11" t="n">
-        <v>7178943</v>
+        <v>7178975</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1970,7 +2020,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1980,7 +2030,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2038,7 +2088,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119731948</v>
+        <v>119731966</v>
       </c>
       <c r="B12" t="n">
         <v>57310</v>
@@ -2076,7 +2126,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2086,10 +2136,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525970</v>
+        <v>525966</v>
       </c>
       <c r="R12" t="n">
-        <v>7178928</v>
+        <v>7178973</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2121,7 +2171,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2131,12 +2181,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2183,7 +2233,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119731939</v>
+        <v>119731940</v>
       </c>
       <c r="B13" t="n">
         <v>79608</v>
@@ -2226,10 +2276,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525986</v>
+        <v>525970</v>
       </c>
       <c r="R13" t="n">
-        <v>7178882</v>
+        <v>7178901</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2261,7 +2311,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2271,12 +2321,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på knäckt levande sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2475,10 +2525,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119731924</v>
+        <v>119731933</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2491,31 +2541,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2523,10 +2568,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525862</v>
+        <v>525971</v>
       </c>
       <c r="R15" t="n">
-        <v>7178759</v>
+        <v>7178801</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2558,7 +2603,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2568,12 +2613,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2582,27 +2622,13 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2620,10 +2646,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119731920</v>
+        <v>119731969</v>
       </c>
       <c r="B16" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2636,21 +2662,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2663,10 +2689,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525843</v>
+        <v>525973</v>
       </c>
       <c r="R16" t="n">
-        <v>7178750</v>
+        <v>7178969</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2698,7 +2724,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2708,12 +2734,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:38</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>på stubbe</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2728,27 +2749,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2766,10 +2767,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119731950</v>
+        <v>119731932</v>
       </c>
       <c r="B17" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2778,25 +2779,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2809,10 +2810,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525969</v>
+        <v>525935</v>
       </c>
       <c r="R17" t="n">
-        <v>7178936</v>
+        <v>7178787</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2844,7 +2845,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2854,12 +2855,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>på liggande död björkstam</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2875,26 +2871,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2912,10 +2888,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119731965</v>
+        <v>119731926</v>
       </c>
       <c r="B18" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2928,21 +2904,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2955,10 +2931,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525945</v>
+        <v>525888</v>
       </c>
       <c r="R18" t="n">
-        <v>7178975</v>
+        <v>7178777</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2990,7 +2966,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3000,12 +2976,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3020,27 +2996,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3058,10 +3014,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119731940</v>
+        <v>119731962</v>
       </c>
       <c r="B19" t="n">
-        <v>79608</v>
+        <v>90846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3074,21 +3030,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3101,10 +3057,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525970</v>
+        <v>525906</v>
       </c>
       <c r="R19" t="n">
-        <v>7178901</v>
+        <v>7179007</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3136,7 +3092,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3146,12 +3102,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3171,22 +3127,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3204,10 +3160,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119731936</v>
+        <v>119731954</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3216,25 +3172,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3247,10 +3203,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525983</v>
+        <v>525946</v>
       </c>
       <c r="R20" t="n">
-        <v>7178824</v>
+        <v>7178956</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3282,7 +3238,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3292,12 +3248,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3317,12 +3273,12 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -3332,7 +3288,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3350,10 +3306,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119731919</v>
+        <v>119731956</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3366,31 +3322,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3398,10 +3349,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525842</v>
+        <v>525939</v>
       </c>
       <c r="R21" t="n">
-        <v>7178749</v>
+        <v>7178962</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3433,7 +3384,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3443,12 +3394,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3457,27 +3408,33 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3495,10 +3452,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119731945</v>
+        <v>119731950</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3507,38 +3464,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525961</v>
+        <v>525969</v>
       </c>
       <c r="R22" t="n">
-        <v>7178906</v>
+        <v>7178936</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3570,7 +3530,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3580,7 +3540,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>på liggande död björkstam</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3589,8 +3554,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3607,10 +3598,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119731935</v>
+        <v>119731925</v>
       </c>
       <c r="B23" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3623,26 +3614,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3650,10 +3646,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525983</v>
+        <v>525849</v>
       </c>
       <c r="R23" t="n">
-        <v>7178824</v>
+        <v>7178772</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3685,7 +3681,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3695,12 +3691,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3709,33 +3705,27 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3753,10 +3743,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119731956</v>
+        <v>119731924</v>
       </c>
       <c r="B24" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3769,26 +3759,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3796,10 +3791,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525939</v>
+        <v>525862</v>
       </c>
       <c r="R24" t="n">
-        <v>7178962</v>
+        <v>7178759</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3831,7 +3826,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3841,12 +3836,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3855,33 +3850,27 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3899,10 +3888,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119731953</v>
+        <v>119731944</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3915,21 +3904,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3942,10 +3931,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525946</v>
+        <v>525985</v>
       </c>
       <c r="R25" t="n">
-        <v>7178938</v>
+        <v>7178897</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3977,7 +3966,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3987,7 +3976,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4003,6 +3997,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4020,10 +4034,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119731943</v>
+        <v>119731927</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4032,25 +4046,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -4063,10 +4077,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525979</v>
+        <v>525918</v>
       </c>
       <c r="R26" t="n">
-        <v>7178902</v>
+        <v>7178789</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4098,7 +4112,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4108,7 +4122,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4166,10 +4180,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119731954</v>
+        <v>119731938</v>
       </c>
       <c r="B27" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4182,26 +4196,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4209,10 +4228,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525946</v>
+        <v>525979</v>
       </c>
       <c r="R27" t="n">
-        <v>7178956</v>
+        <v>7178844</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4244,7 +4263,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4254,12 +4273,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4268,7 +4287,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4279,22 +4297,17 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4312,7 +4325,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119731922</v>
+        <v>119731930</v>
       </c>
       <c r="B28" t="n">
         <v>79608</v>
@@ -4355,10 +4368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525859</v>
+        <v>525916</v>
       </c>
       <c r="R28" t="n">
-        <v>7178751</v>
+        <v>7178775</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4390,7 +4403,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4400,7 +4413,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4420,7 +4433,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4458,10 +4471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119731964</v>
+        <v>119731921</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4470,25 +4483,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4501,10 +4514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525926</v>
+        <v>525859</v>
       </c>
       <c r="R29" t="n">
-        <v>7178980</v>
+        <v>7178751</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4536,7 +4549,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4546,7 +4559,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4561,7 +4579,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4579,10 +4617,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119731962</v>
+        <v>119731942</v>
       </c>
       <c r="B30" t="n">
-        <v>90846</v>
+        <v>79636</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4591,25 +4629,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4622,10 +4660,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525906</v>
+        <v>525970</v>
       </c>
       <c r="R30" t="n">
-        <v>7179007</v>
+        <v>7178901</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4657,7 +4695,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4667,12 +4705,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4692,22 +4730,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4725,10 +4763,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119731938</v>
+        <v>119731945</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4741,42 +4779,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525979</v>
+        <v>525961</v>
       </c>
       <c r="R31" t="n">
-        <v>7178844</v>
+        <v>7178906</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4808,7 +4838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4818,12 +4848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4834,26 +4859,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4870,10 +4875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119731927</v>
+        <v>119731943</v>
       </c>
       <c r="B32" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4882,25 +4887,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4913,10 +4918,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525918</v>
+        <v>525979</v>
       </c>
       <c r="R32" t="n">
-        <v>7178789</v>
+        <v>7178902</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4948,7 +4953,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4958,7 +4963,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5016,10 +5021,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119731926</v>
+        <v>119731935</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5032,21 +5037,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -5059,10 +5064,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525888</v>
+        <v>525983</v>
       </c>
       <c r="R33" t="n">
-        <v>7178777</v>
+        <v>7178824</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -5094,7 +5099,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5104,12 +5109,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5124,7 +5129,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5142,10 +5167,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119731942</v>
+        <v>119731919</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5154,30 +5179,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5185,10 +5215,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525970</v>
+        <v>525842</v>
       </c>
       <c r="R34" t="n">
-        <v>7178901</v>
+        <v>7178749</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -5220,7 +5250,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5230,12 +5260,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5244,33 +5274,27 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5288,10 +5312,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119731946</v>
+        <v>119731920</v>
       </c>
       <c r="B35" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5304,21 +5328,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5331,10 +5355,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525974</v>
+        <v>525843</v>
       </c>
       <c r="R35" t="n">
-        <v>7178925</v>
+        <v>7178750</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5366,7 +5390,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5376,12 +5400,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5396,7 +5420,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5411,12 +5435,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5434,10 +5458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119731930</v>
+        <v>119731952</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5446,25 +5470,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5477,10 +5501,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525916</v>
+        <v>525970</v>
       </c>
       <c r="R36" t="n">
-        <v>7178775</v>
+        <v>7178943</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5512,7 +5536,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5522,7 +5546,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5580,10 +5604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119731957</v>
+        <v>119731953</v>
       </c>
       <c r="B37" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5596,21 +5620,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5623,10 +5647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525916</v>
+        <v>525946</v>
       </c>
       <c r="R37" t="n">
-        <v>7178975</v>
+        <v>7178938</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5658,7 +5682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5668,12 +5692,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5689,26 +5708,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5726,10 +5725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119731925</v>
+        <v>119731939</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5742,31 +5741,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5774,10 +5768,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525849</v>
+        <v>525986</v>
       </c>
       <c r="R38" t="n">
-        <v>7178772</v>
+        <v>7178882</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5809,7 +5803,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5819,12 +5813,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på knäckt levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5833,27 +5827,33 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5871,7 +5871,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119731856</v>
+        <v>119731848</v>
       </c>
       <c r="B39" t="n">
         <v>79608</v>
@@ -5914,10 +5914,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525854</v>
+        <v>525936</v>
       </c>
       <c r="R39" t="n">
-        <v>7178867</v>
+        <v>7178808</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -6017,10 +6017,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119731900</v>
+        <v>119731874</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6033,34 +6033,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525738</v>
+        <v>525790</v>
       </c>
       <c r="R40" t="n">
-        <v>7178870</v>
+        <v>7178955</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -6092,7 +6095,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6102,7 +6105,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6111,8 +6119,34 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -6129,10 +6163,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119731916</v>
+        <v>119731893</v>
       </c>
       <c r="B41" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6141,25 +6175,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -6172,10 +6206,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525842</v>
+        <v>525694</v>
       </c>
       <c r="R41" t="n">
-        <v>7178769</v>
+        <v>7178950</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -6207,7 +6241,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6217,12 +6251,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6237,27 +6271,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6275,10 +6289,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119731915</v>
+        <v>119731883</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6287,25 +6301,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6318,10 +6332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525820</v>
+        <v>525725</v>
       </c>
       <c r="R42" t="n">
-        <v>7178762</v>
+        <v>7178979</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6353,7 +6367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6363,7 +6377,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6378,7 +6397,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6396,10 +6435,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119731868</v>
+        <v>119731898</v>
       </c>
       <c r="B43" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6412,21 +6451,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6439,10 +6478,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525802</v>
+        <v>525707</v>
       </c>
       <c r="R43" t="n">
-        <v>7178930</v>
+        <v>7178873</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6474,7 +6513,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6484,12 +6523,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6509,22 +6548,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6542,10 +6581,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119731870</v>
+        <v>119731842</v>
       </c>
       <c r="B44" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6554,25 +6593,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6585,10 +6624,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525790</v>
+        <v>525950</v>
       </c>
       <c r="R44" t="n">
-        <v>7178955</v>
+        <v>7178893</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6620,7 +6659,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6630,7 +6669,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6688,10 +6727,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119731899</v>
+        <v>119731885</v>
       </c>
       <c r="B45" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6700,30 +6739,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6731,10 +6775,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525724</v>
+        <v>525697</v>
       </c>
       <c r="R45" t="n">
-        <v>7178884</v>
+        <v>7179006</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6766,7 +6810,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6776,12 +6820,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>på levande asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6790,7 +6834,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6801,22 +6844,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6834,10 +6872,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119731893</v>
+        <v>119731843</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6850,26 +6888,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6877,10 +6920,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525694</v>
+        <v>525949</v>
       </c>
       <c r="R46" t="n">
-        <v>7178950</v>
+        <v>7178888</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6912,7 +6955,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6922,12 +6965,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6936,13 +6979,27 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6960,10 +7017,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119731910</v>
+        <v>119731881</v>
       </c>
       <c r="B47" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6976,31 +7033,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -7008,10 +7060,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525767</v>
+        <v>525738</v>
       </c>
       <c r="R47" t="n">
-        <v>7178808</v>
+        <v>7178966</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -7043,7 +7095,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7053,12 +7105,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7067,6 +7119,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -7077,17 +7130,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7105,7 +7163,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119731863</v>
+        <v>119731897</v>
       </c>
       <c r="B48" t="n">
         <v>79608</v>
@@ -7148,10 +7206,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525807</v>
+        <v>525705</v>
       </c>
       <c r="R48" t="n">
-        <v>7178896</v>
+        <v>7178875</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -7183,7 +7241,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7193,7 +7251,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7251,10 +7309,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119731842</v>
+        <v>119731889</v>
       </c>
       <c r="B49" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7267,21 +7325,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -7294,10 +7352,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525950</v>
+        <v>525688</v>
       </c>
       <c r="R49" t="n">
-        <v>7178893</v>
+        <v>7179014</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7329,7 +7387,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7339,12 +7397,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7360,26 +7418,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7397,10 +7435,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119731841</v>
+        <v>119731905</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7413,31 +7451,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -7445,10 +7478,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525940</v>
+        <v>525762</v>
       </c>
       <c r="R50" t="n">
-        <v>7178908</v>
+        <v>7178853</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7480,7 +7513,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7490,12 +7523,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7504,6 +7537,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7522,9 +7556,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7542,10 +7581,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119731876</v>
+        <v>119731888</v>
       </c>
       <c r="B51" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7558,31 +7597,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -7590,10 +7624,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525781</v>
+        <v>525689</v>
       </c>
       <c r="R51" t="n">
-        <v>7178998</v>
+        <v>7179025</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7625,7 +7659,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7635,12 +7669,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7649,6 +7683,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7659,17 +7694,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7687,7 +7727,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119731874</v>
+        <v>119731917</v>
       </c>
       <c r="B52" t="n">
         <v>79608</v>
@@ -7730,10 +7770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525790</v>
+        <v>525842</v>
       </c>
       <c r="R52" t="n">
-        <v>7178955</v>
+        <v>7178769</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7765,7 +7805,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7775,7 +7815,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7795,7 +7835,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7833,7 +7873,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119731902</v>
+        <v>119731856</v>
       </c>
       <c r="B53" t="n">
         <v>79608</v>
@@ -7876,10 +7916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525769</v>
+        <v>525854</v>
       </c>
       <c r="R53" t="n">
-        <v>7178869</v>
+        <v>7178867</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7911,7 +7951,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7921,12 +7961,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>på levande liggande sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7979,10 +8019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119731880</v>
+        <v>119731863</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7995,31 +8035,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -8027,10 +8062,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525751</v>
+        <v>525807</v>
       </c>
       <c r="R54" t="n">
-        <v>7178999</v>
+        <v>7178896</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -8062,7 +8097,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8072,12 +8107,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8086,6 +8121,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -8096,17 +8132,22 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8124,10 +8165,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119731918</v>
+        <v>119731870</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8136,25 +8177,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -8167,10 +8208,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525837</v>
+        <v>525790</v>
       </c>
       <c r="R55" t="n">
-        <v>7178762</v>
+        <v>7178955</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -8202,7 +8243,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8212,7 +8253,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8227,7 +8273,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8245,10 +8311,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119731838</v>
+        <v>119731887</v>
       </c>
       <c r="B56" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8257,30 +8323,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -8288,10 +8359,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525933</v>
+        <v>525707</v>
       </c>
       <c r="R56" t="n">
-        <v>7178937</v>
+        <v>7178998</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -8323,7 +8394,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8333,12 +8404,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8347,7 +8418,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -8358,22 +8428,17 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8391,10 +8456,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119731898</v>
+        <v>119731858</v>
       </c>
       <c r="B57" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8407,21 +8472,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8434,10 +8499,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525707</v>
+        <v>525845</v>
       </c>
       <c r="R57" t="n">
-        <v>7178873</v>
+        <v>7178853</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -8469,7 +8534,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8479,12 +8544,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8504,22 +8569,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8537,7 +8602,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119731855</v>
+        <v>119731865</v>
       </c>
       <c r="B58" t="n">
         <v>79608</v>
@@ -8580,10 +8645,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525852</v>
+        <v>525818</v>
       </c>
       <c r="R58" t="n">
-        <v>7178820</v>
+        <v>7178903</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8615,7 +8680,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8625,12 +8690,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8660,12 +8725,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8683,10 +8748,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119731895</v>
+        <v>119731882</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8699,21 +8764,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8726,10 +8791,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525699</v>
+        <v>525731</v>
       </c>
       <c r="R59" t="n">
-        <v>7178908</v>
+        <v>7178963</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8761,7 +8826,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8771,12 +8836,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8792,6 +8857,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8809,7 +8894,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119731890</v>
+        <v>119731895</v>
       </c>
       <c r="B60" t="n">
         <v>78526</v>
@@ -8852,10 +8937,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525658</v>
+        <v>525699</v>
       </c>
       <c r="R60" t="n">
-        <v>7178997</v>
+        <v>7178908</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8887,7 +8972,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8897,7 +8982,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8930,10 +9020,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119731904</v>
+        <v>119731866</v>
       </c>
       <c r="B61" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8942,25 +9032,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8973,10 +9063,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525762</v>
+        <v>525806</v>
       </c>
       <c r="R61" t="n">
-        <v>7178853</v>
+        <v>7178927</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -9008,7 +9098,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9018,12 +9108,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9039,26 +9124,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -9076,10 +9141,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119731850</v>
+        <v>119731860</v>
       </c>
       <c r="B62" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9092,26 +9157,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -9119,10 +9189,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525907</v>
+        <v>525848</v>
       </c>
       <c r="R62" t="n">
-        <v>7178822</v>
+        <v>7178857</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -9154,7 +9224,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9164,12 +9234,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>på 2 stående döda granar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9178,13 +9248,12 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -9197,14 +9266,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9222,10 +9286,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731881</v>
+        <v>119731876</v>
       </c>
       <c r="B63" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9238,26 +9302,31 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -9265,10 +9334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525738</v>
+        <v>525781</v>
       </c>
       <c r="R63" t="n">
-        <v>7178966</v>
+        <v>7178998</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9300,7 +9369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9310,12 +9379,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9324,7 +9393,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -9335,22 +9403,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9368,10 +9431,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731903</v>
+        <v>119731838</v>
       </c>
       <c r="B64" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9380,25 +9443,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9411,10 +9474,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525774</v>
+        <v>525933</v>
       </c>
       <c r="R64" t="n">
-        <v>7178852</v>
+        <v>7178937</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9446,7 +9509,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9456,12 +9519,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9491,12 +9554,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9514,10 +9577,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119731865</v>
+        <v>119731914</v>
       </c>
       <c r="B65" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9530,21 +9593,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9557,10 +9620,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525818</v>
+        <v>525792</v>
       </c>
       <c r="R65" t="n">
-        <v>7178903</v>
+        <v>7178785</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9592,7 +9655,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9602,12 +9665,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9627,22 +9690,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9660,7 +9723,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731906</v>
+        <v>119731850</v>
       </c>
       <c r="B66" t="n">
         <v>90558</v>
@@ -9703,10 +9766,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525765</v>
+        <v>525907</v>
       </c>
       <c r="R66" t="n">
-        <v>7178799</v>
+        <v>7178822</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9738,7 +9801,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9748,12 +9811,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på 2 stående döda granar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9768,7 +9831,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9806,10 +9869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731857</v>
+        <v>119731915</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9822,31 +9885,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9854,10 +9912,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525853</v>
+        <v>525820</v>
       </c>
       <c r="R67" t="n">
-        <v>7178853</v>
+        <v>7178762</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9889,7 +9947,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9899,12 +9957,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9913,27 +9966,13 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9951,7 +9990,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119731901</v>
+        <v>119731880</v>
       </c>
       <c r="B68" t="n">
         <v>57310</v>
@@ -9999,10 +10038,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525747</v>
+        <v>525751</v>
       </c>
       <c r="R68" t="n">
-        <v>7178865</v>
+        <v>7178999</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -10034,7 +10073,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10044,7 +10083,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10096,7 +10135,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119731853</v>
+        <v>119731910</v>
       </c>
       <c r="B69" t="n">
         <v>57310</v>
@@ -10144,10 +10183,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525853</v>
+        <v>525767</v>
       </c>
       <c r="R69" t="n">
-        <v>7178800</v>
+        <v>7178808</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -10179,7 +10218,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10189,7 +10228,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10241,7 +10280,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119731912</v>
+        <v>119731841</v>
       </c>
       <c r="B70" t="n">
         <v>57310</v>
@@ -10289,10 +10328,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525763</v>
+        <v>525940</v>
       </c>
       <c r="R70" t="n">
-        <v>7178776</v>
+        <v>7178908</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10324,7 +10363,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10334,7 +10373,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -10386,10 +10425,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119731866</v>
+        <v>119731916</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10398,25 +10437,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10429,10 +10468,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525806</v>
+        <v>525842</v>
       </c>
       <c r="R71" t="n">
-        <v>7178927</v>
+        <v>7178769</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10464,7 +10503,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10474,7 +10513,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10489,7 +10533,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10507,10 +10571,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119731882</v>
+        <v>119731867</v>
       </c>
       <c r="B72" t="n">
-        <v>90558</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10523,21 +10587,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10550,10 +10614,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>525731</v>
+        <v>525802</v>
       </c>
       <c r="R72" t="n">
-        <v>7178963</v>
+        <v>7178930</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -10585,7 +10649,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10595,12 +10659,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10620,22 +10684,22 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10653,10 +10717,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119731917</v>
+        <v>119731900</v>
       </c>
       <c r="B73" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10669,37 +10733,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525842</v>
+        <v>525738</v>
       </c>
       <c r="R73" t="n">
-        <v>7178769</v>
+        <v>7178870</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -10731,7 +10792,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10741,12 +10802,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10755,34 +10811,8 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -10799,10 +10829,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119731887</v>
+        <v>119731913</v>
       </c>
       <c r="B74" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10815,31 +10845,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10847,10 +10872,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>525707</v>
+        <v>525778</v>
       </c>
       <c r="R74" t="n">
-        <v>7178998</v>
+        <v>7178782</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -10882,7 +10907,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10892,12 +10917,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10906,27 +10926,13 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10944,7 +10950,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119731848</v>
+        <v>119731903</v>
       </c>
       <c r="B75" t="n">
         <v>79608</v>
@@ -10987,10 +10993,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>525936</v>
+        <v>525774</v>
       </c>
       <c r="R75" t="n">
-        <v>7178808</v>
+        <v>7178852</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -11022,7 +11028,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11032,12 +11038,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -11052,7 +11058,7 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -11067,12 +11073,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -11090,10 +11096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119731861</v>
+        <v>119731840</v>
       </c>
       <c r="B76" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -11106,26 +11112,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -11133,10 +11144,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>525826</v>
+        <v>525933</v>
       </c>
       <c r="R76" t="n">
-        <v>7178869</v>
+        <v>7178939</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -11168,7 +11179,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11178,12 +11189,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -11192,7 +11203,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -11203,22 +11213,17 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -11236,10 +11241,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119731889</v>
+        <v>119731875</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -11252,26 +11257,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -11279,10 +11289,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525688</v>
+        <v>525792</v>
       </c>
       <c r="R77" t="n">
-        <v>7179014</v>
+        <v>7178967</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -11314,7 +11324,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11324,12 +11334,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -11338,13 +11348,27 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -11362,10 +11386,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119731896</v>
+        <v>119731890</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11378,31 +11402,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -11410,10 +11429,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525699</v>
+        <v>525658</v>
       </c>
       <c r="R78" t="n">
-        <v>7178908</v>
+        <v>7178997</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -11445,7 +11464,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11455,12 +11474,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11469,27 +11483,13 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119731913</v>
+        <v>119731884</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525778</v>
+        <v>525725</v>
       </c>
       <c r="R79" t="n">
-        <v>7178782</v>
+        <v>7178979</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11595,7 +11595,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11611,6 +11616,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11628,10 +11653,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731867</v>
+        <v>119731855</v>
       </c>
       <c r="B80" t="n">
-        <v>79607</v>
+        <v>79608</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11644,21 +11669,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -11671,10 +11696,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525802</v>
+        <v>525852</v>
       </c>
       <c r="R80" t="n">
-        <v>7178930</v>
+        <v>7178820</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11706,7 +11731,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11716,12 +11741,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11751,12 +11776,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11774,10 +11799,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731888</v>
+        <v>119731906</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11790,21 +11815,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11817,10 +11842,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525689</v>
+        <v>525765</v>
       </c>
       <c r="R81" t="n">
-        <v>7179025</v>
+        <v>7178799</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11852,7 +11877,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11862,12 +11887,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11887,22 +11912,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11920,10 +11945,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731851</v>
+        <v>119731854</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11936,31 +11961,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11968,10 +11988,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525862</v>
+        <v>525857</v>
       </c>
       <c r="R82" t="n">
-        <v>7178784</v>
+        <v>7178804</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12003,7 +12023,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12013,12 +12033,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -12027,27 +12047,13 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -12065,10 +12071,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119731907</v>
+        <v>119731904</v>
       </c>
       <c r="B83" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12077,35 +12083,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -12113,10 +12114,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525765</v>
+        <v>525762</v>
       </c>
       <c r="R83" t="n">
-        <v>7178799</v>
+        <v>7178853</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -12148,7 +12149,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12158,12 +12159,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -12172,6 +12173,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -12182,17 +12184,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12210,10 +12217,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119731843</v>
+        <v>119731839</v>
       </c>
       <c r="B84" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12226,31 +12233,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -12258,10 +12260,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525949</v>
+        <v>525933</v>
       </c>
       <c r="R84" t="n">
-        <v>7178888</v>
+        <v>7178937</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -12293,7 +12295,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12303,12 +12305,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12317,6 +12319,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -12327,17 +12330,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -12355,7 +12363,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119731875</v>
+        <v>119731912</v>
       </c>
       <c r="B85" t="n">
         <v>57310</v>
@@ -12393,7 +12401,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -12403,10 +12411,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525792</v>
+        <v>525763</v>
       </c>
       <c r="R85" t="n">
-        <v>7178967</v>
+        <v>7178776</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -12438,7 +12446,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12448,12 +12456,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12500,10 +12508,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731885</v>
+        <v>119731868</v>
       </c>
       <c r="B86" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12516,31 +12524,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12548,10 +12551,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525697</v>
+        <v>525802</v>
       </c>
       <c r="R86" t="n">
-        <v>7179006</v>
+        <v>7178930</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12583,7 +12586,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12593,12 +12596,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12607,6 +12610,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -12617,17 +12621,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12645,10 +12654,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119731905</v>
+        <v>119731899</v>
       </c>
       <c r="B87" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12657,25 +12666,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -12688,10 +12697,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525762</v>
+        <v>525724</v>
       </c>
       <c r="R87" t="n">
-        <v>7178853</v>
+        <v>7178884</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -12723,7 +12732,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12733,12 +12742,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
+          <t>på levande asp</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12758,12 +12767,12 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -12773,7 +12782,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12791,10 +12800,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119731884</v>
+        <v>119731901</v>
       </c>
       <c r="B88" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12807,26 +12816,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -12834,10 +12848,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525725</v>
+        <v>525747</v>
       </c>
       <c r="R88" t="n">
-        <v>7178979</v>
+        <v>7178865</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -12869,7 +12883,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12879,12 +12893,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12893,7 +12907,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -12904,22 +12917,17 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12937,10 +12945,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119731858</v>
+        <v>119731857</v>
       </c>
       <c r="B89" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12953,26 +12961,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -12980,7 +12993,7 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525845</v>
+        <v>525853</v>
       </c>
       <c r="R89" t="n">
         <v>7178853</v>
@@ -13015,7 +13028,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13025,12 +13038,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -13039,7 +13052,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -13050,22 +13062,17 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -13083,10 +13090,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119731897</v>
+        <v>119731896</v>
       </c>
       <c r="B90" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -13099,26 +13106,31 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -13126,10 +13138,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525705</v>
+        <v>525699</v>
       </c>
       <c r="R90" t="n">
-        <v>7178875</v>
+        <v>7178908</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -13161,7 +13173,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13171,12 +13183,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -13185,7 +13197,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -13196,22 +13207,17 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -13229,10 +13235,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119731854</v>
+        <v>119731907</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13245,26 +13251,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -13272,10 +13283,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525857</v>
+        <v>525765</v>
       </c>
       <c r="R91" t="n">
-        <v>7178804</v>
+        <v>7178799</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -13307,7 +13318,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13317,12 +13328,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -13331,13 +13342,27 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13355,10 +13380,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119731883</v>
+        <v>119731853</v>
       </c>
       <c r="B92" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13367,30 +13392,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -13398,10 +13428,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525725</v>
+        <v>525853</v>
       </c>
       <c r="R92" t="n">
-        <v>7178979</v>
+        <v>7178800</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -13433,7 +13463,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13443,12 +13473,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13457,7 +13487,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -13468,22 +13497,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -13501,7 +13525,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119731840</v>
+        <v>119731851</v>
       </c>
       <c r="B93" t="n">
         <v>57310</v>
@@ -13549,10 +13573,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>525933</v>
+        <v>525862</v>
       </c>
       <c r="R93" t="n">
-        <v>7178939</v>
+        <v>7178784</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -13584,7 +13608,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13594,7 +13618,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
@@ -13646,10 +13670,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119731860</v>
+        <v>119731918</v>
       </c>
       <c r="B94" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13662,31 +13686,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -13694,10 +13713,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>525848</v>
+        <v>525837</v>
       </c>
       <c r="R94" t="n">
-        <v>7178857</v>
+        <v>7178762</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -13729,7 +13748,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13739,12 +13758,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13753,27 +13767,13 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -13791,10 +13791,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119731914</v>
+        <v>119731891</v>
       </c>
       <c r="B95" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13807,21 +13807,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -13834,10 +13834,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>525792</v>
+        <v>525653</v>
       </c>
       <c r="R95" t="n">
-        <v>7178785</v>
+        <v>7178999</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13879,12 +13879,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>på gammal stubbe</t>
+          <t>på död högstubbe av sälg</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13904,22 +13904,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119731891</v>
+        <v>119731861</v>
       </c>
       <c r="B96" t="n">
         <v>79608</v>
@@ -13980,10 +13980,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>525653</v>
+        <v>525826</v>
       </c>
       <c r="R96" t="n">
-        <v>7178999</v>
+        <v>7178869</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>på död högstubbe av sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -14060,12 +14060,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -14083,7 +14083,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119731839</v>
+        <v>119731902</v>
       </c>
       <c r="B97" t="n">
         <v>79608</v>
@@ -14126,10 +14126,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>525933</v>
+        <v>525769</v>
       </c>
       <c r="R97" t="n">
-        <v>7178937</v>
+        <v>7178869</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14171,12 +14171,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på levande liggande sälg</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -14229,10 +14229,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119894748</v>
+        <v>119894773</v>
       </c>
       <c r="B98" t="n">
-        <v>90562</v>
+        <v>90558</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>på granlåga med bark</t>
+          <t>på gran stubbe</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -14375,10 +14375,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119894773</v>
+        <v>119894748</v>
       </c>
       <c r="B99" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -14391,21 +14391,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>på gran stubbe</t>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -14498,12 +14498,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -5458,10 +5458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119731952</v>
+        <v>119731939</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5470,25 +5470,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525970</v>
+        <v>525986</v>
       </c>
       <c r="R36" t="n">
-        <v>7178943</v>
+        <v>7178882</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på knäckt levande sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119731953</v>
+        <v>119731952</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5616,25 +5616,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525946</v>
+        <v>525970</v>
       </c>
       <c r="R37" t="n">
-        <v>7178938</v>
+        <v>7178943</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5692,7 +5692,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5708,6 +5713,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5725,10 +5750,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119731939</v>
+        <v>119731953</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5741,21 +5766,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5768,10 +5793,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525986</v>
+        <v>525946</v>
       </c>
       <c r="R38" t="n">
-        <v>7178882</v>
+        <v>7178938</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5803,7 +5828,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5813,12 +5838,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>på knäckt levande sälg</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5834,26 +5854,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119731914</v>
+        <v>119731915</v>
       </c>
       <c r="B65" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9593,21 +9593,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9620,10 +9620,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525792</v>
+        <v>525820</v>
       </c>
       <c r="R65" t="n">
-        <v>7178785</v>
+        <v>7178762</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9665,12 +9665,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>på gammal stubbe</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9685,27 +9680,7 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9723,7 +9698,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731850</v>
+        <v>119731914</v>
       </c>
       <c r="B66" t="n">
         <v>90558</v>
@@ -9766,10 +9741,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525907</v>
+        <v>525792</v>
       </c>
       <c r="R66" t="n">
-        <v>7178822</v>
+        <v>7178785</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9801,7 +9776,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9811,12 +9786,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på 2 stående döda granar</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9831,7 +9806,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9869,10 +9844,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731915</v>
+        <v>119731850</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9885,21 +9860,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9912,10 +9887,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525820</v>
+        <v>525907</v>
       </c>
       <c r="R67" t="n">
-        <v>7178762</v>
+        <v>7178822</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9947,7 +9922,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9957,7 +9932,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>på 2 stående döda granar</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9972,7 +9952,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119731884</v>
+        <v>119731854</v>
       </c>
       <c r="B79" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525725</v>
+        <v>525857</v>
       </c>
       <c r="R79" t="n">
-        <v>7178979</v>
+        <v>7178804</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11616,26 +11616,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11653,7 +11633,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731855</v>
+        <v>119731884</v>
       </c>
       <c r="B80" t="n">
         <v>79608</v>
@@ -11696,10 +11676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525852</v>
+        <v>525725</v>
       </c>
       <c r="R80" t="n">
-        <v>7178820</v>
+        <v>7178979</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11731,7 +11711,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11741,12 +11721,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11776,12 +11756,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11799,10 +11779,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731906</v>
+        <v>119731855</v>
       </c>
       <c r="B81" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11815,21 +11795,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11842,10 +11822,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525765</v>
+        <v>525852</v>
       </c>
       <c r="R81" t="n">
-        <v>7178799</v>
+        <v>7178820</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11877,7 +11857,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11887,12 +11867,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11912,22 +11892,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11945,10 +11925,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731854</v>
+        <v>119731906</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11961,21 +11941,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11988,10 +11968,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525857</v>
+        <v>525765</v>
       </c>
       <c r="R82" t="n">
-        <v>7178804</v>
+        <v>7178799</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12023,7 +12003,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12033,12 +12013,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -12054,6 +12034,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -12508,10 +12508,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731868</v>
+        <v>119731901</v>
       </c>
       <c r="B86" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12524,26 +12524,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12551,10 +12556,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525802</v>
+        <v>525747</v>
       </c>
       <c r="R86" t="n">
-        <v>7178930</v>
+        <v>7178865</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12586,7 +12591,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12596,12 +12601,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12610,7 +12615,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -12621,22 +12625,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12654,10 +12653,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119731899</v>
+        <v>119731857</v>
       </c>
       <c r="B87" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12666,30 +12665,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -12697,10 +12701,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525724</v>
+        <v>525853</v>
       </c>
       <c r="R87" t="n">
-        <v>7178884</v>
+        <v>7178853</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -12732,7 +12736,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12742,12 +12746,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>på levande asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12756,7 +12760,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -12767,22 +12770,17 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12800,7 +12798,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119731901</v>
+        <v>119731896</v>
       </c>
       <c r="B88" t="n">
         <v>57310</v>
@@ -12848,10 +12846,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525747</v>
+        <v>525699</v>
       </c>
       <c r="R88" t="n">
-        <v>7178865</v>
+        <v>7178908</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -12883,7 +12881,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12893,7 +12891,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -12945,7 +12943,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119731857</v>
+        <v>119731907</v>
       </c>
       <c r="B89" t="n">
         <v>57310</v>
@@ -12993,10 +12991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525853</v>
+        <v>525765</v>
       </c>
       <c r="R89" t="n">
-        <v>7178853</v>
+        <v>7178799</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -13028,7 +13026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13038,7 +13036,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13090,7 +13088,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119731896</v>
+        <v>119731853</v>
       </c>
       <c r="B90" t="n">
         <v>57310</v>
@@ -13138,10 +13136,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525699</v>
+        <v>525853</v>
       </c>
       <c r="R90" t="n">
-        <v>7178908</v>
+        <v>7178800</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -13173,7 +13171,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13183,7 +13181,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -13235,10 +13233,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119731907</v>
+        <v>119731868</v>
       </c>
       <c r="B91" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13251,31 +13249,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -13283,10 +13276,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525765</v>
+        <v>525802</v>
       </c>
       <c r="R91" t="n">
-        <v>7178799</v>
+        <v>7178930</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -13318,7 +13311,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13328,12 +13321,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -13342,6 +13335,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -13352,17 +13346,22 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13380,10 +13379,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119731853</v>
+        <v>119731899</v>
       </c>
       <c r="B92" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13392,35 +13391,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -13428,10 +13422,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525853</v>
+        <v>525724</v>
       </c>
       <c r="R92" t="n">
-        <v>7178800</v>
+        <v>7178884</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -13463,7 +13457,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13473,12 +13467,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande asp</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13487,6 +13481,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -13497,17 +13492,22 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1530,10 +1530,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119731948</v>
+        <v>119731965</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1546,31 +1546,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1578,10 +1573,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525970</v>
+        <v>525945</v>
       </c>
       <c r="R8" t="n">
-        <v>7178928</v>
+        <v>7178975</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1613,7 +1608,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1623,12 +1618,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1637,6 +1632,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1647,17 +1643,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1675,10 +1676,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119731965</v>
+        <v>119731964</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1691,21 +1692,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1718,10 +1719,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525945</v>
+        <v>525926</v>
       </c>
       <c r="R9" t="n">
-        <v>7178975</v>
+        <v>7178980</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1753,7 +1754,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1763,12 +1764,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1784,26 +1780,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1821,10 +1797,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731964</v>
+        <v>119731948</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1837,26 +1813,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1864,10 +1845,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525926</v>
+        <v>525970</v>
       </c>
       <c r="R10" t="n">
-        <v>7178980</v>
+        <v>7178928</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1899,7 +1880,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1909,7 +1890,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,13 +1904,27 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -5458,10 +5458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119731939</v>
+        <v>119731952</v>
       </c>
       <c r="B36" t="n">
-        <v>79608</v>
+        <v>79636</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5470,25 +5470,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525986</v>
+        <v>525970</v>
       </c>
       <c r="R36" t="n">
-        <v>7178882</v>
+        <v>7178943</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>på knäckt levande sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5604,10 +5604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119731952</v>
+        <v>119731953</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5616,25 +5616,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525970</v>
+        <v>525946</v>
       </c>
       <c r="R37" t="n">
-        <v>7178943</v>
+        <v>7178938</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5692,12 +5692,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5713,26 +5708,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5750,10 +5725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119731953</v>
+        <v>119731939</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5766,21 +5741,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5793,10 +5768,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525946</v>
+        <v>525986</v>
       </c>
       <c r="R38" t="n">
-        <v>7178938</v>
+        <v>7178882</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5828,7 +5803,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5838,7 +5813,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>på knäckt levande sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5854,6 +5834,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119731874</v>
+        <v>119731883</v>
       </c>
       <c r="B40" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6029,25 +6029,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525790</v>
+        <v>525725</v>
       </c>
       <c r="R40" t="n">
-        <v>7178955</v>
+        <v>7178979</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6289,10 +6289,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119731883</v>
+        <v>119731874</v>
       </c>
       <c r="B42" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6301,25 +6301,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525725</v>
+        <v>525790</v>
       </c>
       <c r="R42" t="n">
-        <v>7178979</v>
+        <v>7178955</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1530,10 +1530,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119731965</v>
+        <v>119731948</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1546,26 +1546,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525945</v>
+        <v>525970</v>
       </c>
       <c r="R8" t="n">
-        <v>7178975</v>
+        <v>7178928</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1608,7 +1613,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1618,12 +1623,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1632,7 +1637,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1643,22 +1647,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1676,10 +1675,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119731964</v>
+        <v>119731965</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1692,21 +1691,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1719,10 +1718,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525926</v>
+        <v>525945</v>
       </c>
       <c r="R9" t="n">
-        <v>7178980</v>
+        <v>7178975</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1754,7 +1753,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1764,7 +1763,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1780,6 +1784,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1797,10 +1821,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731948</v>
+        <v>119731964</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1813,31 +1837,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1845,10 +1864,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525970</v>
+        <v>525926</v>
       </c>
       <c r="R10" t="n">
-        <v>7178928</v>
+        <v>7178980</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1880,7 +1899,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1890,12 +1909,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1904,27 +1918,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119731928</v>
+        <v>119731933</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2391,25 +2391,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525916</v>
+        <v>525971</v>
       </c>
       <c r="R14" t="n">
-        <v>7178775</v>
+        <v>7178801</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2467,12 +2467,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2488,26 +2483,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2525,10 +2500,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119731933</v>
+        <v>119731928</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2537,25 +2512,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2568,10 +2543,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525971</v>
+        <v>525916</v>
       </c>
       <c r="R15" t="n">
-        <v>7178801</v>
+        <v>7178775</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2603,7 +2578,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2613,7 +2588,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2629,6 +2609,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119731950</v>
+        <v>119731925</v>
       </c>
       <c r="B22" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3464,30 +3464,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3495,10 +3500,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525969</v>
+        <v>525849</v>
       </c>
       <c r="R22" t="n">
-        <v>7178936</v>
+        <v>7178772</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3540,12 +3545,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på liggande död björkstam</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3554,33 +3559,27 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3598,10 +3597,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119731925</v>
+        <v>119731950</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3610,35 +3609,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3646,10 +3640,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525849</v>
+        <v>525969</v>
       </c>
       <c r="R23" t="n">
-        <v>7178772</v>
+        <v>7178936</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3681,7 +3675,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3691,12 +3685,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på liggande död björkstam</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3705,27 +3699,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119731883</v>
+        <v>119731874</v>
       </c>
       <c r="B40" t="n">
-        <v>79643</v>
+        <v>79608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6029,25 +6029,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525725</v>
+        <v>525790</v>
       </c>
       <c r="R40" t="n">
-        <v>7178979</v>
+        <v>7178955</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -6289,10 +6289,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119731874</v>
+        <v>119731883</v>
       </c>
       <c r="B42" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6301,25 +6301,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6332,10 +6332,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525790</v>
+        <v>525725</v>
       </c>
       <c r="R42" t="n">
-        <v>7178955</v>
+        <v>7178979</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -9286,10 +9286,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731876</v>
+        <v>119731838</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9298,35 +9298,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -9334,10 +9329,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525781</v>
+        <v>525933</v>
       </c>
       <c r="R63" t="n">
-        <v>7178998</v>
+        <v>7178937</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9369,7 +9364,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9379,12 +9374,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9393,6 +9388,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -9403,17 +9399,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9431,10 +9432,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731838</v>
+        <v>119731876</v>
       </c>
       <c r="B64" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9443,30 +9444,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -9474,10 +9480,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525933</v>
+        <v>525781</v>
       </c>
       <c r="R64" t="n">
-        <v>7178937</v>
+        <v>7178998</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9509,7 +9515,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9519,12 +9525,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9533,7 +9539,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -9544,22 +9549,17 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119731854</v>
+        <v>119731884</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525857</v>
+        <v>525725</v>
       </c>
       <c r="R79" t="n">
-        <v>7178804</v>
+        <v>7178979</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11616,6 +11616,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11633,7 +11653,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731884</v>
+        <v>119731855</v>
       </c>
       <c r="B80" t="n">
         <v>79608</v>
@@ -11676,10 +11696,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525725</v>
+        <v>525852</v>
       </c>
       <c r="R80" t="n">
-        <v>7178979</v>
+        <v>7178820</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11711,7 +11731,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11721,12 +11741,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11756,12 +11776,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11779,10 +11799,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731855</v>
+        <v>119731906</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>90558</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11795,21 +11815,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11822,10 +11842,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525852</v>
+        <v>525765</v>
       </c>
       <c r="R81" t="n">
-        <v>7178820</v>
+        <v>7178799</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11857,7 +11877,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11867,12 +11887,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11892,22 +11912,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11925,10 +11945,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731906</v>
+        <v>119731854</v>
       </c>
       <c r="B82" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11941,21 +11961,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11968,10 +11988,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525765</v>
+        <v>525857</v>
       </c>
       <c r="R82" t="n">
-        <v>7178799</v>
+        <v>7178804</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12003,7 +12023,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12013,12 +12033,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -12034,26 +12054,6 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -12508,10 +12508,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731901</v>
+        <v>119731868</v>
       </c>
       <c r="B86" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12524,31 +12524,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12556,10 +12551,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525747</v>
+        <v>525802</v>
       </c>
       <c r="R86" t="n">
-        <v>7178865</v>
+        <v>7178930</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12591,7 +12586,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12601,12 +12596,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12615,6 +12610,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -12625,17 +12621,22 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12653,7 +12654,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119731857</v>
+        <v>119731901</v>
       </c>
       <c r="B87" t="n">
         <v>57310</v>
@@ -12701,10 +12702,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525853</v>
+        <v>525747</v>
       </c>
       <c r="R87" t="n">
-        <v>7178853</v>
+        <v>7178865</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -12736,7 +12737,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12746,7 +12747,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -12798,7 +12799,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119731896</v>
+        <v>119731857</v>
       </c>
       <c r="B88" t="n">
         <v>57310</v>
@@ -12846,10 +12847,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525699</v>
+        <v>525853</v>
       </c>
       <c r="R88" t="n">
-        <v>7178908</v>
+        <v>7178853</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -12881,7 +12882,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12891,7 +12892,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -12943,7 +12944,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119731907</v>
+        <v>119731896</v>
       </c>
       <c r="B89" t="n">
         <v>57310</v>
@@ -12991,10 +12992,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525765</v>
+        <v>525699</v>
       </c>
       <c r="R89" t="n">
-        <v>7178799</v>
+        <v>7178908</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -13026,7 +13027,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13036,7 +13037,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13088,7 +13089,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119731853</v>
+        <v>119731907</v>
       </c>
       <c r="B90" t="n">
         <v>57310</v>
@@ -13136,10 +13137,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525853</v>
+        <v>525765</v>
       </c>
       <c r="R90" t="n">
-        <v>7178800</v>
+        <v>7178799</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -13171,7 +13172,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13181,7 +13182,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -13233,10 +13234,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119731868</v>
+        <v>119731853</v>
       </c>
       <c r="B91" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13249,26 +13250,31 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -13276,10 +13282,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525802</v>
+        <v>525853</v>
       </c>
       <c r="R91" t="n">
-        <v>7178930</v>
+        <v>7178800</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -13311,7 +13317,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13321,12 +13327,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -13335,7 +13341,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -13346,22 +13351,17 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1530,10 +1530,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119731948</v>
+        <v>119731965</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1546,31 +1546,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1578,10 +1573,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525970</v>
+        <v>525945</v>
       </c>
       <c r="R8" t="n">
-        <v>7178928</v>
+        <v>7178975</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1613,7 +1608,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1623,12 +1618,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1637,6 +1632,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1647,17 +1643,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1675,10 +1676,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119731965</v>
+        <v>119731964</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1691,21 +1692,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1718,10 +1719,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525945</v>
+        <v>525926</v>
       </c>
       <c r="R9" t="n">
-        <v>7178975</v>
+        <v>7178980</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1753,7 +1754,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1763,12 +1764,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1784,26 +1780,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1821,10 +1797,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731964</v>
+        <v>119731948</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1837,26 +1813,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1864,10 +1845,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525926</v>
+        <v>525970</v>
       </c>
       <c r="R10" t="n">
-        <v>7178980</v>
+        <v>7178928</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1899,7 +1880,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1909,7 +1890,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,13 +1904,27 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -3452,10 +3452,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119731925</v>
+        <v>119731950</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3464,35 +3464,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3500,10 +3495,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525849</v>
+        <v>525969</v>
       </c>
       <c r="R22" t="n">
-        <v>7178772</v>
+        <v>7178936</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3545,12 +3540,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på liggande död björkstam</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3559,27 +3554,33 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3597,10 +3598,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119731950</v>
+        <v>119731925</v>
       </c>
       <c r="B23" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3609,30 +3610,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3640,10 +3646,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525969</v>
+        <v>525849</v>
       </c>
       <c r="R23" t="n">
-        <v>7178936</v>
+        <v>7178772</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3675,7 +3681,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3685,12 +3691,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på liggande död björkstam</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3699,33 +3705,27 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119731930</v>
+        <v>119731921</v>
       </c>
       <c r="B28" t="n">
-        <v>79608</v>
+        <v>79643</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4337,25 +4337,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525916</v>
+        <v>525859</v>
       </c>
       <c r="R28" t="n">
-        <v>7178775</v>
+        <v>7178751</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4471,10 +4471,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119731921</v>
+        <v>119731942</v>
       </c>
       <c r="B29" t="n">
-        <v>79643</v>
+        <v>79636</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4487,21 +4487,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525859</v>
+        <v>525970</v>
       </c>
       <c r="R29" t="n">
-        <v>7178751</v>
+        <v>7178901</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4617,10 +4617,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119731942</v>
+        <v>119731945</v>
       </c>
       <c r="B30" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4629,41 +4629,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525970</v>
+        <v>525961</v>
       </c>
       <c r="R30" t="n">
-        <v>7178901</v>
+        <v>7178906</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4695,7 +4692,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4705,12 +4702,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4719,34 +4711,8 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4763,10 +4729,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119731945</v>
+        <v>119731930</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4779,34 +4745,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525961</v>
+        <v>525916</v>
       </c>
       <c r="R31" t="n">
-        <v>7178906</v>
+        <v>7178775</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4838,7 +4807,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4848,7 +4817,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4857,8 +4831,34 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -8165,10 +8165,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119731870</v>
+        <v>119731887</v>
       </c>
       <c r="B55" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8177,30 +8177,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -8208,10 +8213,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525790</v>
+        <v>525707</v>
       </c>
       <c r="R55" t="n">
-        <v>7178955</v>
+        <v>7178998</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -8243,7 +8248,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8253,12 +8258,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8267,7 +8272,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -8278,22 +8282,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8311,10 +8310,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119731887</v>
+        <v>119731870</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8323,35 +8322,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -8359,10 +8353,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525707</v>
+        <v>525790</v>
       </c>
       <c r="R56" t="n">
-        <v>7178998</v>
+        <v>7178955</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -8394,7 +8388,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8404,12 +8398,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8418,6 +8412,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -8428,17 +8423,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731838</v>
+        <v>119731876</v>
       </c>
       <c r="B63" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9298,30 +9298,35 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -9329,10 +9334,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525933</v>
+        <v>525781</v>
       </c>
       <c r="R63" t="n">
-        <v>7178937</v>
+        <v>7178998</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9364,7 +9369,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9374,12 +9379,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9388,7 +9393,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -9399,22 +9403,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9432,10 +9431,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731876</v>
+        <v>119731838</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9444,35 +9443,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -9480,10 +9474,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525781</v>
+        <v>525933</v>
       </c>
       <c r="R64" t="n">
-        <v>7178998</v>
+        <v>7178937</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9515,7 +9509,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9525,12 +9519,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9539,6 +9533,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -9549,17 +9544,22 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119731884</v>
+        <v>119731854</v>
       </c>
       <c r="B79" t="n">
-        <v>79608</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11523,21 +11523,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525725</v>
+        <v>525857</v>
       </c>
       <c r="R79" t="n">
-        <v>7178979</v>
+        <v>7178804</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11616,26 +11616,6 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11653,7 +11633,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731855</v>
+        <v>119731884</v>
       </c>
       <c r="B80" t="n">
         <v>79608</v>
@@ -11696,10 +11676,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525852</v>
+        <v>525725</v>
       </c>
       <c r="R80" t="n">
-        <v>7178820</v>
+        <v>7178979</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11731,7 +11711,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11741,12 +11721,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11776,12 +11756,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11799,10 +11779,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731906</v>
+        <v>119731855</v>
       </c>
       <c r="B81" t="n">
-        <v>90558</v>
+        <v>79608</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11815,21 +11795,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -11842,10 +11822,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525765</v>
+        <v>525852</v>
       </c>
       <c r="R81" t="n">
-        <v>7178799</v>
+        <v>7178820</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11877,7 +11857,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11887,12 +11867,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11912,22 +11892,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11945,10 +11925,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731854</v>
+        <v>119731906</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11961,21 +11941,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -11988,10 +11968,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525857</v>
+        <v>525765</v>
       </c>
       <c r="R82" t="n">
-        <v>7178804</v>
+        <v>7178799</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12023,7 +12003,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12033,12 +12013,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -12054,6 +12034,26 @@
       <c r="AH82" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -9577,10 +9577,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119731915</v>
+        <v>119731914</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>90558</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9593,21 +9593,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9620,10 +9620,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525820</v>
+        <v>525792</v>
       </c>
       <c r="R65" t="n">
-        <v>7178762</v>
+        <v>7178785</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9665,7 +9665,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9680,7 +9685,27 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9698,7 +9723,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731914</v>
+        <v>119731850</v>
       </c>
       <c r="B66" t="n">
         <v>90558</v>
@@ -9741,10 +9766,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525792</v>
+        <v>525907</v>
       </c>
       <c r="R66" t="n">
-        <v>7178785</v>
+        <v>7178822</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9776,7 +9801,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9786,12 +9811,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på gammal stubbe</t>
+          <t>på 2 stående döda granar</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9806,7 +9831,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -9844,10 +9869,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731850</v>
+        <v>119731915</v>
       </c>
       <c r="B67" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9860,21 +9885,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9887,10 +9912,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525907</v>
+        <v>525820</v>
       </c>
       <c r="R67" t="n">
-        <v>7178822</v>
+        <v>7178762</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9922,7 +9947,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9932,12 +9957,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>på 2 stående döda granar</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9952,27 +9972,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -11096,10 +11096,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119731840</v>
+        <v>119731890</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -11112,31 +11112,26 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -11144,10 +11139,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>525933</v>
+        <v>525658</v>
       </c>
       <c r="R76" t="n">
-        <v>7178939</v>
+        <v>7178997</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -11179,7 +11174,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11189,12 +11184,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:11</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -11203,27 +11193,13 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -11241,7 +11217,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119731875</v>
+        <v>119731840</v>
       </c>
       <c r="B77" t="n">
         <v>57310</v>
@@ -11289,10 +11265,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525792</v>
+        <v>525933</v>
       </c>
       <c r="R77" t="n">
-        <v>7178967</v>
+        <v>7178939</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -11324,7 +11300,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11334,7 +11310,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -11386,10 +11362,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119731890</v>
+        <v>119731875</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11402,26 +11378,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -11429,10 +11410,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525658</v>
+        <v>525792</v>
       </c>
       <c r="R78" t="n">
-        <v>7178997</v>
+        <v>7178967</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -11464,7 +11445,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11474,7 +11455,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11483,13 +11469,27 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -12508,10 +12508,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731868</v>
+        <v>119731901</v>
       </c>
       <c r="B86" t="n">
-        <v>79608</v>
+        <v>57310</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12524,26 +12524,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12551,10 +12556,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525802</v>
+        <v>525747</v>
       </c>
       <c r="R86" t="n">
-        <v>7178930</v>
+        <v>7178865</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12586,7 +12591,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12596,12 +12601,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12610,7 +12615,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -12621,22 +12625,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12654,7 +12653,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119731901</v>
+        <v>119731857</v>
       </c>
       <c r="B87" t="n">
         <v>57310</v>
@@ -12702,10 +12701,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525747</v>
+        <v>525853</v>
       </c>
       <c r="R87" t="n">
-        <v>7178865</v>
+        <v>7178853</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -12737,7 +12736,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12747,7 +12746,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -12799,7 +12798,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119731857</v>
+        <v>119731896</v>
       </c>
       <c r="B88" t="n">
         <v>57310</v>
@@ -12847,10 +12846,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525853</v>
+        <v>525699</v>
       </c>
       <c r="R88" t="n">
-        <v>7178853</v>
+        <v>7178908</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -12882,7 +12881,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12892,7 +12891,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -12944,7 +12943,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119731896</v>
+        <v>119731907</v>
       </c>
       <c r="B89" t="n">
         <v>57310</v>
@@ -12992,10 +12991,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525699</v>
+        <v>525765</v>
       </c>
       <c r="R89" t="n">
-        <v>7178908</v>
+        <v>7178799</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -13027,7 +13026,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13037,7 +13036,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -13089,7 +13088,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119731907</v>
+        <v>119731853</v>
       </c>
       <c r="B90" t="n">
         <v>57310</v>
@@ -13137,10 +13136,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525765</v>
+        <v>525853</v>
       </c>
       <c r="R90" t="n">
-        <v>7178799</v>
+        <v>7178800</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -13172,7 +13171,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13182,7 +13181,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -13234,10 +13233,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119731853</v>
+        <v>119731868</v>
       </c>
       <c r="B91" t="n">
-        <v>57310</v>
+        <v>79608</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13250,31 +13249,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -13282,10 +13276,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525853</v>
+        <v>525802</v>
       </c>
       <c r="R91" t="n">
-        <v>7178800</v>
+        <v>7178930</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -13317,7 +13311,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13327,12 +13321,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -13341,6 +13335,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -13351,17 +13346,22 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -1092,10 +1092,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119731946</v>
+        <v>119731944</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,21 +1108,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525974</v>
+        <v>525985</v>
       </c>
       <c r="R5" t="n">
-        <v>7178925</v>
+        <v>7178897</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,22 +1205,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119731922</v>
+        <v>119731962</v>
       </c>
       <c r="B6" t="n">
-        <v>79608</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,21 +1254,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525859</v>
+        <v>525906</v>
       </c>
       <c r="R6" t="n">
-        <v>7178751</v>
+        <v>7179007</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1346,27 +1346,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,10 +1384,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119731936</v>
+        <v>119731919</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1396,30 +1396,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1427,10 +1432,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525983</v>
+        <v>525842</v>
       </c>
       <c r="R7" t="n">
-        <v>7178824</v>
+        <v>7178749</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1462,7 +1467,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1472,12 +1477,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1486,33 +1491,27 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1530,10 +1529,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119731965</v>
+        <v>119731954</v>
       </c>
       <c r="B8" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1573,10 +1572,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525945</v>
+        <v>525946</v>
       </c>
       <c r="R8" t="n">
-        <v>7178975</v>
+        <v>7178956</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1608,7 +1607,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1618,7 +1617,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1676,10 +1675,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119731964</v>
+        <v>119731924</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1692,26 +1691,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1719,10 +1723,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525926</v>
+        <v>525862</v>
       </c>
       <c r="R9" t="n">
-        <v>7178980</v>
+        <v>7178759</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1754,7 +1758,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1764,7 +1768,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1773,13 +1782,27 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1797,10 +1820,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119731948</v>
+        <v>119731938</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1845,10 +1868,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525970</v>
+        <v>525979</v>
       </c>
       <c r="R10" t="n">
-        <v>7178928</v>
+        <v>7178844</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1880,7 +1903,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1890,7 +1913,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1942,10 +1965,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119731957</v>
+        <v>119731964</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1958,21 +1981,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1985,10 +2008,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525916</v>
+        <v>525926</v>
       </c>
       <c r="R11" t="n">
-        <v>7178975</v>
+        <v>7178980</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -2020,7 +2043,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2030,12 +2053,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2051,26 +2069,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2088,10 +2086,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119731966</v>
+        <v>119731953</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2104,31 +2102,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2136,10 +2129,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525966</v>
+        <v>525946</v>
       </c>
       <c r="R12" t="n">
-        <v>7178973</v>
+        <v>7178938</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2171,7 +2164,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2181,12 +2174,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2195,27 +2183,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2233,10 +2207,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119731940</v>
+        <v>119731946</v>
       </c>
       <c r="B13" t="n">
-        <v>79608</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2249,21 +2223,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2276,10 +2250,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525970</v>
+        <v>525974</v>
       </c>
       <c r="R13" t="n">
-        <v>7178901</v>
+        <v>7178925</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2311,7 +2285,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2321,12 +2295,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2346,22 +2320,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2379,10 +2353,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119731933</v>
+        <v>119731921</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>79659</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2391,25 +2365,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2422,10 +2396,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525971</v>
+        <v>525859</v>
       </c>
       <c r="R14" t="n">
-        <v>7178801</v>
+        <v>7178751</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2457,7 +2431,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2467,7 +2441,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2482,7 +2461,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2500,10 +2499,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119731928</v>
+        <v>119731926</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2512,25 +2511,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2543,10 +2542,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525916</v>
+        <v>525888</v>
       </c>
       <c r="R15" t="n">
-        <v>7178775</v>
+        <v>7178777</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2578,7 +2577,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2588,12 +2587,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2608,27 +2607,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2646,10 +2625,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119731969</v>
+        <v>119731943</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>79652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2658,25 +2637,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2689,10 +2668,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525973</v>
+        <v>525979</v>
       </c>
       <c r="R16" t="n">
-        <v>7178969</v>
+        <v>7178902</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2724,7 +2703,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2734,7 +2713,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2750,6 +2734,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2767,10 +2771,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119731932</v>
+        <v>119731948</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2783,26 +2787,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2810,10 +2819,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525935</v>
+        <v>525970</v>
       </c>
       <c r="R17" t="n">
-        <v>7178787</v>
+        <v>7178928</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2845,7 +2854,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2855,7 +2864,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2864,13 +2878,27 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2888,10 +2916,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119731926</v>
+        <v>119731966</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2904,26 +2932,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2931,10 +2964,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525888</v>
+        <v>525966</v>
       </c>
       <c r="R18" t="n">
-        <v>7178777</v>
+        <v>7178973</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2966,7 +2999,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2976,12 +3009,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2990,13 +3023,27 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3014,10 +3061,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119731962</v>
+        <v>119731930</v>
       </c>
       <c r="B19" t="n">
-        <v>90846</v>
+        <v>79624</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3030,21 +3077,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3057,10 +3104,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525906</v>
+        <v>525916</v>
       </c>
       <c r="R19" t="n">
-        <v>7179007</v>
+        <v>7178775</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3092,7 +3139,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3102,12 +3149,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3127,22 +3174,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3160,10 +3207,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119731954</v>
+        <v>119731922</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3203,10 +3250,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525946</v>
+        <v>525859</v>
       </c>
       <c r="R20" t="n">
-        <v>7178956</v>
+        <v>7178751</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3238,7 +3285,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3248,7 +3295,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3268,7 +3315,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3306,10 +3353,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119731956</v>
+        <v>119731969</v>
       </c>
       <c r="B21" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3322,21 +3369,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3349,10 +3396,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525939</v>
+        <v>525973</v>
       </c>
       <c r="R21" t="n">
-        <v>7178962</v>
+        <v>7178969</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3384,7 +3431,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3394,12 +3441,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3415,26 +3457,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3452,10 +3474,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119731950</v>
+        <v>119731935</v>
       </c>
       <c r="B22" t="n">
-        <v>79643</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3464,25 +3486,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3495,10 +3517,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525969</v>
+        <v>525983</v>
       </c>
       <c r="R22" t="n">
-        <v>7178936</v>
+        <v>7178824</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3530,7 +3552,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3540,12 +3562,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på liggande död björkstam</t>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3565,22 +3587,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3598,10 +3620,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119731925</v>
+        <v>119731920</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3614,31 +3636,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3646,10 +3663,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525849</v>
+        <v>525843</v>
       </c>
       <c r="R23" t="n">
-        <v>7178772</v>
+        <v>7178750</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3681,7 +3698,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3691,12 +3708,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3705,6 +3722,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3723,9 +3741,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3743,10 +3766,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119731924</v>
+        <v>119731927</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3759,31 +3782,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3791,10 +3809,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525862</v>
+        <v>525918</v>
       </c>
       <c r="R24" t="n">
-        <v>7178759</v>
+        <v>7178789</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3826,7 +3844,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3836,12 +3854,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3850,27 +3868,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3888,10 +3912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119731944</v>
+        <v>119731932</v>
       </c>
       <c r="B25" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3904,21 +3928,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3931,10 +3955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525985</v>
+        <v>525935</v>
       </c>
       <c r="R25" t="n">
-        <v>7178897</v>
+        <v>7178787</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3966,7 +3990,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3976,12 +4000,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3997,26 +4016,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4034,10 +4033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119731927</v>
+        <v>119731939</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4077,10 +4076,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525918</v>
+        <v>525986</v>
       </c>
       <c r="R26" t="n">
-        <v>7178789</v>
+        <v>7178882</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4112,7 +4111,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4122,12 +4121,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på knäckt levande sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4180,10 +4179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119731938</v>
+        <v>119731940</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4196,31 +4195,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4228,10 +4222,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525979</v>
+        <v>525970</v>
       </c>
       <c r="R27" t="n">
-        <v>7178844</v>
+        <v>7178901</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4263,7 +4257,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4273,12 +4267,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4287,6 +4281,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4297,17 +4292,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4325,10 +4325,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119731921</v>
+        <v>119731945</v>
       </c>
       <c r="B28" t="n">
-        <v>79643</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4337,41 +4337,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525859</v>
+        <v>525961</v>
       </c>
       <c r="R28" t="n">
-        <v>7178751</v>
+        <v>7178906</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4403,7 +4400,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4413,12 +4410,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4427,34 +4419,8 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4471,10 +4437,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119731942</v>
+        <v>119731950</v>
       </c>
       <c r="B29" t="n">
-        <v>79636</v>
+        <v>79659</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4487,21 +4453,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4514,10 +4480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525970</v>
+        <v>525969</v>
       </c>
       <c r="R29" t="n">
-        <v>7178901</v>
+        <v>7178936</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4549,7 +4515,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4559,12 +4525,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på liggande död björkstam</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4584,22 +4550,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Betula</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4617,10 +4583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119731945</v>
+        <v>119731942</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>79652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4629,38 +4595,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525961</v>
+        <v>525970</v>
       </c>
       <c r="R30" t="n">
-        <v>7178906</v>
+        <v>7178901</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4692,7 +4661,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4702,7 +4671,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4711,8 +4685,34 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4729,10 +4729,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119731930</v>
+        <v>119731933</v>
       </c>
       <c r="B31" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4745,21 +4745,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525916</v>
+        <v>525971</v>
       </c>
       <c r="R31" t="n">
-        <v>7178775</v>
+        <v>7178801</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4817,12 +4817,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4838,26 +4833,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4875,10 +4850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119731943</v>
+        <v>119731928</v>
       </c>
       <c r="B32" t="n">
-        <v>79636</v>
+        <v>79652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4918,10 +4893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525979</v>
+        <v>525916</v>
       </c>
       <c r="R32" t="n">
-        <v>7178902</v>
+        <v>7178775</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4953,7 +4928,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4963,7 +4938,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -5021,10 +4996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119731935</v>
+        <v>119731936</v>
       </c>
       <c r="B33" t="n">
-        <v>79608</v>
+        <v>79652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5033,25 +5008,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -5167,10 +5142,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119731919</v>
+        <v>119731965</v>
       </c>
       <c r="B34" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -5183,31 +5158,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5215,10 +5185,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525842</v>
+        <v>525945</v>
       </c>
       <c r="R34" t="n">
-        <v>7178749</v>
+        <v>7178975</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -5250,7 +5220,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5260,12 +5230,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5274,27 +5244,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5312,10 +5288,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119731920</v>
+        <v>119731957</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>79624</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5328,21 +5304,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -5355,10 +5331,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525843</v>
+        <v>525916</v>
       </c>
       <c r="R35" t="n">
-        <v>7178750</v>
+        <v>7178975</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5390,7 +5366,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5400,12 +5376,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5420,27 +5396,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5458,10 +5434,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119731952</v>
+        <v>119731956</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>79624</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5470,25 +5446,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5501,10 +5477,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525970</v>
+        <v>525939</v>
       </c>
       <c r="R36" t="n">
-        <v>7178943</v>
+        <v>7178962</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5536,7 +5512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5546,7 +5522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5604,10 +5580,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119731953</v>
+        <v>119731952</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>79652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5616,25 +5592,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5647,10 +5623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525946</v>
+        <v>525970</v>
       </c>
       <c r="R37" t="n">
-        <v>7178938</v>
+        <v>7178943</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5682,7 +5658,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5692,7 +5668,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5708,6 +5689,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5725,10 +5726,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119731939</v>
+        <v>119731925</v>
       </c>
       <c r="B38" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5741,26 +5742,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5768,10 +5774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525986</v>
+        <v>525849</v>
       </c>
       <c r="R38" t="n">
-        <v>7178882</v>
+        <v>7178772</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5803,7 +5809,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5813,12 +5819,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>på knäckt levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5827,33 +5833,27 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5871,10 +5871,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119731848</v>
+        <v>119731880</v>
       </c>
       <c r="B39" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5887,26 +5887,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5914,10 +5919,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525936</v>
+        <v>525751</v>
       </c>
       <c r="R39" t="n">
-        <v>7178808</v>
+        <v>7178999</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5949,7 +5954,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5959,12 +5964,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5973,33 +5978,27 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6020,7 +6019,7 @@
         <v>119731874</v>
       </c>
       <c r="B40" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6163,10 +6162,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119731893</v>
+        <v>119731891</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6179,21 +6178,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -6206,10 +6205,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525694</v>
+        <v>525653</v>
       </c>
       <c r="R41" t="n">
-        <v>7178950</v>
+        <v>7178999</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -6241,7 +6240,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6251,12 +6250,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på död högstubbe av sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6272,6 +6271,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6289,10 +6308,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119731883</v>
+        <v>119731898</v>
       </c>
       <c r="B42" t="n">
-        <v>79643</v>
+        <v>90576</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6301,25 +6320,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6332,10 +6351,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525725</v>
+        <v>525707</v>
       </c>
       <c r="R42" t="n">
-        <v>7178979</v>
+        <v>7178873</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6367,7 +6386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6377,12 +6396,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6402,22 +6421,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6435,10 +6454,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119731898</v>
+        <v>119731904</v>
       </c>
       <c r="B43" t="n">
-        <v>90558</v>
+        <v>79659</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6447,25 +6466,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -6478,10 +6497,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525707</v>
+        <v>525762</v>
       </c>
       <c r="R43" t="n">
-        <v>7178873</v>
+        <v>7178853</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6513,7 +6532,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6523,12 +6542,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6548,22 +6567,22 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6581,10 +6600,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119731842</v>
+        <v>119731916</v>
       </c>
       <c r="B44" t="n">
-        <v>79608</v>
+        <v>79659</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6593,25 +6612,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6624,10 +6643,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525950</v>
+        <v>525842</v>
       </c>
       <c r="R44" t="n">
-        <v>7178893</v>
+        <v>7178769</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6659,7 +6678,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6669,7 +6688,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6689,7 +6708,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6727,10 +6746,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119731885</v>
+        <v>119731918</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6743,31 +6762,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6775,10 +6789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525697</v>
+        <v>525837</v>
       </c>
       <c r="R45" t="n">
-        <v>7179006</v>
+        <v>7178762</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6810,7 +6824,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6820,12 +6834,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6834,27 +6843,13 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6872,10 +6867,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119731843</v>
+        <v>119731851</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6920,10 +6915,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525949</v>
+        <v>525862</v>
       </c>
       <c r="R46" t="n">
-        <v>7178888</v>
+        <v>7178784</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6955,7 +6950,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6965,7 +6960,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7017,10 +7012,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119731881</v>
+        <v>119731896</v>
       </c>
       <c r="B47" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7033,26 +7028,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -7060,10 +7060,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525738</v>
+        <v>525699</v>
       </c>
       <c r="R47" t="n">
-        <v>7178966</v>
+        <v>7178908</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7119,7 +7119,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -7130,22 +7129,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7163,10 +7157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119731897</v>
+        <v>119731899</v>
       </c>
       <c r="B48" t="n">
-        <v>79608</v>
+        <v>79659</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7175,25 +7169,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -7206,10 +7200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525705</v>
+        <v>525724</v>
       </c>
       <c r="R48" t="n">
-        <v>7178875</v>
+        <v>7178884</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -7241,7 +7235,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7251,12 +7245,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på levande asp</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7276,12 +7270,12 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -7291,7 +7285,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7309,10 +7303,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119731889</v>
+        <v>119731890</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7352,10 +7346,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525688</v>
+        <v>525658</v>
       </c>
       <c r="R49" t="n">
-        <v>7179014</v>
+        <v>7178997</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7387,7 +7381,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7397,12 +7391,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7435,10 +7424,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119731905</v>
+        <v>119731915</v>
       </c>
       <c r="B50" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7451,21 +7440,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7478,10 +7467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525762</v>
+        <v>525820</v>
       </c>
       <c r="R50" t="n">
-        <v>7178853</v>
+        <v>7178762</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7513,7 +7502,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7523,12 +7512,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7543,27 +7527,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7581,10 +7545,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119731888</v>
+        <v>119731858</v>
       </c>
       <c r="B51" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7624,10 +7588,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525689</v>
+        <v>525845</v>
       </c>
       <c r="R51" t="n">
-        <v>7179025</v>
+        <v>7178853</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7659,7 +7623,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7669,7 +7633,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7727,10 +7691,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119731917</v>
+        <v>119731855</v>
       </c>
       <c r="B52" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7770,10 +7734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525842</v>
+        <v>525852</v>
       </c>
       <c r="R52" t="n">
-        <v>7178769</v>
+        <v>7178820</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7805,7 +7769,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7815,12 +7779,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7835,7 +7799,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7850,12 +7814,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7873,10 +7837,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119731856</v>
+        <v>119731912</v>
       </c>
       <c r="B53" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7889,26 +7853,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7916,10 +7885,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525854</v>
+        <v>525763</v>
       </c>
       <c r="R53" t="n">
-        <v>7178867</v>
+        <v>7178776</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7951,7 +7920,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7961,12 +7930,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7975,7 +7944,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7986,22 +7954,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8019,10 +7982,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119731863</v>
+        <v>119731917</v>
       </c>
       <c r="B54" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -8062,10 +8025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525807</v>
+        <v>525842</v>
       </c>
       <c r="R54" t="n">
-        <v>7178896</v>
+        <v>7178769</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -8097,7 +8060,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8107,7 +8070,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -8127,7 +8090,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -8165,10 +8128,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119731887</v>
+        <v>119731856</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -8181,31 +8144,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -8213,10 +8171,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525707</v>
+        <v>525854</v>
       </c>
       <c r="R55" t="n">
-        <v>7178998</v>
+        <v>7178867</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -8248,7 +8206,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8258,12 +8216,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8272,6 +8230,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -8282,17 +8241,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8310,10 +8274,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119731870</v>
+        <v>119731866</v>
       </c>
       <c r="B56" t="n">
-        <v>79643</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8322,25 +8286,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8353,10 +8317,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525790</v>
+        <v>525806</v>
       </c>
       <c r="R56" t="n">
-        <v>7178955</v>
+        <v>7178927</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -8388,7 +8352,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8398,12 +8362,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:11</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8419,26 +8378,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8456,10 +8395,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119731858</v>
+        <v>119731914</v>
       </c>
       <c r="B57" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8472,21 +8411,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8499,10 +8438,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525845</v>
+        <v>525792</v>
       </c>
       <c r="R57" t="n">
-        <v>7178853</v>
+        <v>7178785</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -8534,7 +8473,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8544,12 +8483,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8569,22 +8508,22 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8602,10 +8541,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119731865</v>
+        <v>119731900</v>
       </c>
       <c r="B58" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8618,37 +8557,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525818</v>
+        <v>525738</v>
       </c>
       <c r="R58" t="n">
-        <v>7178903</v>
+        <v>7178870</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8680,7 +8616,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8690,12 +8626,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8704,34 +8635,8 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -8748,10 +8653,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119731882</v>
+        <v>119731883</v>
       </c>
       <c r="B59" t="n">
-        <v>90558</v>
+        <v>79659</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8760,25 +8665,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8791,10 +8696,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525731</v>
+        <v>525725</v>
       </c>
       <c r="R59" t="n">
-        <v>7178963</v>
+        <v>7178979</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8826,7 +8731,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8836,12 +8741,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8861,22 +8766,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8894,10 +8799,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119731895</v>
+        <v>119731903</v>
       </c>
       <c r="B60" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8910,21 +8815,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8937,10 +8842,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525699</v>
+        <v>525774</v>
       </c>
       <c r="R60" t="n">
-        <v>7178908</v>
+        <v>7178852</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8972,7 +8877,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8982,12 +8887,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -9003,6 +8908,26 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -9020,10 +8945,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119731866</v>
+        <v>119731854</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -9063,10 +8988,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525806</v>
+        <v>525857</v>
       </c>
       <c r="R61" t="n">
-        <v>7178927</v>
+        <v>7178804</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -9098,7 +9023,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9108,7 +9033,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9141,10 +9071,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119731860</v>
+        <v>119731913</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9157,31 +9087,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -9189,10 +9114,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525848</v>
+        <v>525778</v>
       </c>
       <c r="R62" t="n">
-        <v>7178857</v>
+        <v>7178782</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -9224,7 +9149,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9234,12 +9159,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9248,27 +9168,13 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9286,10 +9192,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731876</v>
+        <v>119731875</v>
       </c>
       <c r="B63" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9334,10 +9240,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525781</v>
+        <v>525792</v>
       </c>
       <c r="R63" t="n">
-        <v>7178998</v>
+        <v>7178967</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9369,7 +9275,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9379,7 +9285,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9431,10 +9337,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731838</v>
+        <v>119731884</v>
       </c>
       <c r="B64" t="n">
-        <v>79636</v>
+        <v>79624</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9443,25 +9349,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -9474,10 +9380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525933</v>
+        <v>525725</v>
       </c>
       <c r="R64" t="n">
-        <v>7178937</v>
+        <v>7178979</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9509,7 +9415,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9519,7 +9425,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9577,10 +9483,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119731914</v>
+        <v>119731888</v>
       </c>
       <c r="B65" t="n">
-        <v>90558</v>
+        <v>79624</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9593,21 +9499,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -9620,10 +9526,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525792</v>
+        <v>525689</v>
       </c>
       <c r="R65" t="n">
-        <v>7178785</v>
+        <v>7179025</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9655,7 +9561,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9665,12 +9571,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>på gammal stubbe</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9690,22 +9596,22 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9723,10 +9629,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731850</v>
+        <v>119731902</v>
       </c>
       <c r="B66" t="n">
-        <v>90558</v>
+        <v>79624</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9739,21 +9645,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9766,10 +9672,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525907</v>
+        <v>525769</v>
       </c>
       <c r="R66" t="n">
-        <v>7178822</v>
+        <v>7178869</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9801,7 +9707,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9811,12 +9717,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på 2 stående döda granar</t>
+          <t>på levande liggande sälg</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9831,27 +9737,27 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9869,10 +9775,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731915</v>
+        <v>119731882</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>90576</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9885,21 +9791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9912,10 +9818,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525820</v>
+        <v>525731</v>
       </c>
       <c r="R67" t="n">
-        <v>7178762</v>
+        <v>7178963</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9947,7 +9853,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9957,7 +9863,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9972,7 +9883,27 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9990,10 +9921,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119731880</v>
+        <v>119731838</v>
       </c>
       <c r="B68" t="n">
-        <v>57310</v>
+        <v>79652</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -10002,35 +9933,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -10038,10 +9964,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525751</v>
+        <v>525933</v>
       </c>
       <c r="R68" t="n">
-        <v>7178999</v>
+        <v>7178937</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -10073,7 +9999,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10083,12 +10009,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -10097,6 +10023,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -10107,17 +10034,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -10135,10 +10067,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119731910</v>
+        <v>119731863</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -10151,31 +10083,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -10183,10 +10110,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525767</v>
+        <v>525807</v>
       </c>
       <c r="R69" t="n">
-        <v>7178808</v>
+        <v>7178896</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -10218,7 +10145,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10228,12 +10155,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10242,6 +10169,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -10252,17 +10180,22 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -10280,10 +10213,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119731841</v>
+        <v>119731868</v>
       </c>
       <c r="B70" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -10296,31 +10229,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -10328,10 +10256,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525940</v>
+        <v>525802</v>
       </c>
       <c r="R70" t="n">
-        <v>7178908</v>
+        <v>7178930</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10363,7 +10291,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10373,12 +10301,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -10387,6 +10315,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -10397,17 +10326,22 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -10425,10 +10359,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119731916</v>
+        <v>119731848</v>
       </c>
       <c r="B71" t="n">
-        <v>79643</v>
+        <v>79624</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10437,25 +10371,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10468,10 +10402,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525842</v>
+        <v>525936</v>
       </c>
       <c r="R71" t="n">
-        <v>7178769</v>
+        <v>7178808</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10503,7 +10437,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10513,7 +10447,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10533,7 +10467,7 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -10571,10 +10505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119731867</v>
+        <v>119731850</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>90576</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10587,21 +10521,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10614,10 +10548,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>525802</v>
+        <v>525907</v>
       </c>
       <c r="R72" t="n">
-        <v>7178930</v>
+        <v>7178822</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -10649,7 +10583,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10659,12 +10593,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på 2 stående döda granar</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10679,27 +10613,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10717,10 +10651,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119731900</v>
+        <v>119731839</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10733,34 +10667,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525738</v>
+        <v>525933</v>
       </c>
       <c r="R73" t="n">
-        <v>7178870</v>
+        <v>7178937</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -10792,7 +10729,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10802,7 +10739,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10811,8 +10753,34 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -10829,10 +10797,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119731913</v>
+        <v>119731897</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>79624</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10845,21 +10813,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -10872,10 +10840,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>525778</v>
+        <v>525705</v>
       </c>
       <c r="R74" t="n">
-        <v>7178782</v>
+        <v>7178875</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -10907,7 +10875,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10917,7 +10885,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10933,6 +10906,26 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10950,10 +10943,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119731903</v>
+        <v>119731840</v>
       </c>
       <c r="B75" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10966,26 +10959,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -10993,10 +10991,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>525774</v>
+        <v>525933</v>
       </c>
       <c r="R75" t="n">
-        <v>7178852</v>
+        <v>7178939</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -11028,7 +11026,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11038,12 +11036,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -11052,7 +11050,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -11063,22 +11060,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -11096,10 +11088,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119731890</v>
+        <v>119731887</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -11112,26 +11104,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -11139,10 +11136,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>525658</v>
+        <v>525707</v>
       </c>
       <c r="R76" t="n">
-        <v>7178997</v>
+        <v>7178998</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -11174,7 +11171,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11184,7 +11181,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -11193,13 +11195,27 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -11217,10 +11233,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119731840</v>
+        <v>119731907</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -11265,10 +11281,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525933</v>
+        <v>525765</v>
       </c>
       <c r="R77" t="n">
-        <v>7178939</v>
+        <v>7178799</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -11300,7 +11316,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11310,7 +11326,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
@@ -11362,10 +11378,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119731875</v>
+        <v>119731865</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11378,31 +11394,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -11410,10 +11421,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525792</v>
+        <v>525818</v>
       </c>
       <c r="R78" t="n">
-        <v>7178967</v>
+        <v>7178903</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -11445,7 +11456,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11455,12 +11466,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11469,6 +11480,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -11479,17 +11491,22 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11507,10 +11524,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119731854</v>
+        <v>119731867</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11523,21 +11540,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11550,10 +11567,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525857</v>
+        <v>525802</v>
       </c>
       <c r="R79" t="n">
-        <v>7178804</v>
+        <v>7178930</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -11585,7 +11602,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11595,12 +11612,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11616,6 +11633,26 @@
       <c r="AH79" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11633,10 +11670,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731884</v>
+        <v>119731861</v>
       </c>
       <c r="B80" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11676,10 +11713,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525725</v>
+        <v>525826</v>
       </c>
       <c r="R80" t="n">
-        <v>7178979</v>
+        <v>7178869</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11711,7 +11748,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11721,7 +11758,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
@@ -11779,10 +11816,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731855</v>
+        <v>119731876</v>
       </c>
       <c r="B81" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11795,26 +11832,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11822,10 +11864,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525852</v>
+        <v>525781</v>
       </c>
       <c r="R81" t="n">
-        <v>7178820</v>
+        <v>7178998</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11857,7 +11899,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11867,12 +11909,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11881,7 +11923,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11892,22 +11933,17 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11925,10 +11961,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731906</v>
+        <v>119731843</v>
       </c>
       <c r="B82" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -11941,26 +11977,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -11968,10 +12009,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525765</v>
+        <v>525949</v>
       </c>
       <c r="R82" t="n">
-        <v>7178799</v>
+        <v>7178888</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12003,7 +12044,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12013,12 +12054,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -12027,7 +12068,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -12046,14 +12086,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -12071,10 +12106,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119731904</v>
+        <v>119731857</v>
       </c>
       <c r="B83" t="n">
-        <v>79643</v>
+        <v>57320</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12083,30 +12118,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -12114,7 +12154,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525762</v>
+        <v>525853</v>
       </c>
       <c r="R83" t="n">
         <v>7178853</v>
@@ -12149,7 +12189,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12159,12 +12199,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -12173,7 +12213,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -12184,22 +12223,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12217,10 +12251,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119731839</v>
+        <v>119731906</v>
       </c>
       <c r="B84" t="n">
-        <v>79608</v>
+        <v>90576</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12233,21 +12267,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -12260,10 +12294,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525933</v>
+        <v>525765</v>
       </c>
       <c r="R84" t="n">
-        <v>7178937</v>
+        <v>7178799</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -12295,7 +12329,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12305,12 +12339,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12330,22 +12364,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -12363,10 +12397,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119731912</v>
+        <v>119731870</v>
       </c>
       <c r="B85" t="n">
-        <v>57310</v>
+        <v>79659</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12375,35 +12409,30 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -12411,10 +12440,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525763</v>
+        <v>525790</v>
       </c>
       <c r="R85" t="n">
-        <v>7178776</v>
+        <v>7178955</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -12446,7 +12475,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12456,12 +12485,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12470,6 +12499,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -12480,17 +12510,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12508,10 +12543,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731901</v>
+        <v>119731910</v>
       </c>
       <c r="B86" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12556,10 +12591,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525747</v>
+        <v>525767</v>
       </c>
       <c r="R86" t="n">
-        <v>7178865</v>
+        <v>7178808</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12591,7 +12626,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12601,7 +12636,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -12653,10 +12688,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119731857</v>
+        <v>119731895</v>
       </c>
       <c r="B87" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12669,31 +12704,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -12701,10 +12731,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525853</v>
+        <v>525699</v>
       </c>
       <c r="R87" t="n">
-        <v>7178853</v>
+        <v>7178908</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -12736,7 +12766,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12746,12 +12776,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12760,27 +12790,13 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12798,10 +12814,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119731896</v>
+        <v>119731901</v>
       </c>
       <c r="B88" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12846,10 +12862,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525699</v>
+        <v>525747</v>
       </c>
       <c r="R88" t="n">
-        <v>7178908</v>
+        <v>7178865</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -12881,7 +12897,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12891,7 +12907,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -12943,10 +12959,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119731907</v>
+        <v>119731860</v>
       </c>
       <c r="B89" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12981,7 +12997,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -12991,10 +13007,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525765</v>
+        <v>525848</v>
       </c>
       <c r="R89" t="n">
-        <v>7178799</v>
+        <v>7178857</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -13026,7 +13042,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13036,12 +13052,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -13088,10 +13104,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119731853</v>
+        <v>119731905</v>
       </c>
       <c r="B90" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -13104,31 +13120,26 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -13136,10 +13147,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525853</v>
+        <v>525762</v>
       </c>
       <c r="R90" t="n">
-        <v>7178800</v>
+        <v>7178853</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -13171,7 +13182,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13181,12 +13192,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -13195,6 +13206,7 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -13213,9 +13225,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -13233,10 +13250,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119731868</v>
+        <v>119731842</v>
       </c>
       <c r="B91" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -13276,10 +13293,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525802</v>
+        <v>525950</v>
       </c>
       <c r="R91" t="n">
-        <v>7178930</v>
+        <v>7178893</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -13311,7 +13328,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13321,7 +13338,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -13379,10 +13396,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119731899</v>
+        <v>119731853</v>
       </c>
       <c r="B92" t="n">
-        <v>79643</v>
+        <v>57320</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13391,30 +13408,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -13422,10 +13444,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525724</v>
+        <v>525853</v>
       </c>
       <c r="R92" t="n">
-        <v>7178884</v>
+        <v>7178800</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -13457,7 +13479,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13467,12 +13489,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>på levande asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13481,7 +13503,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -13492,22 +13513,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -13525,10 +13541,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119731851</v>
+        <v>119731881</v>
       </c>
       <c r="B93" t="n">
-        <v>57310</v>
+        <v>79624</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13541,31 +13557,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -13573,10 +13584,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>525862</v>
+        <v>525738</v>
       </c>
       <c r="R93" t="n">
-        <v>7178784</v>
+        <v>7178966</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -13608,7 +13619,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13618,12 +13629,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13632,6 +13643,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -13642,17 +13654,22 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -13670,10 +13687,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119731918</v>
+        <v>119731889</v>
       </c>
       <c r="B94" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13713,10 +13730,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>525837</v>
+        <v>525688</v>
       </c>
       <c r="R94" t="n">
-        <v>7178762</v>
+        <v>7179014</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -13748,7 +13765,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13758,7 +13775,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13773,7 +13795,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -13791,10 +13813,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119731891</v>
+        <v>119731893</v>
       </c>
       <c r="B95" t="n">
-        <v>79608</v>
+        <v>78542</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13807,21 +13829,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -13834,10 +13856,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>525653</v>
+        <v>525694</v>
       </c>
       <c r="R95" t="n">
-        <v>7178999</v>
+        <v>7178950</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -13869,7 +13891,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13879,12 +13901,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>på död högstubbe av sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13900,26 +13922,6 @@
       <c r="AH95" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13937,10 +13939,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119731861</v>
+        <v>119731885</v>
       </c>
       <c r="B96" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -13953,26 +13955,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -13980,10 +13987,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>525826</v>
+        <v>525697</v>
       </c>
       <c r="R96" t="n">
-        <v>7178869</v>
+        <v>7179006</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -14015,7 +14022,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14025,12 +14032,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -14039,7 +14046,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -14050,22 +14056,17 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -14083,10 +14084,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119731902</v>
+        <v>119731841</v>
       </c>
       <c r="B97" t="n">
-        <v>79608</v>
+        <v>57320</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -14099,26 +14100,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -14126,10 +14132,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>525769</v>
+        <v>525940</v>
       </c>
       <c r="R97" t="n">
-        <v>7178869</v>
+        <v>7178908</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -14161,7 +14167,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -14171,12 +14177,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>på levande liggande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -14185,7 +14191,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -14196,22 +14201,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -14229,10 +14229,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119894773</v>
+        <v>119894748</v>
       </c>
       <c r="B98" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>på gran stubbe</t>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -14375,10 +14375,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119894748</v>
+        <v>119894773</v>
       </c>
       <c r="B99" t="n">
-        <v>90562</v>
+        <v>90576</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -14391,21 +14391,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>på granlåga med bark</t>
+          <t>på gran stubbe</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -14498,12 +14498,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -6867,10 +6867,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119731851</v>
+        <v>119731899</v>
       </c>
       <c r="B46" t="n">
-        <v>57320</v>
+        <v>79659</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6879,35 +6879,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6915,10 +6910,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525862</v>
+        <v>525724</v>
       </c>
       <c r="R46" t="n">
-        <v>7178784</v>
+        <v>7178884</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6950,7 +6945,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6960,12 +6955,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande asp</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6974,6 +6969,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6984,17 +6980,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7012,7 +7013,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119731896</v>
+        <v>119731851</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -7060,10 +7061,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525699</v>
+        <v>525862</v>
       </c>
       <c r="R47" t="n">
-        <v>7178908</v>
+        <v>7178784</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -7095,7 +7096,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7105,7 +7106,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7157,10 +7158,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119731899</v>
+        <v>119731896</v>
       </c>
       <c r="B48" t="n">
-        <v>79659</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7169,30 +7170,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -7200,10 +7206,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525724</v>
+        <v>525699</v>
       </c>
       <c r="R48" t="n">
-        <v>7178884</v>
+        <v>7178908</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -7235,7 +7241,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7245,12 +7251,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>på levande asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7259,7 +7265,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -7270,22 +7275,17 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7303,7 +7303,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119731890</v>
+        <v>119731915</v>
       </c>
       <c r="B49" t="n">
         <v>78542</v>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525658</v>
+        <v>525820</v>
       </c>
       <c r="R49" t="n">
-        <v>7178997</v>
+        <v>7178762</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7424,10 +7424,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119731915</v>
+        <v>119731858</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7440,21 +7440,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525820</v>
+        <v>525845</v>
       </c>
       <c r="R50" t="n">
-        <v>7178762</v>
+        <v>7178853</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7512,7 +7512,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7527,7 +7532,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7545,7 +7570,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119731858</v>
+        <v>119731855</v>
       </c>
       <c r="B51" t="n">
         <v>79624</v>
@@ -7588,10 +7613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525845</v>
+        <v>525852</v>
       </c>
       <c r="R51" t="n">
-        <v>7178853</v>
+        <v>7178820</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7623,7 +7648,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7633,12 +7658,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7668,12 +7693,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7691,10 +7716,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119731855</v>
+        <v>119731890</v>
       </c>
       <c r="B52" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7707,21 +7732,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7734,10 +7759,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525852</v>
+        <v>525658</v>
       </c>
       <c r="R52" t="n">
-        <v>7178820</v>
+        <v>7178997</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7769,7 +7794,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7779,12 +7804,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>på död sälg</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7800,26 +7820,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7982,10 +7982,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119731917</v>
+        <v>119731866</v>
       </c>
       <c r="B54" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7998,21 +7998,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -8025,10 +8025,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525842</v>
+        <v>525806</v>
       </c>
       <c r="R54" t="n">
-        <v>7178769</v>
+        <v>7178927</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8070,12 +8070,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8090,27 +8085,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8128,7 +8103,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119731856</v>
+        <v>119731917</v>
       </c>
       <c r="B55" t="n">
         <v>79624</v>
@@ -8171,10 +8146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525854</v>
+        <v>525842</v>
       </c>
       <c r="R55" t="n">
-        <v>7178867</v>
+        <v>7178769</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -8206,7 +8181,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8216,7 +8191,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8236,7 +8211,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -8274,10 +8249,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119731866</v>
+        <v>119731856</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8290,21 +8265,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8317,10 +8292,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525806</v>
+        <v>525854</v>
       </c>
       <c r="R56" t="n">
-        <v>7178927</v>
+        <v>7178867</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -8352,7 +8327,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8362,7 +8337,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8378,6 +8358,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -13396,10 +13396,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119731853</v>
+        <v>119731881</v>
       </c>
       <c r="B92" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13412,31 +13412,26 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -13444,10 +13439,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525853</v>
+        <v>525738</v>
       </c>
       <c r="R92" t="n">
-        <v>7178800</v>
+        <v>7178966</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -13479,7 +13474,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13489,12 +13484,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13503,6 +13498,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -13513,17 +13509,22 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -13541,10 +13542,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119731881</v>
+        <v>119731853</v>
       </c>
       <c r="B93" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13557,26 +13558,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -13584,10 +13590,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>525738</v>
+        <v>525853</v>
       </c>
       <c r="R93" t="n">
-        <v>7178966</v>
+        <v>7178800</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -13619,7 +13625,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13629,12 +13635,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13643,7 +13649,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -13654,22 +13659,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -14229,10 +14229,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119894748</v>
+        <v>119894773</v>
       </c>
       <c r="B98" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>på granlåga med bark</t>
+          <t>på gran stubbe</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -14375,10 +14375,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119894773</v>
+        <v>119894748</v>
       </c>
       <c r="B99" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -14391,21 +14391,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>på gran stubbe</t>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -14498,12 +14498,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>

--- a/artfynd/A 31476-2024 artfynd.xlsx
+++ b/artfynd/A 31476-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AY98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2207,10 +2207,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119731946</v>
+        <v>119731921</v>
       </c>
       <c r="B13" t="n">
-        <v>90598</v>
+        <v>79659</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2219,25 +2219,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525974</v>
+        <v>525859</v>
       </c>
       <c r="R13" t="n">
-        <v>7178925</v>
+        <v>7178751</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på granlåga</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2315,27 +2315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119731921</v>
+        <v>119731926</v>
       </c>
       <c r="B14" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2365,25 +2365,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2396,10 +2396,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525859</v>
+        <v>525888</v>
       </c>
       <c r="R14" t="n">
-        <v>7178751</v>
+        <v>7178777</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2462,26 +2462,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2499,10 +2479,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119731926</v>
+        <v>119731943</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2511,25 +2491,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2542,10 +2522,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>525888</v>
+        <v>525979</v>
       </c>
       <c r="R15" t="n">
-        <v>7178777</v>
+        <v>7178902</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2577,7 +2557,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2587,12 +2567,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2607,7 +2587,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2625,10 +2625,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119731943</v>
+        <v>119731948</v>
       </c>
       <c r="B16" t="n">
-        <v>79652</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2637,30 +2637,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2668,10 +2673,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525979</v>
+        <v>525970</v>
       </c>
       <c r="R16" t="n">
-        <v>7178902</v>
+        <v>7178928</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2703,7 +2708,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2713,12 +2718,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2727,7 +2732,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2738,22 +2742,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2771,7 +2770,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119731948</v>
+        <v>119731966</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2809,7 +2808,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2819,10 +2818,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525970</v>
+        <v>525966</v>
       </c>
       <c r="R17" t="n">
-        <v>7178928</v>
+        <v>7178973</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2854,7 +2853,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2864,12 +2863,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2916,10 +2915,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119731966</v>
+        <v>119731930</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2932,31 +2931,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2964,10 +2958,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525966</v>
+        <v>525916</v>
       </c>
       <c r="R18" t="n">
-        <v>7178973</v>
+        <v>7178775</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2999,7 +2993,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3009,12 +3003,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3023,6 +3017,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -3033,17 +3028,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119731930</v>
+        <v>119731922</v>
       </c>
       <c r="B19" t="n">
         <v>79624</v>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525916</v>
+        <v>525859</v>
       </c>
       <c r="R19" t="n">
-        <v>7178775</v>
+        <v>7178751</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3207,10 +3207,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119731922</v>
+        <v>119731969</v>
       </c>
       <c r="B20" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3223,21 +3223,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525859</v>
+        <v>525973</v>
       </c>
       <c r="R20" t="n">
-        <v>7178751</v>
+        <v>7178969</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3295,12 +3295,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,27 +3310,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3353,10 +3328,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119731969</v>
+        <v>119731935</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3369,21 +3344,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3396,10 +3371,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525973</v>
+        <v>525983</v>
       </c>
       <c r="R21" t="n">
-        <v>7178969</v>
+        <v>7178824</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3431,7 +3406,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3441,7 +3416,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3457,6 +3437,26 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119731935</v>
+        <v>119731920</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3490,21 +3490,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525983</v>
+        <v>525843</v>
       </c>
       <c r="R22" t="n">
-        <v>7178824</v>
+        <v>7178750</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>på stubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3582,27 +3582,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119731920</v>
+        <v>119731927</v>
       </c>
       <c r="B23" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525843</v>
+        <v>525918</v>
       </c>
       <c r="R23" t="n">
-        <v>7178750</v>
+        <v>7178789</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>på stubbe</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3728,27 +3728,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119731927</v>
+        <v>119731932</v>
       </c>
       <c r="B24" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3782,21 +3782,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525918</v>
+        <v>525935</v>
       </c>
       <c r="R24" t="n">
-        <v>7178789</v>
+        <v>7178787</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3854,12 +3854,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3875,26 +3870,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3912,10 +3887,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119731932</v>
+        <v>119731939</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3928,21 +3903,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3955,10 +3930,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525935</v>
+        <v>525986</v>
       </c>
       <c r="R25" t="n">
-        <v>7178787</v>
+        <v>7178882</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3990,7 +3965,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4000,7 +3975,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>på knäckt levande sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4016,6 +3996,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119731939</v>
+        <v>119731940</v>
       </c>
       <c r="B26" t="n">
         <v>79624</v>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>525986</v>
+        <v>525970</v>
       </c>
       <c r="R26" t="n">
-        <v>7178882</v>
+        <v>7178901</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>på knäckt levande sälg</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4179,10 +4179,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119731940</v>
+        <v>119731945</v>
       </c>
       <c r="B27" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4195,37 +4195,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525970</v>
+        <v>525961</v>
       </c>
       <c r="R27" t="n">
-        <v>7178901</v>
+        <v>7178906</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -4257,7 +4254,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4267,12 +4264,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4281,34 +4273,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -4325,10 +4291,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119731945</v>
+        <v>119731950</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4337,38 +4303,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525961</v>
+        <v>525969</v>
       </c>
       <c r="R28" t="n">
-        <v>7178906</v>
+        <v>7178936</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -4400,7 +4369,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4410,7 +4379,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>på liggande död björkstam</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4419,8 +4393,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Betula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4437,10 +4437,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119731950</v>
+        <v>119731942</v>
       </c>
       <c r="B29" t="n">
-        <v>79659</v>
+        <v>79652</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4453,21 +4453,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525969</v>
+        <v>525970</v>
       </c>
       <c r="R29" t="n">
-        <v>7178936</v>
+        <v>7178901</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>på liggande död björkstam</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4550,22 +4550,22 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4583,10 +4583,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119731942</v>
+        <v>119731933</v>
       </c>
       <c r="B30" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4595,25 +4595,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4626,10 +4626,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525970</v>
+        <v>525971</v>
       </c>
       <c r="R30" t="n">
-        <v>7178901</v>
+        <v>7178801</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4671,12 +4671,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4692,26 +4687,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4729,10 +4704,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119731933</v>
+        <v>119731928</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4741,25 +4716,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4772,10 +4747,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525971</v>
+        <v>525916</v>
       </c>
       <c r="R31" t="n">
-        <v>7178801</v>
+        <v>7178775</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4807,7 +4782,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4817,7 +4792,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4833,6 +4813,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119731928</v>
+        <v>119731936</v>
       </c>
       <c r="B32" t="n">
         <v>79652</v>
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>525916</v>
+        <v>525983</v>
       </c>
       <c r="R32" t="n">
-        <v>7178775</v>
+        <v>7178824</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på asp</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119731936</v>
+        <v>119731965</v>
       </c>
       <c r="B33" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5008,25 +5008,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>525983</v>
+        <v>525945</v>
       </c>
       <c r="R33" t="n">
-        <v>7178824</v>
+        <v>7178975</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>på asp</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119731965</v>
+        <v>119731957</v>
       </c>
       <c r="B34" t="n">
         <v>79624</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>525945</v>
+        <v>525916</v>
       </c>
       <c r="R34" t="n">
         <v>7178975</v>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5288,7 +5288,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119731957</v>
+        <v>119731956</v>
       </c>
       <c r="B35" t="n">
         <v>79624</v>
@@ -5331,10 +5331,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>525916</v>
+        <v>525939</v>
       </c>
       <c r="R35" t="n">
-        <v>7178975</v>
+        <v>7178962</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5434,10 +5434,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119731956</v>
+        <v>119731952</v>
       </c>
       <c r="B36" t="n">
-        <v>79624</v>
+        <v>79652</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5446,25 +5446,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>525939</v>
+        <v>525970</v>
       </c>
       <c r="R36" t="n">
-        <v>7178962</v>
+        <v>7178943</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5580,10 +5580,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119731952</v>
+        <v>119731925</v>
       </c>
       <c r="B37" t="n">
-        <v>79652</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5592,30 +5592,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5623,10 +5628,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>525970</v>
+        <v>525849</v>
       </c>
       <c r="R37" t="n">
-        <v>7178943</v>
+        <v>7178772</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -5658,7 +5663,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5668,12 +5673,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5682,33 +5687,27 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5726,7 +5725,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119731925</v>
+        <v>119731880</v>
       </c>
       <c r="B38" t="n">
         <v>57320</v>
@@ -5774,10 +5773,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>525849</v>
+        <v>525751</v>
       </c>
       <c r="R38" t="n">
-        <v>7178772</v>
+        <v>7178999</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -5809,7 +5808,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5819,7 +5818,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5838,7 +5837,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5871,10 +5870,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119731880</v>
+        <v>119731874</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5887,31 +5886,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5919,10 +5913,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>525751</v>
+        <v>525790</v>
       </c>
       <c r="R39" t="n">
-        <v>7178999</v>
+        <v>7178955</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -5954,7 +5948,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5964,12 +5958,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5978,6 +5972,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5988,17 +5983,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119731874</v>
+        <v>119731891</v>
       </c>
       <c r="B40" t="n">
         <v>79624</v>
@@ -6059,10 +6059,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>525790</v>
+        <v>525653</v>
       </c>
       <c r="R40" t="n">
-        <v>7178955</v>
+        <v>7178999</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död högstubbe av sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119731891</v>
+        <v>119731898</v>
       </c>
       <c r="B41" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6178,21 +6178,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>525653</v>
+        <v>525707</v>
       </c>
       <c r="R41" t="n">
-        <v>7178999</v>
+        <v>7178873</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>på död högstubbe av sälg</t>
+          <t>på levande gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6275,22 +6275,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6308,10 +6308,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119731898</v>
+        <v>119731904</v>
       </c>
       <c r="B42" t="n">
-        <v>90576</v>
+        <v>79659</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6320,25 +6320,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>525707</v>
+        <v>525762</v>
       </c>
       <c r="R42" t="n">
-        <v>7178873</v>
+        <v>7178853</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>på levande gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6421,22 +6421,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6454,7 +6454,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119731904</v>
+        <v>119731916</v>
       </c>
       <c r="B43" t="n">
         <v>79659</v>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>525762</v>
+        <v>525842</v>
       </c>
       <c r="R43" t="n">
-        <v>7178853</v>
+        <v>7178769</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6600,10 +6600,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119731916</v>
+        <v>119731918</v>
       </c>
       <c r="B44" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6612,25 +6612,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>525842</v>
+        <v>525837</v>
       </c>
       <c r="R44" t="n">
-        <v>7178769</v>
+        <v>7178762</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6688,12 +6688,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>på levande sälg</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6709,26 +6704,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6746,10 +6721,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119731918</v>
+        <v>119731899</v>
       </c>
       <c r="B45" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6758,25 +6733,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -6789,10 +6764,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>525837</v>
+        <v>525724</v>
       </c>
       <c r="R45" t="n">
-        <v>7178762</v>
+        <v>7178884</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -6824,7 +6799,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6834,7 +6809,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>på levande asp</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6849,7 +6829,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6867,10 +6867,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119731899</v>
+        <v>119731851</v>
       </c>
       <c r="B46" t="n">
-        <v>79659</v>
+        <v>57320</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6879,30 +6879,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6910,10 +6915,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>525724</v>
+        <v>525862</v>
       </c>
       <c r="R46" t="n">
-        <v>7178884</v>
+        <v>7178784</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -6945,7 +6950,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6955,12 +6960,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>på levande asp</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6969,7 +6974,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6980,22 +6984,17 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7013,7 +7012,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119731851</v>
+        <v>119731896</v>
       </c>
       <c r="B47" t="n">
         <v>57320</v>
@@ -7061,10 +7060,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>525862</v>
+        <v>525699</v>
       </c>
       <c r="R47" t="n">
-        <v>7178784</v>
+        <v>7178908</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -7096,7 +7095,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -7106,7 +7105,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7158,10 +7157,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119731896</v>
+        <v>119731915</v>
       </c>
       <c r="B48" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7174,31 +7173,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -7206,10 +7200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>525699</v>
+        <v>525820</v>
       </c>
       <c r="R48" t="n">
-        <v>7178908</v>
+        <v>7178762</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -7241,7 +7235,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7251,12 +7245,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7265,27 +7254,13 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7303,10 +7278,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119731915</v>
+        <v>119731858</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7319,21 +7294,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -7346,10 +7321,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>525820</v>
+        <v>525845</v>
       </c>
       <c r="R49" t="n">
-        <v>7178762</v>
+        <v>7178853</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -7381,7 +7356,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7391,7 +7366,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7406,7 +7386,27 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7424,7 +7424,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119731858</v>
+        <v>119731855</v>
       </c>
       <c r="B50" t="n">
         <v>79624</v>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>525845</v>
+        <v>525852</v>
       </c>
       <c r="R50" t="n">
-        <v>7178853</v>
+        <v>7178820</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7547,12 +7547,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119731855</v>
+        <v>119731890</v>
       </c>
       <c r="B51" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7586,21 +7586,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>525852</v>
+        <v>525658</v>
       </c>
       <c r="R51" t="n">
-        <v>7178820</v>
+        <v>7178997</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7658,12 +7658,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>på död sälg</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7679,26 +7674,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7716,10 +7691,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119731890</v>
+        <v>119731912</v>
       </c>
       <c r="B52" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7732,26 +7707,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7759,10 +7739,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>525658</v>
+        <v>525763</v>
       </c>
       <c r="R52" t="n">
-        <v>7178997</v>
+        <v>7178776</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -7794,7 +7774,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7804,7 +7784,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7813,13 +7798,27 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7837,10 +7836,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119731912</v>
+        <v>119731866</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7853,31 +7852,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7885,10 +7879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>525763</v>
+        <v>525806</v>
       </c>
       <c r="R53" t="n">
-        <v>7178776</v>
+        <v>7178927</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -7920,7 +7914,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7930,12 +7924,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7944,27 +7933,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7982,10 +7957,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119731866</v>
+        <v>119731917</v>
       </c>
       <c r="B54" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7998,21 +7973,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -8025,10 +8000,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>525806</v>
+        <v>525842</v>
       </c>
       <c r="R54" t="n">
-        <v>7178927</v>
+        <v>7178769</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -8060,7 +8035,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -8070,7 +8045,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8085,7 +8065,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8103,7 +8103,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119731917</v>
+        <v>119731856</v>
       </c>
       <c r="B55" t="n">
         <v>79624</v>
@@ -8146,10 +8146,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>525842</v>
+        <v>525854</v>
       </c>
       <c r="R55" t="n">
-        <v>7178769</v>
+        <v>7178867</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -8249,10 +8249,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119731856</v>
+        <v>119731914</v>
       </c>
       <c r="B56" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -8265,21 +8265,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>525854</v>
+        <v>525792</v>
       </c>
       <c r="R56" t="n">
-        <v>7178867</v>
+        <v>7178785</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på gammal stubbe</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8362,22 +8362,22 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8395,10 +8395,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119731914</v>
+        <v>119731900</v>
       </c>
       <c r="B57" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8411,37 +8411,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>525792</v>
+        <v>525738</v>
       </c>
       <c r="R57" t="n">
-        <v>7178785</v>
+        <v>7178870</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -8473,7 +8470,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8483,12 +8480,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>på gammal stubbe</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8497,34 +8489,8 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -8541,10 +8507,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119731900</v>
+        <v>119731883</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8553,38 +8519,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Björnberget, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>525738</v>
+        <v>525725</v>
       </c>
       <c r="R58" t="n">
-        <v>7178870</v>
+        <v>7178979</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8616,7 +8585,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8626,7 +8595,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8635,8 +8609,34 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -8653,10 +8653,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119731883</v>
+        <v>119731903</v>
       </c>
       <c r="B59" t="n">
-        <v>79659</v>
+        <v>79624</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8665,25 +8665,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>525725</v>
+        <v>525774</v>
       </c>
       <c r="R59" t="n">
-        <v>7178979</v>
+        <v>7178852</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på död sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8799,10 +8799,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119731903</v>
+        <v>119731854</v>
       </c>
       <c r="B60" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8815,21 +8815,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>525774</v>
+        <v>525857</v>
       </c>
       <c r="R60" t="n">
-        <v>7178852</v>
+        <v>7178804</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>på död sälg</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8908,26 +8908,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8945,7 +8925,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119731854</v>
+        <v>119731913</v>
       </c>
       <c r="B61" t="n">
         <v>78542</v>
@@ -8988,10 +8968,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>525857</v>
+        <v>525778</v>
       </c>
       <c r="R61" t="n">
-        <v>7178804</v>
+        <v>7178782</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -9023,7 +9003,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -9033,12 +9013,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>riklig förekomst</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -9071,10 +9046,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119731913</v>
+        <v>119731875</v>
       </c>
       <c r="B62" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -9087,26 +9062,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -9114,10 +9094,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>525778</v>
+        <v>525792</v>
       </c>
       <c r="R62" t="n">
-        <v>7178782</v>
+        <v>7178967</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -9149,7 +9129,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -9159,7 +9139,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -9168,13 +9153,27 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9192,10 +9191,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119731875</v>
+        <v>119731884</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9208,31 +9207,26 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -9240,10 +9234,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>525792</v>
+        <v>525725</v>
       </c>
       <c r="R63" t="n">
-        <v>7178967</v>
+        <v>7178979</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -9275,7 +9269,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -9285,12 +9279,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -9299,6 +9293,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -9309,17 +9304,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9337,7 +9337,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119731884</v>
+        <v>119731888</v>
       </c>
       <c r="B64" t="n">
         <v>79624</v>
@@ -9380,10 +9380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>525725</v>
+        <v>525689</v>
       </c>
       <c r="R64" t="n">
-        <v>7178979</v>
+        <v>7179025</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9483,7 +9483,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119731888</v>
+        <v>119731902</v>
       </c>
       <c r="B65" t="n">
         <v>79624</v>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>525689</v>
+        <v>525769</v>
       </c>
       <c r="R65" t="n">
-        <v>7179025</v>
+        <v>7178869</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på levande liggande sälg</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9629,10 +9629,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119731902</v>
+        <v>119731882</v>
       </c>
       <c r="B66" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9645,21 +9645,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -9672,10 +9672,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>525769</v>
+        <v>525731</v>
       </c>
       <c r="R66" t="n">
-        <v>7178869</v>
+        <v>7178963</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>på levande liggande sälg</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9742,22 +9742,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9775,10 +9775,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119731882</v>
+        <v>119731838</v>
       </c>
       <c r="B67" t="n">
-        <v>90576</v>
+        <v>79652</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9787,25 +9787,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>525731</v>
+        <v>525933</v>
       </c>
       <c r="R67" t="n">
-        <v>7178963</v>
+        <v>7178937</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9888,22 +9888,22 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119731838</v>
+        <v>119731863</v>
       </c>
       <c r="B68" t="n">
-        <v>79652</v>
+        <v>79624</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9933,25 +9933,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9964,10 +9964,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>525933</v>
+        <v>525807</v>
       </c>
       <c r="R68" t="n">
-        <v>7178937</v>
+        <v>7178896</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -10067,7 +10067,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119731863</v>
+        <v>119731868</v>
       </c>
       <c r="B69" t="n">
         <v>79624</v>
@@ -10110,10 +10110,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>525807</v>
+        <v>525802</v>
       </c>
       <c r="R69" t="n">
-        <v>7178896</v>
+        <v>7178930</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -10213,7 +10213,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119731868</v>
+        <v>119731848</v>
       </c>
       <c r="B70" t="n">
         <v>79624</v>
@@ -10256,10 +10256,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>525802</v>
+        <v>525936</v>
       </c>
       <c r="R70" t="n">
-        <v>7178930</v>
+        <v>7178808</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10291,7 +10291,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blandskog i branter</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -10359,10 +10359,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119731848</v>
+        <v>119731850</v>
       </c>
       <c r="B71" t="n">
-        <v>79624</v>
+        <v>90576</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -10375,21 +10375,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10402,10 +10402,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>525936</v>
+        <v>525907</v>
       </c>
       <c r="R71" t="n">
-        <v>7178808</v>
+        <v>7178822</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>på 2 stående döda granar</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10472,22 +10472,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10505,10 +10505,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119731850</v>
+        <v>119731839</v>
       </c>
       <c r="B72" t="n">
-        <v>90576</v>
+        <v>79624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10521,21 +10521,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>525907</v>
+        <v>525933</v>
       </c>
       <c r="R72" t="n">
-        <v>7178822</v>
+        <v>7178937</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10593,12 +10593,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>på 2 stående döda granar</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10613,27 +10613,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Blandskog i branter</t>
+          <t>Blandskog på blockmark</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10651,7 +10651,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119731839</v>
+        <v>119731897</v>
       </c>
       <c r="B73" t="n">
         <v>79624</v>
@@ -10694,10 +10694,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>525933</v>
+        <v>525705</v>
       </c>
       <c r="R73" t="n">
-        <v>7178937</v>
+        <v>7178875</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
@@ -10797,10 +10797,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119731897</v>
+        <v>119731840</v>
       </c>
       <c r="B74" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10813,26 +10813,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -10840,10 +10845,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>525705</v>
+        <v>525933</v>
       </c>
       <c r="R74" t="n">
-        <v>7178875</v>
+        <v>7178939</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -10875,7 +10880,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10885,12 +10890,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10899,7 +10904,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -10910,22 +10914,17 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10943,7 +10942,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119731840</v>
+        <v>119731887</v>
       </c>
       <c r="B75" t="n">
         <v>57320</v>
@@ -10991,10 +10990,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>525933</v>
+        <v>525707</v>
       </c>
       <c r="R75" t="n">
-        <v>7178939</v>
+        <v>7178998</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -11026,7 +11025,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -11036,7 +11035,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
@@ -11088,7 +11087,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119731887</v>
+        <v>119731907</v>
       </c>
       <c r="B76" t="n">
         <v>57320</v>
@@ -11136,10 +11135,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>525707</v>
+        <v>525765</v>
       </c>
       <c r="R76" t="n">
-        <v>7178998</v>
+        <v>7178799</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -11171,7 +11170,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -11181,7 +11180,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -11233,10 +11232,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119731907</v>
+        <v>119731865</v>
       </c>
       <c r="B77" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -11249,31 +11248,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -11281,10 +11275,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>525765</v>
+        <v>525818</v>
       </c>
       <c r="R77" t="n">
-        <v>7178799</v>
+        <v>7178903</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -11316,7 +11310,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -11326,12 +11320,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -11340,6 +11334,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -11350,17 +11345,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -11378,10 +11378,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119731865</v>
+        <v>119731867</v>
       </c>
       <c r="B78" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -11394,21 +11394,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -11421,10 +11421,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>525818</v>
+        <v>525802</v>
       </c>
       <c r="R78" t="n">
-        <v>7178903</v>
+        <v>7178930</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
@@ -11524,10 +11524,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119731867</v>
+        <v>119731861</v>
       </c>
       <c r="B79" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11540,21 +11540,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -11567,10 +11567,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>525802</v>
+        <v>525826</v>
       </c>
       <c r="R79" t="n">
-        <v>7178930</v>
+        <v>7178869</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
@@ -11670,10 +11670,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119731861</v>
+        <v>119731876</v>
       </c>
       <c r="B80" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11686,26 +11686,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -11713,10 +11718,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>525826</v>
+        <v>525781</v>
       </c>
       <c r="R80" t="n">
-        <v>7178869</v>
+        <v>7178998</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -11748,7 +11753,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11758,12 +11763,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11772,7 +11777,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -11783,22 +11787,17 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11816,7 +11815,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119731876</v>
+        <v>119731843</v>
       </c>
       <c r="B81" t="n">
         <v>57320</v>
@@ -11864,10 +11863,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>525781</v>
+        <v>525949</v>
       </c>
       <c r="R81" t="n">
-        <v>7178998</v>
+        <v>7178888</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -11899,7 +11898,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11909,7 +11908,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -11961,7 +11960,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119731843</v>
+        <v>119731857</v>
       </c>
       <c r="B82" t="n">
         <v>57320</v>
@@ -12009,10 +12008,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>525949</v>
+        <v>525853</v>
       </c>
       <c r="R82" t="n">
-        <v>7178888</v>
+        <v>7178853</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -12044,7 +12043,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -12054,7 +12053,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -12106,10 +12105,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119731857</v>
+        <v>119731906</v>
       </c>
       <c r="B83" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12122,31 +12121,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -12154,10 +12148,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>525853</v>
+        <v>525765</v>
       </c>
       <c r="R83" t="n">
-        <v>7178853</v>
+        <v>7178799</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -12189,7 +12183,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -12199,12 +12193,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>på död stående gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -12213,6 +12207,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -12231,9 +12226,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -12251,10 +12251,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119731906</v>
+        <v>119731870</v>
       </c>
       <c r="B84" t="n">
-        <v>90576</v>
+        <v>79659</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -12263,25 +12263,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -12294,10 +12294,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>525765</v>
+        <v>525790</v>
       </c>
       <c r="R84" t="n">
-        <v>7178799</v>
+        <v>7178955</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>på död stående gran</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -12364,22 +12364,22 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -12397,10 +12397,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119731870</v>
+        <v>119731910</v>
       </c>
       <c r="B85" t="n">
-        <v>79659</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -12409,30 +12409,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -12440,10 +12445,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>525790</v>
+        <v>525767</v>
       </c>
       <c r="R85" t="n">
-        <v>7178955</v>
+        <v>7178808</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -12475,7 +12480,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12485,12 +12490,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12499,7 +12504,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -12510,22 +12514,17 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12543,10 +12542,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119731910</v>
+        <v>119731895</v>
       </c>
       <c r="B86" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12559,31 +12558,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12591,10 +12585,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>525767</v>
+        <v>525699</v>
       </c>
       <c r="R86" t="n">
-        <v>7178808</v>
+        <v>7178908</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -12626,7 +12620,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12636,12 +12630,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12650,27 +12644,13 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12688,10 +12668,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119731895</v>
+        <v>119731901</v>
       </c>
       <c r="B87" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12704,26 +12684,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -12731,10 +12716,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>525699</v>
+        <v>525747</v>
       </c>
       <c r="R87" t="n">
-        <v>7178908</v>
+        <v>7178865</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -12766,7 +12751,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12776,12 +12761,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12790,13 +12775,27 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12814,7 +12813,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119731901</v>
+        <v>119731860</v>
       </c>
       <c r="B88" t="n">
         <v>57320</v>
@@ -12852,7 +12851,7 @@
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
@@ -12862,10 +12861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>525747</v>
+        <v>525848</v>
       </c>
       <c r="R88" t="n">
-        <v>7178865</v>
+        <v>7178857</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -12897,7 +12896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12907,12 +12906,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12959,10 +12958,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119731860</v>
+        <v>119731905</v>
       </c>
       <c r="B89" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12975,31 +12974,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -13007,10 +13001,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>525848</v>
+        <v>525762</v>
       </c>
       <c r="R89" t="n">
-        <v>7178857</v>
+        <v>7178853</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -13042,7 +13036,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -13052,12 +13046,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -13066,6 +13060,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -13084,9 +13079,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -13104,7 +13104,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119731905</v>
+        <v>119731842</v>
       </c>
       <c r="B90" t="n">
         <v>79624</v>
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>525762</v>
+        <v>525950</v>
       </c>
       <c r="R90" t="n">
-        <v>7178853</v>
+        <v>7178893</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -13192,12 +13192,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>på levande sälg samt på gren av levande gran som växte in under sälgen</t>
+          <t>på levande sälg</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -13217,12 +13217,12 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -13250,7 +13250,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119731842</v>
+        <v>119731881</v>
       </c>
       <c r="B91" t="n">
         <v>79624</v>
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>525950</v>
+        <v>525738</v>
       </c>
       <c r="R91" t="n">
-        <v>7178893</v>
+        <v>7178966</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
@@ -13396,10 +13396,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119731881</v>
+        <v>119731853</v>
       </c>
       <c r="B92" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13412,26 +13412,31 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -13439,10 +13444,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>525738</v>
+        <v>525853</v>
       </c>
       <c r="R92" t="n">
-        <v>7178966</v>
+        <v>7178800</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -13474,7 +13479,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13484,12 +13489,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>på levande sälg</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13498,7 +13503,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -13509,22 +13513,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -13542,10 +13541,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119731853</v>
+        <v>119731889</v>
       </c>
       <c r="B93" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13558,31 +13557,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -13590,10 +13584,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>525853</v>
+        <v>525688</v>
       </c>
       <c r="R93" t="n">
-        <v>7178800</v>
+        <v>7179014</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -13625,7 +13619,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13635,12 +13629,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>riklig förekomst</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13649,27 +13643,13 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -13687,7 +13667,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119731889</v>
+        <v>119731893</v>
       </c>
       <c r="B94" t="n">
         <v>78542</v>
@@ -13730,10 +13710,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>525688</v>
+        <v>525694</v>
       </c>
       <c r="R94" t="n">
-        <v>7179014</v>
+        <v>7178950</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -13765,7 +13745,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13775,7 +13755,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -13813,10 +13793,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119731893</v>
+        <v>119731885</v>
       </c>
       <c r="B95" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13829,26 +13809,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -13856,10 +13841,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>525694</v>
+        <v>525697</v>
       </c>
       <c r="R95" t="n">
-        <v>7178950</v>
+        <v>7179006</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -13891,7 +13876,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13901,12 +13886,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>riklig förekomst</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13915,13 +13900,27 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
           <t>Blandskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13939,7 +13938,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119731885</v>
+        <v>119731841</v>
       </c>
       <c r="B96" t="n">
         <v>57320</v>
@@ -13977,7 +13976,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -13987,10 +13986,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>525697</v>
+        <v>525940</v>
       </c>
       <c r="R96" t="n">
-        <v>7179006</v>
+        <v>7178908</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -14022,7 +14021,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -14032,12 +14031,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -14084,10 +14083,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119731841</v>
+        <v>119894773</v>
       </c>
       <c r="B97" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -14100,31 +14099,26 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -14132,10 +14126,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>525940</v>
+        <v>525799</v>
       </c>
       <c r="R97" t="n">
-        <v>7178908</v>
+        <v>7178770</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -14162,27 +14156,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>på gran stubbe</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -14191,12 +14185,13 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Blandskog på blockmark</t>
+          <t>Blåbärsblandskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -14209,9 +14204,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -14229,14 +14229,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119894773</v>
+        <v>119894748</v>
       </c>
       <c r="B98" t="n">
-        <v>90576</v>
+        <v>90679</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -14245,21 +14245,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -14322,7 +14322,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>på gran stubbe</t>
+          <t>på granlåga med bark</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -14352,12 +14352,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -14372,152 +14372,6 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>119894748</v>
-      </c>
-      <c r="B99" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Björnberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q99" t="n">
-        <v>525799</v>
-      </c>
-      <c r="R99" t="n">
-        <v>7178770</v>
-      </c>
-      <c r="S99" t="n">
-        <v>15</v>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>Dorotea</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>2024-09-20</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:43</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>på granlåga med bark</t>
-        </is>
-      </c>
-      <c r="AD99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>Blåbärsblandskog</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT99" t="inlineStr"/>
-      <c r="AW99" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>Eva Mårtensson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
